--- a/word/elementary_words_ko_zh.xlsx
+++ b/word/elementary_words_ko_zh.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Grape</t>
+          <t>grape</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>strawberry</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Peach</t>
+          <t>peach</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Watermelon</t>
+          <t>watermelon</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>lemon</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Melon</t>
+          <t>melon</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>tomato</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Juice</t>
+          <t>juice</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>rice</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Egg</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cake</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Candy</t>
+          <t>candy</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Cookie</t>
+          <t>cookie</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>chocolate</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Ice cream</t>
+          <t>ice cream</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Pizza</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Hamburger</t>
+          <t>hamburger</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Noodle</t>
+          <t>noodle</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Soup</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Salad</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>cheese</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>butter</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cherry</t>
+          <t>cherry</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>potato</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>carrot</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Onion</t>
+          <t>onion</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Corn</t>
+          <t>corn</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>salt</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>honey</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Pie</t>
+          <t>pie</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Donut</t>
+          <t>donut</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Sandwich</t>
+          <t>sandwich</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Sausage</t>
+          <t>sausage</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Pork</t>
+          <t>pork</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Beef</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Jam</t>
+          <t>jam</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>oil</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>bacon</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Bagel</t>
+          <t>bagel</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Bean</t>
+          <t>bean</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Berry</t>
+          <t>berry</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Biscuit</t>
+          <t>biscuit</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Coconut</t>
+          <t>coconut</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Jelly</t>
+          <t>jelly</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>mango</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Kiwi</t>
+          <t>kiwi</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Plum</t>
+          <t>plum</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Blueberry</t>
+          <t>blueberry</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Chestnut</t>
+          <t>chestnut</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Walnut</t>
+          <t>walnut</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Peanut</t>
+          <t>peanut</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Almond</t>
+          <t>almond</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>cabbage</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Lettuce</t>
+          <t>lettuce</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Spinach</t>
+          <t>spinach</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Pumpkin</t>
+          <t>pumpkin</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Garlic</t>
+          <t>garlic</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Cucumber</t>
+          <t>cucumber</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Ham</t>
+          <t>ham</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Shrimp</t>
+          <t>shrimp</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Tuna</t>
+          <t>tuna</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Seaweed</t>
+          <t>seaweed</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Tofu</t>
+          <t>tofu</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Dumpling</t>
+          <t>dumpling</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Pancake</t>
+          <t>pancake</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Flour</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Pepper</t>
+          <t>pepper</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Sauce</t>
+          <t>sauce</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Stew</t>
+          <t>stew</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Cereal</t>
+          <t>cereal</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t>bird</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Duck</t>
+          <t>duck</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>pig</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>cow</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Sheep</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Bear</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>lion</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>tiger</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>elephant</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>giraffe</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Monkey</t>
+          <t>monkey</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Fox</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Turtle</t>
+          <t>turtle</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>whale</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>dolphin</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>shark</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Mouse</t>
+          <t>mouse</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>butterfly</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>ant</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>spider</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Penguin</t>
+          <t>penguin</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Panda</t>
+          <t>panda</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Deer</t>
+          <t>deer</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Zebra</t>
+          <t>zebra</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Koala</t>
+          <t>koala</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Owl</t>
+          <t>owl</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>eagle</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Bat</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Crab</t>
+          <t>crab</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>octopus</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Camel</t>
+          <t>camel</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Goat</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Donkey</t>
+          <t>donkey</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Beak</t>
+          <t>beak</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Beaver</t>
+          <t>beaver</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>calf</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Dinosaur</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>insect</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Kangaroo</t>
+          <t>kangaroo</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Kitten</t>
+          <t>kitten</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>lizard</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>Squirrel</t>
+          <t>squirrel</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Rat</t>
+          <t>rat</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Hamster</t>
+          <t>hamster</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Crocodile</t>
+          <t>crocodile</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Jellyfish</t>
+          <t>jellyfish</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Starfish</t>
+          <t>starfish</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>Seal</t>
+          <t>seal</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>crow</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>sparrow</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Pigeon</t>
+          <t>pigeon</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>parrot</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>peacock</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>swan</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Goose</t>
+          <t>goose</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>Hippo</t>
+          <t>hippo</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Snail</t>
+          <t>snail</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>Worm</t>
+          <t>worm</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Beetle</t>
+          <t>beetle</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>grasshopper</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Dragonfly</t>
+          <t>dragonfly</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Firefly</t>
+          <t>firefly</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Mosquito</t>
+          <t>mosquito</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>caterpillar</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Moth</t>
+          <t>moth</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>Ladybug</t>
+          <t>ladybug</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>wing</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Tail</t>
+          <t>tail</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Paw</t>
+          <t>paw</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>baby</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Grandfather</t>
+          <t>grandfather</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>grandmother</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>boy</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>girl</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>man</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Woman</t>
+          <t>woman</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>Child</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>king</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Queen</t>
+          <t>queen</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>hero</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>Party</t>
+          <t>party</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>angel</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>beauty</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Cousin</t>
+          <t>cousin</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>monster</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>Nephew</t>
+          <t>nephew</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Niece</t>
+          <t>niece</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>twin</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Kid</t>
+          <t>kid</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>Classmate</t>
+          <t>classmate</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Roommate</t>
+          <t>roommate</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>Grandchild</t>
+          <t>grandchild</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>grandson</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B199" s="7" t="inlineStr">
         <is>
-          <t>Granddaughter</t>
+          <t>granddaughter</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Gentleman</t>
+          <t>gentleman</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B201" s="7" t="inlineStr">
         <is>
-          <t>Lady</t>
+          <t>lady</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Neighborhood</t>
+          <t>neighborhood</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="B203" s="7" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Farmer</t>
+          <t>farmer</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="B207" s="7" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>cook</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>police</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="B209" s="7" t="inlineStr">
         <is>
-          <t>Firefighter</t>
+          <t>firefighter</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Singer</t>
+          <t>singer</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="B211" s="7" t="inlineStr">
         <is>
-          <t>Dancer</t>
+          <t>dancer</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="B213" s="7" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>driver</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>actor</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Actress</t>
+          <t>actress</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>Artist</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Barber</t>
+          <t>barber</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>Chef</t>
+          <t>chef</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Clown</t>
+          <t>clown</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="B221" s="7" t="inlineStr">
         <is>
-          <t>Dentist</t>
+          <t>dentist</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="B223" s="7" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>baker</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Tailor</t>
+          <t>tailor</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>Sailor</t>
+          <t>sailor</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Scientist</t>
+          <t>scientist</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="B227" s="7" t="inlineStr">
         <is>
-          <t>Reporter</t>
+          <t>reporter</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Photographer</t>
+          <t>photographer</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>designer</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Mechanic</t>
+          <t>mechanic</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="B231" s="7" t="inlineStr">
         <is>
-          <t>Carpenter</t>
+          <t>carpenter</t>
         </is>
       </c>
       <c r="C231" s="6" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Gardener</t>
+          <t>gardener</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B233" s="7" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>head</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Hair</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="B235" s="7" t="inlineStr">
         <is>
-          <t>Eye</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Nose</t>
+          <t>nose</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="B237" s="7" t="inlineStr">
         <is>
-          <t>Mouth</t>
+          <t>mouth</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Ear</t>
+          <t>ear</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B239" s="7" t="inlineStr">
         <is>
-          <t>Tooth</t>
+          <t>tooth</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B241" s="7" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="C241" s="6" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Finger</t>
+          <t>finger</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B243" s="7" t="inlineStr">
         <is>
-          <t>Arm</t>
+          <t>arm</t>
         </is>
       </c>
       <c r="C243" s="6" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Leg</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="B245" s="7" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>foot</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Neck</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B247" s="7" t="inlineStr">
         <is>
-          <t>Shoulder</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Toe</t>
+          <t>toe</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="B249" s="7" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>voice</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="B251" s="7" t="inlineStr">
         <is>
-          <t>Beard</t>
+          <t>beard</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Bone</t>
+          <t>bone</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="B253" s="7" t="inlineStr">
         <is>
-          <t>Brain</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="C253" s="6" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="B255" s="7" t="inlineStr">
         <is>
-          <t>Chin</t>
+          <t>chin</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Claw</t>
+          <t>claw</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B257" s="7" t="inlineStr">
         <is>
-          <t>Feather</t>
+          <t>feather</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>fingerprint</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>Horn</t>
+          <t>horn</t>
         </is>
       </c>
       <c r="C259" s="6" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Forehead</t>
+          <t>forehead</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="B261" s="7" t="inlineStr">
         <is>
-          <t>Cheek</t>
+          <t>cheek</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Throat</t>
+          <t>throat</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>Elbow</t>
+          <t>elbow</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Wrist</t>
+          <t>wrist</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>Palm</t>
+          <t>palm</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Thumb</t>
+          <t>thumb</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="B267" s="7" t="inlineStr">
         <is>
-          <t>Waist</t>
+          <t>waist</t>
         </is>
       </c>
       <c r="C267" s="6" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>hip</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>thigh</t>
         </is>
       </c>
       <c r="C269" s="6" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Cap</t>
+          <t>cap</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>Hat</t>
+          <t>hat</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Shirt</t>
+          <t>shirt</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="B273" s="7" t="inlineStr">
         <is>
-          <t>Pants</t>
+          <t>pants</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Shoes</t>
+          <t>shoes</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="B275" s="7" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>pocket</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Apron</t>
+          <t>apron</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B277" s="7" t="inlineStr">
         <is>
-          <t>Badge</t>
+          <t>badge</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Belt</t>
+          <t>belt</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="B279" s="7" t="inlineStr">
         <is>
-          <t>Blouse</t>
+          <t>blouse</t>
         </is>
       </c>
       <c r="C279" s="6" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Coat</t>
+          <t>coat</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="B281" s="7" t="inlineStr">
         <is>
-          <t>Collar</t>
+          <t>collar</t>
         </is>
       </c>
       <c r="C281" s="6" t="inlineStr">
@@ -15983,7 +15983,7 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Crown</t>
+          <t>crown</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="B283" s="7" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>dress</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Glove</t>
+          <t>glove</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B285" s="7" t="inlineStr">
         <is>
-          <t>Helmet</t>
+          <t>helmet</t>
         </is>
       </c>
       <c r="C285" s="6" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="B287" s="7" t="inlineStr">
         <is>
-          <t>Skirt</t>
+          <t>skirt</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Sweater</t>
+          <t>sweater</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B289" s="7" t="inlineStr">
         <is>
-          <t>Vest</t>
+          <t>vest</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
@@ -16423,7 +16423,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>jeans</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="B291" s="7" t="inlineStr">
         <is>
-          <t>Shorts</t>
+          <t>shorts</t>
         </is>
       </c>
       <c r="C291" s="6" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Boots</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="B293" s="7" t="inlineStr">
         <is>
-          <t>Sandals</t>
+          <t>sandals</t>
         </is>
       </c>
       <c r="C293" s="6" t="inlineStr">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Sneakers</t>
+          <t>sneakers</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B295" s="7" t="inlineStr">
         <is>
-          <t>Slippers</t>
+          <t>slippers</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Gloves</t>
+          <t>gloves</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="B297" s="7" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="B299" s="7" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>pen</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="B301" s="7" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>eraser</t>
         </is>
       </c>
       <c r="C301" s="6" t="inlineStr">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Ruler</t>
+          <t>ruler</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="B303" s="7" t="inlineStr">
         <is>
-          <t>Crayon</t>
+          <t>crayon</t>
         </is>
       </c>
       <c r="C303" s="6" t="inlineStr">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Scissors</t>
+          <t>scissors</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -17248,7 +17248,7 @@
       </c>
       <c r="B305" s="7" t="inlineStr">
         <is>
-          <t>Glue</t>
+          <t>glue</t>
         </is>
       </c>
       <c r="C305" s="6" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>notebook</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>bag</t>
         </is>
       </c>
       <c r="C307" s="6" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>desk</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="C309" s="6" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Classroom</t>
+          <t>classroom</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -17578,7 +17578,7 @@
       </c>
       <c r="B311" s="7" t="inlineStr">
         <is>
-          <t>Blackboard</t>
+          <t>blackboard</t>
         </is>
       </c>
       <c r="C311" s="6" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Computer</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="B313" s="7" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>paper</t>
         </is>
       </c>
       <c r="C313" s="6" t="inlineStr">
@@ -17743,7 +17743,7 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>board</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="B315" s="7" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C315" s="6" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -17908,7 +17908,7 @@
       </c>
       <c r="B317" s="7" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C317" s="6" t="inlineStr">
@@ -17963,7 +17963,7 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="B319" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C319" s="6" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>class</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="B321" s="7" t="inlineStr">
         <is>
-          <t>Lesson</t>
+          <t>lesson</t>
         </is>
       </c>
       <c r="C321" s="6" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="B323" s="7" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C323" s="6" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="B325" s="7" t="inlineStr">
         <is>
-          <t>Chalk</t>
+          <t>chalk</t>
         </is>
       </c>
       <c r="C325" s="6" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Comic</t>
+          <t>comic</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="B327" s="7" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>cube</t>
         </is>
       </c>
       <c r="C327" s="6" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Diary</t>
+          <t>diary</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="B329" s="7" t="inlineStr">
         <is>
-          <t>Dictionary</t>
+          <t>dictionary</t>
         </is>
       </c>
       <c r="C329" s="6" t="inlineStr">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Globe</t>
+          <t>globe</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="B331" s="7" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>grammar</t>
         </is>
       </c>
       <c r="C331" s="6" t="inlineStr">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Magnet</t>
+          <t>magnet</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="B333" s="7" t="inlineStr">
         <is>
-          <t>Playground</t>
+          <t>playground</t>
         </is>
       </c>
       <c r="C333" s="6" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Gym</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="B335" s="7" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>cafeteria</t>
         </is>
       </c>
       <c r="C335" s="6" t="inlineStr">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Homework</t>
+          <t>homework</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="B337" s="7" t="inlineStr">
         <is>
-          <t>Workbook</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="C337" s="6" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Stapler</t>
+          <t>stapler</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="B339" s="7" t="inlineStr">
         <is>
-          <t>Marker</t>
+          <t>marker</t>
         </is>
       </c>
       <c r="C339" s="6" t="inlineStr">
@@ -19173,7 +19173,7 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Highlighter</t>
+          <t>highlighter</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -19228,7 +19228,7 @@
       </c>
       <c r="B341" s="7" t="inlineStr">
         <is>
-          <t>Whiteboard</t>
+          <t>whiteboard</t>
         </is>
       </c>
       <c r="C341" s="6" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>Locker</t>
+          <t>locker</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="B343" s="7" t="inlineStr">
         <is>
-          <t>Sharpener</t>
+          <t>sharpener</t>
         </is>
       </c>
       <c r="C343" s="6" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Calculator</t>
+          <t>calculator</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="B345" s="7" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>bell</t>
         </is>
       </c>
       <c r="C345" s="6" t="inlineStr">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>chart</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="B347" s="7" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>model</t>
         </is>
       </c>
       <c r="C347" s="6" t="inlineStr">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Timetable</t>
+          <t>timetable</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B349" s="7" t="inlineStr">
         <is>
-          <t>Clock</t>
+          <t>clock</t>
         </is>
       </c>
       <c r="C349" s="6" t="inlineStr">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="B351" s="7" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>house</t>
         </is>
       </c>
       <c r="C351" s="6" t="inlineStr">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>door</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="B353" s="7" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>window</t>
         </is>
       </c>
       <c r="C353" s="6" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>room</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -19998,7 +19998,7 @@
       </c>
       <c r="B355" s="7" t="inlineStr">
         <is>
-          <t>Bed</t>
+          <t>bed</t>
         </is>
       </c>
       <c r="C355" s="6" t="inlineStr">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -20108,7 +20108,7 @@
       </c>
       <c r="B357" s="7" t="inlineStr">
         <is>
-          <t>Cup</t>
+          <t>cup</t>
         </is>
       </c>
       <c r="C357" s="6" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Spoon</t>
+          <t>spoon</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="B359" s="7" t="inlineStr">
         <is>
-          <t>Fork</t>
+          <t>fork</t>
         </is>
       </c>
       <c r="C359" s="6" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Plate</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="B361" s="7" t="inlineStr">
         <is>
-          <t>Towel</t>
+          <t>towel</t>
         </is>
       </c>
       <c r="C361" s="6" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Soap</t>
+          <t>soap</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="B363" s="7" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>key</t>
         </is>
       </c>
       <c r="C363" s="6" t="inlineStr">
@@ -20493,7 +20493,7 @@
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="B365" s="7" t="inlineStr">
         <is>
-          <t>Television</t>
+          <t>television</t>
         </is>
       </c>
       <c r="C365" s="6" t="inlineStr">
@@ -20603,7 +20603,7 @@
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>Toy</t>
+          <t>toy</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="B367" s="7" t="inlineStr">
         <is>
-          <t>Doll</t>
+          <t>doll</t>
         </is>
       </c>
       <c r="C367" s="6" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>Umbrella</t>
+          <t>umbrella</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -20768,7 +20768,7 @@
       </c>
       <c r="B369" s="7" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="C369" s="6" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>calendar</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="B371" s="7" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>map</t>
         </is>
       </c>
       <c r="C371" s="6" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>box</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="B373" s="7" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C373" s="6" t="inlineStr">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="B375" s="7" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>mirror</t>
         </is>
       </c>
       <c r="C375" s="6" t="inlineStr">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -21208,7 +21208,7 @@
       </c>
       <c r="B377" s="7" t="inlineStr">
         <is>
-          <t>Bowl</t>
+          <t>bowl</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -21318,7 +21318,7 @@
       </c>
       <c r="B379" s="7" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>gift</t>
         </is>
       </c>
       <c r="C379" s="6" t="inlineStr">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="B381" s="7" t="inlineStr">
         <is>
-          <t>Basket</t>
+          <t>basket</t>
         </is>
       </c>
       <c r="C381" s="6" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Letter</t>
+          <t>letter</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="B383" s="7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C383" s="6" t="inlineStr">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="B385" s="7" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C385" s="6" t="inlineStr">
@@ -21703,7 +21703,7 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>story</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="B387" s="7" t="inlineStr">
         <is>
-          <t>Novel</t>
+          <t>novel</t>
         </is>
       </c>
       <c r="C387" s="6" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Poem</t>
+          <t>poem</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -21868,7 +21868,7 @@
       </c>
       <c r="B389" s="7" t="inlineStr">
         <is>
-          <t>Picture</t>
+          <t>picture</t>
         </is>
       </c>
       <c r="C389" s="6" t="inlineStr">
@@ -21923,7 +21923,7 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>Photo</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="B391" s="7" t="inlineStr">
         <is>
-          <t>Film</t>
+          <t>film</t>
         </is>
       </c>
       <c r="C391" s="6" t="inlineStr">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>Yard</t>
+          <t>yard</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="B393" s="7" t="inlineStr">
         <is>
-          <t>Antenna</t>
+          <t>antenna</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>Arrow</t>
+          <t>arrow</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="B395" s="7" t="inlineStr">
         <is>
-          <t>Axe</t>
+          <t>axe</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="B397" s="7" t="inlineStr">
         <is>
-          <t>Balloon</t>
+          <t>balloon</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>Bandage</t>
+          <t>bandage</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="B399" s="7" t="inlineStr">
         <is>
-          <t>Barrel</t>
+          <t>barrel</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>Basement</t>
+          <t>basement</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="B401" s="7" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
@@ -22583,7 +22583,7 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>Bench</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="B403" s="7" t="inlineStr">
         <is>
-          <t>Bin</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
@@ -22693,7 +22693,7 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>Bottle</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="B405" s="7" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>brick</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>Broom</t>
+          <t>broom</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="B407" s="7" t="inlineStr">
         <is>
-          <t>Bucket</t>
+          <t>bucket</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>Bulb</t>
+          <t>bulb</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="B409" s="7" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>Cage</t>
+          <t>cage</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="B411" s="7" t="inlineStr">
         <is>
-          <t>Candle</t>
+          <t>candle</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>Chimney</t>
+          <t>chimney</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
@@ -23188,7 +23188,7 @@
       </c>
       <c r="B413" s="7" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>compass</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>Cottage</t>
+          <t>cottage</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="B415" s="7" t="inlineStr">
         <is>
-          <t>Curtain</t>
+          <t>curtain</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>Cushion</t>
+          <t>cushion</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="B417" s="7" t="inlineStr">
         <is>
-          <t>Drawer</t>
+          <t>drawer</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>drill</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="B419" s="7" t="inlineStr">
         <is>
-          <t>Envelope</t>
+          <t>envelope</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
@@ -23573,7 +23573,7 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>Fence</t>
+          <t>fence</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
@@ -23628,7 +23628,7 @@
       </c>
       <c r="B421" s="7" t="inlineStr">
         <is>
-          <t>Flashlight</t>
+          <t>flashlight</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>Frame</t>
+          <t>frame</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="B423" s="7" t="inlineStr">
         <is>
-          <t>Garbage</t>
+          <t>garbage</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
@@ -23793,7 +23793,7 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="B425" s="7" t="inlineStr">
         <is>
-          <t>Kettle</t>
+          <t>kettle</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
@@ -23903,7 +23903,7 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>Ladder</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -23958,7 +23958,7 @@
       </c>
       <c r="B427" s="7" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>lantern</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
@@ -24013,7 +24013,7 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>lock</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="B429" s="7" t="inlineStr">
         <is>
-          <t>Mailbox</t>
+          <t>mailbox</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
@@ -24123,7 +24123,7 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>Needle</t>
+          <t>needle</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
@@ -24178,7 +24178,7 @@
       </c>
       <c r="B431" s="7" t="inlineStr">
         <is>
-          <t>Attic</t>
+          <t>attic</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>garage</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="B433" s="7" t="inlineStr">
         <is>
-          <t>Fireplace</t>
+          <t>fireplace</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>Faucet</t>
+          <t>faucet</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="B435" s="7" t="inlineStr">
         <is>
-          <t>Bathtub</t>
+          <t>bathtub</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
@@ -24453,7 +24453,7 @@
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>shower</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="B437" s="7" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="C437" s="6" t="inlineStr">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="B438" s="3" t="inlineStr">
         <is>
-          <t>Closet</t>
+          <t>closet</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
@@ -24618,7 +24618,7 @@
       </c>
       <c r="B439" s="7" t="inlineStr">
         <is>
-          <t>Mattress</t>
+          <t>mattress</t>
         </is>
       </c>
       <c r="C439" s="6" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>quilt</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="B441" s="7" t="inlineStr">
         <is>
-          <t>Vacuum</t>
+          <t>vacuum</t>
         </is>
       </c>
       <c r="C441" s="6" t="inlineStr">
@@ -24783,7 +24783,7 @@
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>Stove</t>
+          <t>stove</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -24838,7 +24838,7 @@
       </c>
       <c r="B443" s="7" t="inlineStr">
         <is>
-          <t>Oven</t>
+          <t>oven</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>Microwave</t>
+          <t>microwave</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="B445" s="7" t="inlineStr">
         <is>
-          <t>Freezer</t>
+          <t>freezer</t>
         </is>
       </c>
       <c r="C445" s="6" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>Toaster</t>
+          <t>toaster</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="B447" s="7" t="inlineStr">
         <is>
-          <t>Teapot</t>
+          <t>teapot</t>
         </is>
       </c>
       <c r="C447" s="6" t="inlineStr">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>Mug</t>
+          <t>mug</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
@@ -25168,7 +25168,7 @@
       </c>
       <c r="B449" s="7" t="inlineStr">
         <is>
-          <t>Chopsticks</t>
+          <t>chopsticks</t>
         </is>
       </c>
       <c r="C449" s="6" t="inlineStr">
@@ -25223,7 +25223,7 @@
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>Thermos</t>
+          <t>thermos</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="B451" s="7" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C451" s="6" t="inlineStr">
@@ -25333,7 +25333,7 @@
       </c>
       <c r="B452" s="3" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>headphone</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -25388,7 +25388,7 @@
       </c>
       <c r="B453" s="7" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>park</t>
         </is>
       </c>
       <c r="C453" s="6" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>Zoo</t>
+          <t>zoo</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="B455" s="7" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C455" s="6" t="inlineStr">
@@ -25553,7 +25553,7 @@
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>store</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -25608,7 +25608,7 @@
       </c>
       <c r="B457" s="7" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>library</t>
         </is>
       </c>
       <c r="C457" s="6" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="B459" s="7" t="inlineStr">
         <is>
-          <t>Station</t>
+          <t>station</t>
         </is>
       </c>
       <c r="C459" s="6" t="inlineStr">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>Airport</t>
+          <t>airport</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="B461" s="7" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C461" s="6" t="inlineStr">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>market</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -25938,7 +25938,7 @@
       </c>
       <c r="B463" s="7" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>shop</t>
         </is>
       </c>
       <c r="C463" s="6" t="inlineStr">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
@@ -26048,7 +26048,7 @@
       </c>
       <c r="B465" s="7" t="inlineStr">
         <is>
-          <t>Farm</t>
+          <t>farm</t>
         </is>
       </c>
       <c r="C465" s="6" t="inlineStr">
@@ -26103,7 +26103,7 @@
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>arch</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
@@ -26158,7 +26158,7 @@
       </c>
       <c r="B467" s="7" t="inlineStr">
         <is>
-          <t>Barn</t>
+          <t>barn</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>Castle</t>
+          <t>castle</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
@@ -26268,7 +26268,7 @@
       </c>
       <c r="B469" s="7" t="inlineStr">
         <is>
-          <t>Flagpole</t>
+          <t>flagpole</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
@@ -26323,7 +26323,7 @@
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>Fountain</t>
+          <t>fountain</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="B471" s="7" t="inlineStr">
         <is>
-          <t>Graveyard</t>
+          <t>graveyard</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="B472" s="3" t="inlineStr">
         <is>
-          <t>Museum</t>
+          <t>museum</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="B473" s="7" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>church</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>temple</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
@@ -26598,7 +26598,7 @@
       </c>
       <c r="B475" s="7" t="inlineStr">
         <is>
-          <t>Palace</t>
+          <t>palace</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
@@ -26653,7 +26653,7 @@
       </c>
       <c r="B476" s="3" t="inlineStr">
         <is>
-          <t>Theater</t>
+          <t>theater</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
@@ -26708,7 +26708,7 @@
       </c>
       <c r="B477" s="7" t="inlineStr">
         <is>
-          <t>Cinema</t>
+          <t>cinema</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="B478" s="3" t="inlineStr">
         <is>
-          <t>Stadium</t>
+          <t>stadium</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -26818,7 +26818,7 @@
       </c>
       <c r="B479" s="7" t="inlineStr">
         <is>
-          <t>Mall</t>
+          <t>mall</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
@@ -26873,7 +26873,7 @@
       </c>
       <c r="B480" s="3" t="inlineStr">
         <is>
-          <t>Supermarket</t>
+          <t>supermarket</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="B481" s="7" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>bakery</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
@@ -26983,7 +26983,7 @@
       </c>
       <c r="B482" s="3" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="B483" s="7" t="inlineStr">
         <is>
-          <t>Cafe</t>
+          <t>cafe</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>Factory</t>
+          <t>factory</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="B485" s="7" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
@@ -27203,7 +27203,7 @@
       </c>
       <c r="B486" s="3" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>village</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="B487" s="7" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="B488" s="3" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
@@ -27368,7 +27368,7 @@
       </c>
       <c r="B489" s="7" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
@@ -27423,7 +27423,7 @@
       </c>
       <c r="B490" s="3" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>subway</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -27478,7 +27478,7 @@
       </c>
       <c r="B491" s="7" t="inlineStr">
         <is>
-          <t>Airplane</t>
+          <t>airplane</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="B492" s="3" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>ship</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="B493" s="7" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="B494" s="3" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="B495" s="7" t="inlineStr">
         <is>
-          <t>Taxi</t>
+          <t>taxi</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B496" s="3" t="inlineStr">
         <is>
-          <t>Truck</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="B497" s="7" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
@@ -27863,7 +27863,7 @@
       </c>
       <c r="B498" s="3" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>road</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
@@ -27918,7 +27918,7 @@
       </c>
       <c r="B499" s="7" t="inlineStr">
         <is>
-          <t>Bike</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>street</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="B501" s="7" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>bridge</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
@@ -28083,7 +28083,7 @@
       </c>
       <c r="B502" s="3" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>trip</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
@@ -28138,7 +28138,7 @@
       </c>
       <c r="B503" s="7" t="inlineStr">
         <is>
-          <t>Avenue</t>
+          <t>avenue</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="B504" s="3" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -28248,7 +28248,7 @@
       </c>
       <c r="B505" s="7" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>highway</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="B506" s="3" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C506" s="2" t="inlineStr">
@@ -28358,7 +28358,7 @@
       </c>
       <c r="B507" s="7" t="inlineStr">
         <is>
-          <t>Scooter</t>
+          <t>scooter</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
@@ -28413,7 +28413,7 @@
       </c>
       <c r="B508" s="3" t="inlineStr">
         <is>
-          <t>Helicopter</t>
+          <t>helicopter</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="B509" s="7" t="inlineStr">
         <is>
-          <t>Ferry</t>
+          <t>ferry</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="B510" s="3" t="inlineStr">
         <is>
-          <t>Sailboat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
@@ -28578,7 +28578,7 @@
       </c>
       <c r="B511" s="7" t="inlineStr">
         <is>
-          <t>Tractor</t>
+          <t>tractor</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
@@ -28633,7 +28633,7 @@
       </c>
       <c r="B512" s="3" t="inlineStr">
         <is>
-          <t>Ambulance</t>
+          <t>ambulance</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -28688,7 +28688,7 @@
       </c>
       <c r="B513" s="7" t="inlineStr">
         <is>
-          <t>Wagon</t>
+          <t>wagon</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
@@ -28743,7 +28743,7 @@
       </c>
       <c r="B514" s="3" t="inlineStr">
         <is>
-          <t>Stroller</t>
+          <t>stroller</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
@@ -28798,7 +28798,7 @@
       </c>
       <c r="B515" s="7" t="inlineStr">
         <is>
-          <t>Harbor</t>
+          <t>harbor</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="B516" s="3" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="C516" s="2" t="inlineStr">
@@ -28908,7 +28908,7 @@
       </c>
       <c r="B517" s="7" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>moon</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
@@ -28963,7 +28963,7 @@
       </c>
       <c r="B518" s="3" t="inlineStr">
         <is>
-          <t>Star</t>
+          <t>star</t>
         </is>
       </c>
       <c r="C518" s="2" t="inlineStr">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="B519" s="7" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr">
@@ -29073,7 +29073,7 @@
       </c>
       <c r="B520" s="3" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C520" s="2" t="inlineStr">
@@ -29128,7 +29128,7 @@
       </c>
       <c r="B521" s="7" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="B522" s="3" t="inlineStr">
         <is>
-          <t>Snow</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="C522" s="2" t="inlineStr">
@@ -29238,7 +29238,7 @@
       </c>
       <c r="B523" s="7" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr">
@@ -29293,7 +29293,7 @@
       </c>
       <c r="B524" s="3" t="inlineStr">
         <is>
-          <t>Rainbow</t>
+          <t>rainbow</t>
         </is>
       </c>
       <c r="C524" s="2" t="inlineStr">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="B525" s="7" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr">
@@ -29403,7 +29403,7 @@
       </c>
       <c r="B526" s="3" t="inlineStr">
         <is>
-          <t>Flower</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="C526" s="2" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="B527" s="7" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>grass</t>
         </is>
       </c>
       <c r="C527" s="6" t="inlineStr">
@@ -29513,7 +29513,7 @@
       </c>
       <c r="B528" s="3" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>leaf</t>
         </is>
       </c>
       <c r="C528" s="2" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="B529" s="7" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="B530" s="3" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>river</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="B531" s="7" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>sea</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
@@ -29733,7 +29733,7 @@
       </c>
       <c r="B532" s="3" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C532" s="2" t="inlineStr">
@@ -29788,7 +29788,7 @@
       </c>
       <c r="B533" s="7" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="B534" s="3" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="B535" s="7" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="B536" s="3" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>ice</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="B537" s="7" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>forest</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="B538" s="3" t="inlineStr">
         <is>
-          <t>Ocean</t>
+          <t>ocean</t>
         </is>
       </c>
       <c r="C538" s="2" t="inlineStr">
@@ -30118,7 +30118,7 @@
       </c>
       <c r="B539" s="7" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>earth</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="B540" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="C540" s="2" t="inlineStr">
@@ -30228,7 +30228,7 @@
       </c>
       <c r="B541" s="7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
@@ -30283,7 +30283,7 @@
       </c>
       <c r="B542" s="3" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="C542" s="2" t="inlineStr">
@@ -30338,7 +30338,7 @@
       </c>
       <c r="B543" s="7" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="B544" s="3" t="inlineStr">
         <is>
-          <t>Pond</t>
+          <t>pond</t>
         </is>
       </c>
       <c r="C544" s="2" t="inlineStr">
@@ -30448,7 +30448,7 @@
       </c>
       <c r="B545" s="7" t="inlineStr">
         <is>
-          <t>Hill</t>
+          <t>hill</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
@@ -30503,7 +30503,7 @@
       </c>
       <c r="B546" s="3" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>field</t>
         </is>
       </c>
       <c r="C546" s="2" t="inlineStr">
@@ -30558,7 +30558,7 @@
       </c>
       <c r="B547" s="7" t="inlineStr">
         <is>
-          <t>Island</t>
+          <t>island</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
@@ -30613,7 +30613,7 @@
       </c>
       <c r="B548" s="3" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>air</t>
         </is>
       </c>
       <c r="C548" s="2" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="B549" s="7" t="inlineStr">
         <is>
-          <t>Smoke</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
@@ -30723,7 +30723,7 @@
       </c>
       <c r="B550" s="3" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C550" s="2" t="inlineStr">
@@ -30778,7 +30778,7 @@
       </c>
       <c r="B551" s="7" t="inlineStr">
         <is>
-          <t>Shadow</t>
+          <t>shadow</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
@@ -30833,7 +30833,7 @@
       </c>
       <c r="B552" s="3" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>sound</t>
         </is>
       </c>
       <c r="C552" s="2" t="inlineStr">
@@ -30888,7 +30888,7 @@
       </c>
       <c r="B553" s="7" t="inlineStr">
         <is>
-          <t>Jungle</t>
+          <t>jungle</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="B554" s="3" t="inlineStr">
         <is>
-          <t>Desert</t>
+          <t>desert</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="B555" s="7" t="inlineStr">
         <is>
-          <t>Bamboo</t>
+          <t>bamboo</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
@@ -31053,7 +31053,7 @@
       </c>
       <c r="B556" s="3" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="C556" s="2" t="inlineStr">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="B557" s="7" t="inlineStr">
         <is>
-          <t>Bush</t>
+          <t>bush</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
@@ -31163,7 +31163,7 @@
       </c>
       <c r="B558" s="3" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>cactus</t>
         </is>
       </c>
       <c r="C558" s="2" t="inlineStr">
@@ -31218,7 +31218,7 @@
       </c>
       <c r="B559" s="7" t="inlineStr">
         <is>
-          <t>Canyon</t>
+          <t>canyon</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
@@ -31273,7 +31273,7 @@
       </c>
       <c r="B560" s="3" t="inlineStr">
         <is>
-          <t>Cave</t>
+          <t>cave</t>
         </is>
       </c>
       <c r="C560" s="2" t="inlineStr">
@@ -31328,7 +31328,7 @@
       </c>
       <c r="B561" s="7" t="inlineStr">
         <is>
-          <t>Cliff</t>
+          <t>cliff</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
@@ -31383,7 +31383,7 @@
       </c>
       <c r="B562" s="3" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
@@ -31438,7 +31438,7 @@
       </c>
       <c r="B563" s="7" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
@@ -31493,7 +31493,7 @@
       </c>
       <c r="B564" s="3" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>jewel</t>
         </is>
       </c>
       <c r="C564" s="2" t="inlineStr">
@@ -31548,7 +31548,7 @@
       </c>
       <c r="B565" s="7" t="inlineStr">
         <is>
-          <t>Lawn</t>
+          <t>lawn</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
@@ -31603,7 +31603,7 @@
       </c>
       <c r="B566" s="3" t="inlineStr">
         <is>
-          <t>Typhoon</t>
+          <t>typhoon</t>
         </is>
       </c>
       <c r="C566" s="2" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="B567" s="7" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>tornado</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
@@ -31713,7 +31713,7 @@
       </c>
       <c r="B568" s="3" t="inlineStr">
         <is>
-          <t>Hail</t>
+          <t>hail</t>
         </is>
       </c>
       <c r="C568" s="2" t="inlineStr">
@@ -31768,7 +31768,7 @@
       </c>
       <c r="B569" s="7" t="inlineStr">
         <is>
-          <t>Puddle</t>
+          <t>puddle</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
@@ -31823,7 +31823,7 @@
       </c>
       <c r="B570" s="3" t="inlineStr">
         <is>
-          <t>Icicle</t>
+          <t>icicle</t>
         </is>
       </c>
       <c r="C570" s="2" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="B571" s="7" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>sunrise</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="B572" s="3" t="inlineStr">
         <is>
-          <t>Sunset</t>
+          <t>sunset</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -31988,7 +31988,7 @@
       </c>
       <c r="B573" s="7" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>dawn</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
@@ -32043,7 +32043,7 @@
       </c>
       <c r="B574" s="3" t="inlineStr">
         <is>
-          <t>Dusk</t>
+          <t>dusk</t>
         </is>
       </c>
       <c r="C574" s="2" t="inlineStr">
@@ -32098,7 +32098,7 @@
       </c>
       <c r="B575" s="7" t="inlineStr">
         <is>
-          <t>Shade</t>
+          <t>shade</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="B576" s="3" t="inlineStr">
         <is>
-          <t>Waterfall</t>
+          <t>waterfall</t>
         </is>
       </c>
       <c r="C576" s="2" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B577" s="7" t="inlineStr">
         <is>
-          <t>Pebble</t>
+          <t>pebble</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
@@ -32263,7 +32263,7 @@
       </c>
       <c r="B578" s="3" t="inlineStr">
         <is>
-          <t>Trunk</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="C578" s="2" t="inlineStr">
@@ -32318,7 +32318,7 @@
       </c>
       <c r="B579" s="7" t="inlineStr">
         <is>
-          <t>Twig</t>
+          <t>twig</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
@@ -32373,7 +32373,7 @@
       </c>
       <c r="B580" s="3" t="inlineStr">
         <is>
-          <t>Mist</t>
+          <t>mist</t>
         </is>
       </c>
       <c r="C580" s="2" t="inlineStr">
@@ -32428,7 +32428,7 @@
       </c>
       <c r="B581" s="7" t="inlineStr">
         <is>
-          <t>Blossom</t>
+          <t>blossom</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
@@ -32483,7 +32483,7 @@
       </c>
       <c r="B582" s="3" t="inlineStr">
         <is>
-          <t>Petal</t>
+          <t>petal</t>
         </is>
       </c>
       <c r="C582" s="2" t="inlineStr">
@@ -32538,7 +32538,7 @@
       </c>
       <c r="B583" s="7" t="inlineStr">
         <is>
-          <t>Vine</t>
+          <t>vine</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
@@ -32593,7 +32593,7 @@
       </c>
       <c r="B584" s="3" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C584" s="2" t="inlineStr">
@@ -32648,7 +32648,7 @@
       </c>
       <c r="B585" s="7" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="B586" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="C586" s="2" t="inlineStr">
@@ -32758,7 +32758,7 @@
       </c>
       <c r="B587" s="7" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="B588" s="3" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C588" s="2" t="inlineStr">
@@ -32868,7 +32868,7 @@
       </c>
       <c r="B589" s="7" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
@@ -32923,7 +32923,7 @@
       </c>
       <c r="B590" s="3" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C590" s="2" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="B591" s="7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
@@ -33033,7 +33033,7 @@
       </c>
       <c r="B592" s="3" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C592" s="2" t="inlineStr">
@@ -33088,7 +33088,7 @@
       </c>
       <c r="B593" s="7" t="inlineStr">
         <is>
-          <t>Tomorrow</t>
+          <t>tomorrow</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
@@ -33143,7 +33143,7 @@
       </c>
       <c r="B594" s="3" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="C594" s="2" t="inlineStr">
@@ -33198,7 +33198,7 @@
       </c>
       <c r="B595" s="7" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>week</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
@@ -33253,7 +33253,7 @@
       </c>
       <c r="B596" s="3" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C596" s="2" t="inlineStr">
@@ -33308,7 +33308,7 @@
       </c>
       <c r="B597" s="7" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="B598" s="3" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C598" s="2" t="inlineStr">
@@ -33418,7 +33418,7 @@
       </c>
       <c r="B599" s="7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="B600" s="3" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C600" s="2" t="inlineStr">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="B601" s="7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
@@ -33583,7 +33583,7 @@
       </c>
       <c r="B602" s="3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C602" s="2" t="inlineStr">
@@ -33638,7 +33638,7 @@
       </c>
       <c r="B603" s="7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
@@ -33693,7 +33693,7 @@
       </c>
       <c r="B604" s="3" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C604" s="2" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="B605" s="7" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
@@ -33803,7 +33803,7 @@
       </c>
       <c r="B606" s="3" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C606" s="2" t="inlineStr">
@@ -33858,7 +33858,7 @@
       </c>
       <c r="B607" s="7" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
@@ -33913,7 +33913,7 @@
       </c>
       <c r="B608" s="3" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C608" s="2" t="inlineStr">
@@ -33968,7 +33968,7 @@
       </c>
       <c r="B609" s="7" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="B610" s="3" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
@@ -34078,7 +34078,7 @@
       </c>
       <c r="B611" s="7" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
@@ -34133,7 +34133,7 @@
       </c>
       <c r="B612" s="3" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -34188,7 +34188,7 @@
       </c>
       <c r="B613" s="7" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="B614" s="3" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C614" s="2" t="inlineStr">
@@ -34298,7 +34298,7 @@
       </c>
       <c r="B615" s="7" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
@@ -34353,7 +34353,7 @@
       </c>
       <c r="B616" s="3" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C616" s="2" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="B617" s="7" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>holiday</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
@@ -34463,7 +34463,7 @@
       </c>
       <c r="B618" s="3" t="inlineStr">
         <is>
-          <t>Vacation</t>
+          <t>vacation</t>
         </is>
       </c>
       <c r="C618" s="2" t="inlineStr">
@@ -34518,7 +34518,7 @@
       </c>
       <c r="B619" s="7" t="inlineStr">
         <is>
-          <t>Century</t>
+          <t>century</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
@@ -34573,7 +34573,7 @@
       </c>
       <c r="B620" s="3" t="inlineStr">
         <is>
-          <t>Decade</t>
+          <t>decade</t>
         </is>
       </c>
       <c r="C620" s="2" t="inlineStr">
@@ -34628,7 +34628,7 @@
       </c>
       <c r="B621" s="7" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
@@ -34683,7 +34683,7 @@
       </c>
       <c r="B622" s="3" t="inlineStr">
         <is>
-          <t>Weekday</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C622" s="2" t="inlineStr">
@@ -34738,7 +34738,7 @@
       </c>
       <c r="B623" s="7" t="inlineStr">
         <is>
-          <t>Birthday</t>
+          <t>birthday</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
@@ -34793,7 +34793,7 @@
       </c>
       <c r="B624" s="3" t="inlineStr">
         <is>
-          <t>Anniversary</t>
+          <t>anniversary</t>
         </is>
       </c>
       <c r="C624" s="2" t="inlineStr">
@@ -34848,7 +34848,7 @@
       </c>
       <c r="B625" s="7" t="inlineStr">
         <is>
-          <t>Midnight</t>
+          <t>midnight</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
@@ -34903,7 +34903,7 @@
       </c>
       <c r="B626" s="3" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>noon</t>
         </is>
       </c>
       <c r="C626" s="2" t="inlineStr">
@@ -34958,7 +34958,7 @@
       </c>
       <c r="B627" s="7" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
@@ -35013,7 +35013,7 @@
       </c>
       <c r="B628" s="3" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>minute</t>
         </is>
       </c>
       <c r="C628" s="2" t="inlineStr">
@@ -35068,7 +35068,7 @@
       </c>
       <c r="B629" s="7" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
@@ -35123,7 +35123,7 @@
       </c>
       <c r="B630" s="3" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C630" s="2" t="inlineStr">
@@ -35178,7 +35178,7 @@
       </c>
       <c r="B631" s="7" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
@@ -35233,7 +35233,7 @@
       </c>
       <c r="B632" s="3" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C632" s="2" t="inlineStr">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="B633" s="7" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
@@ -35343,7 +35343,7 @@
       </c>
       <c r="B634" s="3" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C634" s="2" t="inlineStr">
@@ -35398,7 +35398,7 @@
       </c>
       <c r="B635" s="7" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="B636" s="3" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C636" s="2" t="inlineStr">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="B637" s="7" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="B638" s="3" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>two</t>
         </is>
       </c>
       <c r="C638" s="2" t="inlineStr">
@@ -35618,7 +35618,7 @@
       </c>
       <c r="B639" s="7" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="B640" s="3" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>four</t>
         </is>
       </c>
       <c r="C640" s="2" t="inlineStr">
@@ -35728,7 +35728,7 @@
       </c>
       <c r="B641" s="7" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>five</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
@@ -35783,7 +35783,7 @@
       </c>
       <c r="B642" s="3" t="inlineStr">
         <is>
-          <t>Ten</t>
+          <t>ten</t>
         </is>
       </c>
       <c r="C642" s="2" t="inlineStr">
@@ -35838,7 +35838,7 @@
       </c>
       <c r="B643" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C643" s="6" t="inlineStr">
@@ -35893,7 +35893,7 @@
       </c>
       <c r="B644" s="3" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -35948,7 +35948,7 @@
       </c>
       <c r="B645" s="7" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C645" s="6" t="inlineStr">
@@ -36003,7 +36003,7 @@
       </c>
       <c r="B646" s="3" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>six</t>
         </is>
       </c>
       <c r="C646" s="2" t="inlineStr">
@@ -36058,7 +36058,7 @@
       </c>
       <c r="B647" s="7" t="inlineStr">
         <is>
-          <t>Seven</t>
+          <t>seven</t>
         </is>
       </c>
       <c r="C647" s="6" t="inlineStr">
@@ -36113,7 +36113,7 @@
       </c>
       <c r="B648" s="3" t="inlineStr">
         <is>
-          <t>Eight</t>
+          <t>eight</t>
         </is>
       </c>
       <c r="C648" s="2" t="inlineStr">
@@ -36168,7 +36168,7 @@
       </c>
       <c r="B649" s="7" t="inlineStr">
         <is>
-          <t>Nine</t>
+          <t>nine</t>
         </is>
       </c>
       <c r="C649" s="6" t="inlineStr">
@@ -36223,7 +36223,7 @@
       </c>
       <c r="B650" s="3" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>navy</t>
         </is>
       </c>
       <c r="C650" s="2" t="inlineStr">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="B651" s="7" t="inlineStr">
         <is>
-          <t>Beige</t>
+          <t>beige</t>
         </is>
       </c>
       <c r="C651" s="6" t="inlineStr">
@@ -36333,7 +36333,7 @@
       </c>
       <c r="B652" s="3" t="inlineStr">
         <is>
-          <t>Dozen</t>
+          <t>dozen</t>
         </is>
       </c>
       <c r="C652" s="2" t="inlineStr">
@@ -36388,7 +36388,7 @@
       </c>
       <c r="B653" s="7" t="inlineStr">
         <is>
-          <t>Half</t>
+          <t>half</t>
         </is>
       </c>
       <c r="C653" s="6" t="inlineStr">
@@ -36443,7 +36443,7 @@
       </c>
       <c r="B654" s="3" t="inlineStr">
         <is>
-          <t>Quarter</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="C654" s="2" t="inlineStr">
@@ -36498,7 +36498,7 @@
       </c>
       <c r="B655" s="7" t="inlineStr">
         <is>
-          <t>Triple</t>
+          <t>triple</t>
         </is>
       </c>
       <c r="C655" s="6" t="inlineStr">
@@ -36553,7 +36553,7 @@
       </c>
       <c r="B656" s="3" t="inlineStr">
         <is>
-          <t>Million</t>
+          <t>million</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="B657" s="7" t="inlineStr">
         <is>
-          <t>Billion</t>
+          <t>billion</t>
         </is>
       </c>
       <c r="C657" s="6" t="inlineStr">
@@ -36663,7 +36663,7 @@
       </c>
       <c r="B658" s="3" t="inlineStr">
         <is>
-          <t>Pair</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
@@ -36718,7 +36718,7 @@
       </c>
       <c r="B659" s="7" t="inlineStr">
         <is>
-          <t>Dot</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="C659" s="6" t="inlineStr">
@@ -36773,7 +36773,7 @@
       </c>
       <c r="B660" s="3" t="inlineStr">
         <is>
-          <t>Big</t>
+          <t>big</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
@@ -36828,7 +36828,7 @@
       </c>
       <c r="B661" s="7" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C661" s="6" t="inlineStr">
@@ -36883,7 +36883,7 @@
       </c>
       <c r="B662" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="B663" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C663" s="6" t="inlineStr">
@@ -36993,7 +36993,7 @@
       </c>
       <c r="B664" s="3" t="inlineStr">
         <is>
-          <t>Fast</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
@@ -37048,7 +37048,7 @@
       </c>
       <c r="B665" s="7" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C665" s="6" t="inlineStr">
@@ -37103,7 +37103,7 @@
       </c>
       <c r="B666" s="3" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
@@ -37158,7 +37158,7 @@
       </c>
       <c r="B667" s="7" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>cold</t>
         </is>
       </c>
       <c r="C667" s="6" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="B668" s="3" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="B669" s="7" t="inlineStr">
         <is>
-          <t>Cool</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C669" s="6" t="inlineStr">
@@ -37323,7 +37323,7 @@
       </c>
       <c r="B670" s="3" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
@@ -37378,7 +37378,7 @@
       </c>
       <c r="B671" s="7" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C671" s="6" t="inlineStr">
@@ -37433,7 +37433,7 @@
       </c>
       <c r="B672" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
@@ -37488,7 +37488,7 @@
       </c>
       <c r="B673" s="7" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C673" s="6" t="inlineStr">
@@ -37543,7 +37543,7 @@
       </c>
       <c r="B674" s="3" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>young</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
@@ -37598,7 +37598,7 @@
       </c>
       <c r="B675" s="7" t="inlineStr">
         <is>
-          <t>Cute</t>
+          <t>cute</t>
         </is>
       </c>
       <c r="C675" s="6" t="inlineStr">
@@ -37653,7 +37653,7 @@
       </c>
       <c r="B676" s="3" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
@@ -37708,7 +37708,7 @@
       </c>
       <c r="B677" s="7" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C677" s="6" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="B678" s="3" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
@@ -37818,7 +37818,7 @@
       </c>
       <c r="B679" s="7" t="inlineStr">
         <is>
-          <t>Shallow</t>
+          <t>shallow</t>
         </is>
       </c>
       <c r="C679" s="6" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="B680" s="3" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
@@ -37928,7 +37928,7 @@
       </c>
       <c r="B681" s="7" t="inlineStr">
         <is>
-          <t>Curved</t>
+          <t>curved</t>
         </is>
       </c>
       <c r="C681" s="6" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="B682" s="3" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
@@ -38038,7 +38038,7 @@
       </c>
       <c r="B683" s="7" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C683" s="6" t="inlineStr">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="B684" s="3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -38148,7 +38148,7 @@
       </c>
       <c r="B685" s="7" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C685" s="6" t="inlineStr">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="B686" s="3" t="inlineStr">
         <is>
-          <t>Sticky</t>
+          <t>sticky</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="B687" s="7" t="inlineStr">
         <is>
-          <t>Fluffy</t>
+          <t>fluffy</t>
         </is>
       </c>
       <c r="C687" s="6" t="inlineStr">
@@ -38313,7 +38313,7 @@
       </c>
       <c r="B688" s="3" t="inlineStr">
         <is>
-          <t>Crispy</t>
+          <t>crispy</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -38368,7 +38368,7 @@
       </c>
       <c r="B689" s="7" t="inlineStr">
         <is>
-          <t>Salty</t>
+          <t>salty</t>
         </is>
       </c>
       <c r="C689" s="6" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="B690" s="3" t="inlineStr">
         <is>
-          <t>Spicy</t>
+          <t>spicy</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="B691" s="7" t="inlineStr">
         <is>
-          <t>Bitter</t>
+          <t>bitter</t>
         </is>
       </c>
       <c r="C691" s="6" t="inlineStr">
@@ -38533,7 +38533,7 @@
       </c>
       <c r="B692" s="3" t="inlineStr">
         <is>
-          <t>Juicy</t>
+          <t>juicy</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
@@ -38588,7 +38588,7 @@
       </c>
       <c r="B693" s="7" t="inlineStr">
         <is>
-          <t>Tidy</t>
+          <t>tidy</t>
         </is>
       </c>
       <c r="C693" s="6" t="inlineStr">
@@ -38643,7 +38643,7 @@
       </c>
       <c r="B694" s="3" t="inlineStr">
         <is>
-          <t>Messy</t>
+          <t>messy</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
@@ -38698,7 +38698,7 @@
       </c>
       <c r="B695" s="7" t="inlineStr">
         <is>
-          <t>Noisy</t>
+          <t>noisy</t>
         </is>
       </c>
       <c r="C695" s="6" t="inlineStr">
@@ -38753,7 +38753,7 @@
       </c>
       <c r="B696" s="3" t="inlineStr">
         <is>
-          <t>Silly</t>
+          <t>silly</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
@@ -38808,7 +38808,7 @@
       </c>
       <c r="B697" s="7" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C697" s="6" t="inlineStr">
@@ -38863,7 +38863,7 @@
       </c>
       <c r="B698" s="3" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="B699" s="7" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C699" s="6" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="B700" s="3" t="inlineStr">
         <is>
-          <t>Tired</t>
+          <t>tired</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -39028,7 +39028,7 @@
       </c>
       <c r="B701" s="7" t="inlineStr">
         <is>
-          <t>Hungry</t>
+          <t>hungry</t>
         </is>
       </c>
       <c r="C701" s="6" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="B702" s="3" t="inlineStr">
         <is>
-          <t>Thirsty</t>
+          <t>thirsty</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
@@ -39138,7 +39138,7 @@
       </c>
       <c r="B703" s="7" t="inlineStr">
         <is>
-          <t>Sleepy</t>
+          <t>sleepy</t>
         </is>
       </c>
       <c r="C703" s="6" t="inlineStr">
@@ -39193,7 +39193,7 @@
       </c>
       <c r="B704" s="3" t="inlineStr">
         <is>
-          <t>Sick</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
@@ -39248,7 +39248,7 @@
       </c>
       <c r="B705" s="7" t="inlineStr">
         <is>
-          <t>Scared</t>
+          <t>scared</t>
         </is>
       </c>
       <c r="C705" s="6" t="inlineStr">
@@ -39303,7 +39303,7 @@
       </c>
       <c r="B706" s="3" t="inlineStr">
         <is>
-          <t>Excited</t>
+          <t>excited</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
@@ -39358,7 +39358,7 @@
       </c>
       <c r="B707" s="7" t="inlineStr">
         <is>
-          <t>Surprised</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="C707" s="6" t="inlineStr">
@@ -39413,7 +39413,7 @@
       </c>
       <c r="B708" s="3" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>love</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
@@ -39468,7 +39468,7 @@
       </c>
       <c r="B709" s="7" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C709" s="6" t="inlineStr">
@@ -39523,7 +39523,7 @@
       </c>
       <c r="B710" s="3" t="inlineStr">
         <is>
-          <t>Sorry</t>
+          <t>sorry</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -39578,7 +39578,7 @@
       </c>
       <c r="B711" s="7" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>fine</t>
         </is>
       </c>
       <c r="C711" s="6" t="inlineStr">
@@ -39633,7 +39633,7 @@
       </c>
       <c r="B712" s="3" t="inlineStr">
         <is>
-          <t>Hurt</t>
+          <t>hurt</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
@@ -39688,7 +39688,7 @@
       </c>
       <c r="B713" s="7" t="inlineStr">
         <is>
-          <t>Well</t>
+          <t>well</t>
         </is>
       </c>
       <c r="C713" s="6" t="inlineStr">
@@ -39743,7 +39743,7 @@
       </c>
       <c r="B714" s="3" t="inlineStr">
         <is>
-          <t>Smart</t>
+          <t>smart</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
@@ -39798,7 +39798,7 @@
       </c>
       <c r="B715" s="7" t="inlineStr">
         <is>
-          <t>Funny</t>
+          <t>funny</t>
         </is>
       </c>
       <c r="C715" s="6" t="inlineStr">
@@ -39853,7 +39853,7 @@
       </c>
       <c r="B716" s="3" t="inlineStr">
         <is>
-          <t>Friendly</t>
+          <t>friendly</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
@@ -39908,7 +39908,7 @@
       </c>
       <c r="B717" s="7" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C717" s="6" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="B718" s="3" t="inlineStr">
         <is>
-          <t>Merry</t>
+          <t>merry</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
@@ -40018,7 +40018,7 @@
       </c>
       <c r="B719" s="7" t="inlineStr">
         <is>
-          <t>Bold</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="C719" s="6" t="inlineStr">
@@ -40073,7 +40073,7 @@
       </c>
       <c r="B720" s="3" t="inlineStr">
         <is>
-          <t>Safe</t>
+          <t>safe</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
@@ -40128,7 +40128,7 @@
       </c>
       <c r="B721" s="7" t="inlineStr">
         <is>
-          <t>Sure</t>
+          <t>sure</t>
         </is>
       </c>
       <c r="C721" s="6" t="inlineStr">
@@ -40183,7 +40183,7 @@
       </c>
       <c r="B722" s="3" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
@@ -40238,7 +40238,7 @@
       </c>
       <c r="B723" s="7" t="inlineStr">
         <is>
-          <t>Jump</t>
+          <t>jump</t>
         </is>
       </c>
       <c r="C723" s="6" t="inlineStr">
@@ -40293,7 +40293,7 @@
       </c>
       <c r="B724" s="3" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="B725" s="7" t="inlineStr">
         <is>
-          <t>Eat</t>
+          <t>eat</t>
         </is>
       </c>
       <c r="C725" s="6" t="inlineStr">
@@ -40403,7 +40403,7 @@
       </c>
       <c r="B726" s="3" t="inlineStr">
         <is>
-          <t>Drink</t>
+          <t>drink</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
@@ -40458,7 +40458,7 @@
       </c>
       <c r="B727" s="7" t="inlineStr">
         <is>
-          <t>Sleep</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C727" s="6" t="inlineStr">
@@ -40513,7 +40513,7 @@
       </c>
       <c r="B728" s="3" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>read</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
@@ -40568,7 +40568,7 @@
       </c>
       <c r="B729" s="7" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>write</t>
         </is>
       </c>
       <c r="C729" s="6" t="inlineStr">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="B730" s="3" t="inlineStr">
         <is>
-          <t>Sing</t>
+          <t>sing</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
@@ -40678,7 +40678,7 @@
       </c>
       <c r="B731" s="7" t="inlineStr">
         <is>
-          <t>Dance</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C731" s="6" t="inlineStr">
@@ -40733,7 +40733,7 @@
       </c>
       <c r="B732" s="3" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>play</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
@@ -40788,7 +40788,7 @@
       </c>
       <c r="B733" s="7" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>study</t>
         </is>
       </c>
       <c r="C733" s="6" t="inlineStr">
@@ -40843,7 +40843,7 @@
       </c>
       <c r="B734" s="3" t="inlineStr">
         <is>
-          <t>Swim</t>
+          <t>swim</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
@@ -40898,7 +40898,7 @@
       </c>
       <c r="B735" s="7" t="inlineStr">
         <is>
-          <t>Fly</t>
+          <t>fly</t>
         </is>
       </c>
       <c r="C735" s="6" t="inlineStr">
@@ -40953,7 +40953,7 @@
       </c>
       <c r="B736" s="3" t="inlineStr">
         <is>
-          <t>Clean</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
@@ -41008,7 +41008,7 @@
       </c>
       <c r="B737" s="7" t="inlineStr">
         <is>
-          <t>Wash</t>
+          <t>wash</t>
         </is>
       </c>
       <c r="C737" s="6" t="inlineStr">
@@ -41063,7 +41063,7 @@
       </c>
       <c r="B738" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="B739" s="7" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>close</t>
         </is>
       </c>
       <c r="C739" s="6" t="inlineStr">
@@ -41173,7 +41173,7 @@
       </c>
       <c r="B740" s="3" t="inlineStr">
         <is>
-          <t>Push</t>
+          <t>push</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
@@ -41228,7 +41228,7 @@
       </c>
       <c r="B741" s="7" t="inlineStr">
         <is>
-          <t>Pull</t>
+          <t>pull</t>
         </is>
       </c>
       <c r="C741" s="6" t="inlineStr">
@@ -41283,7 +41283,7 @@
       </c>
       <c r="B742" s="3" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
@@ -41338,7 +41338,7 @@
       </c>
       <c r="B743" s="7" t="inlineStr">
         <is>
-          <t>Pay</t>
+          <t>pay</t>
         </is>
       </c>
       <c r="C743" s="6" t="inlineStr">
@@ -41393,7 +41393,7 @@
       </c>
       <c r="B744" s="3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="B745" s="7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>sell</t>
         </is>
       </c>
       <c r="C745" s="6" t="inlineStr">
@@ -41503,7 +41503,7 @@
       </c>
       <c r="B746" s="3" t="inlineStr">
         <is>
-          <t>Sit</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
@@ -41558,7 +41558,7 @@
       </c>
       <c r="B747" s="7" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="C747" s="6" t="inlineStr">
@@ -41613,7 +41613,7 @@
       </c>
       <c r="B748" s="3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
@@ -41668,7 +41668,7 @@
       </c>
       <c r="B749" s="7" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>comb</t>
         </is>
       </c>
       <c r="C749" s="6" t="inlineStr">
@@ -41723,7 +41723,7 @@
       </c>
       <c r="B750" s="3" t="inlineStr">
         <is>
-          <t>Bake</t>
+          <t>bake</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
@@ -41778,7 +41778,7 @@
       </c>
       <c r="B751" s="7" t="inlineStr">
         <is>
-          <t>Taste</t>
+          <t>taste</t>
         </is>
       </c>
       <c r="C751" s="6" t="inlineStr">
@@ -41833,7 +41833,7 @@
       </c>
       <c r="B752" s="3" t="inlineStr">
         <is>
-          <t>Smell</t>
+          <t>smell</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
@@ -41888,7 +41888,7 @@
       </c>
       <c r="B753" s="7" t="inlineStr">
         <is>
-          <t>Hear</t>
+          <t>hear</t>
         </is>
       </c>
       <c r="C753" s="6" t="inlineStr">
@@ -41943,7 +41943,7 @@
       </c>
       <c r="B754" s="3" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>listen</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
@@ -41998,7 +41998,7 @@
       </c>
       <c r="B755" s="7" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="C755" s="6" t="inlineStr">
@@ -42053,7 +42053,7 @@
       </c>
       <c r="B756" s="3" t="inlineStr">
         <is>
-          <t>Clap</t>
+          <t>clap</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
@@ -42108,7 +42108,7 @@
       </c>
       <c r="B757" s="7" t="inlineStr">
         <is>
-          <t>Hug</t>
+          <t>hug</t>
         </is>
       </c>
       <c r="C757" s="6" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="B758" s="3" t="inlineStr">
         <is>
-          <t>Ring</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
@@ -42218,7 +42218,7 @@
       </c>
       <c r="B759" s="7" t="inlineStr">
         <is>
-          <t>Blow</t>
+          <t>blow</t>
         </is>
       </c>
       <c r="C759" s="6" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="B760" s="3" t="inlineStr">
         <is>
-          <t>Bite</t>
+          <t>bite</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
@@ -42328,7 +42328,7 @@
       </c>
       <c r="B761" s="7" t="inlineStr">
         <is>
-          <t>Chew</t>
+          <t>chew</t>
         </is>
       </c>
       <c r="C761" s="6" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="B762" s="3" t="inlineStr">
         <is>
-          <t>Lick</t>
+          <t>lick</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
@@ -42438,7 +42438,7 @@
       </c>
       <c r="B763" s="7" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>drive</t>
         </is>
       </c>
       <c r="C763" s="6" t="inlineStr">
@@ -42493,7 +42493,7 @@
       </c>
       <c r="B764" s="3" t="inlineStr">
         <is>
-          <t>Slip</t>
+          <t>slip</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -42548,7 +42548,7 @@
       </c>
       <c r="B765" s="7" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="C765" s="6" t="inlineStr">
@@ -42603,7 +42603,7 @@
       </c>
       <c r="B766" s="3" t="inlineStr">
         <is>
-          <t>Hop</t>
+          <t>hop</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
@@ -42658,7 +42658,7 @@
       </c>
       <c r="B767" s="7" t="inlineStr">
         <is>
-          <t>Kneel</t>
+          <t>kneel</t>
         </is>
       </c>
       <c r="C767" s="6" t="inlineStr">
@@ -42713,7 +42713,7 @@
       </c>
       <c r="B768" s="3" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>pat</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
@@ -42768,7 +42768,7 @@
       </c>
       <c r="B769" s="7" t="inlineStr">
         <is>
-          <t>Rub</t>
+          <t>rub</t>
         </is>
       </c>
       <c r="C769" s="6" t="inlineStr">
@@ -42823,7 +42823,7 @@
       </c>
       <c r="B770" s="3" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
@@ -42878,7 +42878,7 @@
       </c>
       <c r="B771" s="7" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>game</t>
         </is>
       </c>
       <c r="C771" s="6" t="inlineStr">
@@ -42933,7 +42933,7 @@
       </c>
       <c r="B772" s="3" t="inlineStr">
         <is>
-          <t>Song</t>
+          <t>song</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
@@ -42988,7 +42988,7 @@
       </c>
       <c r="B773" s="7" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C773" s="6" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B774" s="3" t="inlineStr">
         <is>
-          <t>Show</t>
+          <t>show</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
@@ -43098,7 +43098,7 @@
       </c>
       <c r="B775" s="7" t="inlineStr">
         <is>
-          <t>Violin</t>
+          <t>violin</t>
         </is>
       </c>
       <c r="C775" s="6" t="inlineStr">
@@ -43153,7 +43153,7 @@
       </c>
       <c r="B776" s="3" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>flute</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
@@ -43208,7 +43208,7 @@
       </c>
       <c r="B777" s="7" t="inlineStr">
         <is>
-          <t>Trumpet</t>
+          <t>trumpet</t>
         </is>
       </c>
       <c r="C777" s="6" t="inlineStr">
@@ -43263,7 +43263,7 @@
       </c>
       <c r="B778" s="3" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>sport</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="B779" s="7" t="inlineStr">
         <is>
-          <t>Soccer</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C779" s="6" t="inlineStr">
@@ -43373,7 +43373,7 @@
       </c>
       <c r="B780" s="3" t="inlineStr">
         <is>
-          <t>Baseball</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
@@ -43428,7 +43428,7 @@
       </c>
       <c r="B781" s="7" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C781" s="6" t="inlineStr">
@@ -43483,7 +43483,7 @@
       </c>
       <c r="B782" s="3" t="inlineStr">
         <is>
-          <t>Volleyball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
@@ -43538,7 +43538,7 @@
       </c>
       <c r="B783" s="7" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C783" s="6" t="inlineStr">
@@ -43593,7 +43593,7 @@
       </c>
       <c r="B784" s="3" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>golf</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
@@ -43648,7 +43648,7 @@
       </c>
       <c r="B785" s="7" t="inlineStr">
         <is>
-          <t>Ski</t>
+          <t>ski</t>
         </is>
       </c>
       <c r="C785" s="6" t="inlineStr">
@@ -43703,7 +43703,7 @@
       </c>
       <c r="B786" s="3" t="inlineStr">
         <is>
-          <t>Skate</t>
+          <t>skate</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="B787" s="7" t="inlineStr">
         <is>
-          <t>Disk</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="C787" s="6" t="inlineStr">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="B788" s="3" t="inlineStr">
         <is>
-          <t>Firework</t>
+          <t>firework</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
@@ -43868,7 +43868,7 @@
       </c>
       <c r="B789" s="7" t="inlineStr">
         <is>
-          <t>Kite</t>
+          <t>kite</t>
         </is>
       </c>
       <c r="C789" s="6" t="inlineStr">
@@ -43923,7 +43923,7 @@
       </c>
       <c r="B790" s="3" t="inlineStr">
         <is>
-          <t>Badminton</t>
+          <t>badminton</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
@@ -43978,7 +43978,7 @@
       </c>
       <c r="B791" s="7" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C791" s="6" t="inlineStr">
@@ -44033,7 +44033,7 @@
       </c>
       <c r="B792" s="3" t="inlineStr">
         <is>
-          <t>Skating</t>
+          <t>skating</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
@@ -44088,7 +44088,7 @@
       </c>
       <c r="B793" s="7" t="inlineStr">
         <is>
-          <t>Skiing</t>
+          <t>skiing</t>
         </is>
       </c>
       <c r="C793" s="6" t="inlineStr">
@@ -44143,7 +44143,7 @@
       </c>
       <c r="B794" s="3" t="inlineStr">
         <is>
-          <t>Boxing</t>
+          <t>boxing</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
@@ -44198,7 +44198,7 @@
       </c>
       <c r="B795" s="7" t="inlineStr">
         <is>
-          <t>Taekwondo</t>
+          <t>taekwondo</t>
         </is>
       </c>
       <c r="C795" s="6" t="inlineStr">
@@ -44253,7 +44253,7 @@
       </c>
       <c r="B796" s="3" t="inlineStr">
         <is>
-          <t>Hiking</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
@@ -44308,7 +44308,7 @@
       </c>
       <c r="B797" s="7" t="inlineStr">
         <is>
-          <t>Camping</t>
+          <t>camping</t>
         </is>
       </c>
       <c r="C797" s="6" t="inlineStr">
@@ -44363,7 +44363,7 @@
       </c>
       <c r="B798" s="3" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>fishing</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
@@ -44418,7 +44418,7 @@
       </c>
       <c r="B799" s="7" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>drawing</t>
         </is>
       </c>
       <c r="C799" s="6" t="inlineStr">
@@ -44473,7 +44473,7 @@
       </c>
       <c r="B800" s="3" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
@@ -44528,7 +44528,7 @@
       </c>
       <c r="B801" s="7" t="inlineStr">
         <is>
-          <t>Puzzle</t>
+          <t>puzzle</t>
         </is>
       </c>
       <c r="C801" s="6" t="inlineStr">

--- a/word/elementary_words_ko_zh.xlsx
+++ b/word/elementary_words_ko_zh.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" s="28" t="inlineStr">
         <is>
-          <t>Apple.png</t>
+          <t>apple.png</t>
         </is>
       </c>
       <c r="I2" s="28" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="H3" s="30" t="inlineStr">
         <is>
-          <t>Banana.png</t>
+          <t>banana.png</t>
         </is>
       </c>
       <c r="I3" s="30" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="H4" s="28" t="inlineStr">
         <is>
-          <t>Orange.png</t>
+          <t>orange.png</t>
         </is>
       </c>
       <c r="I4" s="28" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H5" s="30" t="inlineStr">
         <is>
-          <t>Grape.png</t>
+          <t>grape.png</t>
         </is>
       </c>
       <c r="I5" s="30" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="H6" s="28" t="inlineStr">
         <is>
-          <t>Strawberry.png</t>
+          <t>strawberry.png</t>
         </is>
       </c>
       <c r="I6" s="28" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>Peach.png</t>
+          <t>peach.png</t>
         </is>
       </c>
       <c r="I7" s="30" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="H8" s="28" t="inlineStr">
         <is>
-          <t>Watermelon.png</t>
+          <t>watermelon.png</t>
         </is>
       </c>
       <c r="I8" s="28" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="H9" s="30" t="inlineStr">
         <is>
-          <t>Lemon.png</t>
+          <t>lemon.png</t>
         </is>
       </c>
       <c r="I9" s="30" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="H10" s="28" t="inlineStr">
         <is>
-          <t>Melon.png</t>
+          <t>melon.png</t>
         </is>
       </c>
       <c r="I10" s="28" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="H11" s="30" t="inlineStr">
         <is>
-          <t>Tomato.png</t>
+          <t>tomato.png</t>
         </is>
       </c>
       <c r="I11" s="30" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" s="28" t="inlineStr">
         <is>
-          <t>Milk.png</t>
+          <t>milk.png</t>
         </is>
       </c>
       <c r="I12" s="28" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H13" s="30" t="inlineStr">
         <is>
-          <t>Water.png</t>
+          <t>water.png</t>
         </is>
       </c>
       <c r="I13" s="30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H14" s="28" t="inlineStr">
         <is>
-          <t>Juice.png</t>
+          <t>juice.png</t>
         </is>
       </c>
       <c r="I14" s="28" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="H15" s="30" t="inlineStr">
         <is>
-          <t>Bread.png</t>
+          <t>bread.png</t>
         </is>
       </c>
       <c r="I15" s="30" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="H16" s="28" t="inlineStr">
         <is>
-          <t>Rice.png</t>
+          <t>rice.png</t>
         </is>
       </c>
       <c r="I16" s="28" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H17" s="30" t="inlineStr">
         <is>
-          <t>Egg.png</t>
+          <t>egg.png</t>
         </is>
       </c>
       <c r="I17" s="30" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H18" s="28" t="inlineStr">
         <is>
-          <t>Cake.png</t>
+          <t>cake.png</t>
         </is>
       </c>
       <c r="I18" s="28" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="H19" s="30" t="inlineStr">
         <is>
-          <t>Candy.png</t>
+          <t>candy.png</t>
         </is>
       </c>
       <c r="I19" s="30" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="H20" s="28" t="inlineStr">
         <is>
-          <t>Cookie.png</t>
+          <t>cookie.png</t>
         </is>
       </c>
       <c r="I20" s="28" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H21" s="30" t="inlineStr">
         <is>
-          <t>Chocolate.png</t>
+          <t>chocolate.png</t>
         </is>
       </c>
       <c r="I21" s="30" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H22" s="28" t="inlineStr">
         <is>
-          <t>Ice_cream.png</t>
+          <t>ice cream.png</t>
         </is>
       </c>
       <c r="I22" s="28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H23" s="30" t="inlineStr">
         <is>
-          <t>Pizza.png</t>
+          <t>pizza.png</t>
         </is>
       </c>
       <c r="I23" s="30" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="H24" s="28" t="inlineStr">
         <is>
-          <t>Hamburger.png</t>
+          <t>hamburger.png</t>
         </is>
       </c>
       <c r="I24" s="28" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H25" s="30" t="inlineStr">
         <is>
-          <t>Noodle.png</t>
+          <t>noodle.png</t>
         </is>
       </c>
       <c r="I25" s="30" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="H26" s="28" t="inlineStr">
         <is>
-          <t>Soup.png</t>
+          <t>soup.png</t>
         </is>
       </c>
       <c r="I26" s="28" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>Salad.png</t>
+          <t>salad.png</t>
         </is>
       </c>
       <c r="I27" s="30" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H28" s="28" t="inlineStr">
         <is>
-          <t>Meat.png</t>
+          <t>meat.png</t>
         </is>
       </c>
       <c r="I28" s="28" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H29" s="30" t="inlineStr">
         <is>
-          <t>Fish.png</t>
+          <t>fish.png</t>
         </is>
       </c>
       <c r="I29" s="30" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="H30" s="28" t="inlineStr">
         <is>
-          <t>Cheese.png</t>
+          <t>cheese.png</t>
         </is>
       </c>
       <c r="I30" s="28" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="H31" s="30" t="inlineStr">
         <is>
-          <t>Butter.png</t>
+          <t>butter.png</t>
         </is>
       </c>
       <c r="I31" s="30" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H32" s="28" t="inlineStr">
         <is>
-          <t>Cherry.png</t>
+          <t>cherry.png</t>
         </is>
       </c>
       <c r="I32" s="28" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H33" s="30" t="inlineStr">
         <is>
-          <t>Potato.png</t>
+          <t>potato.png</t>
         </is>
       </c>
       <c r="I33" s="30" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="H34" s="28" t="inlineStr">
         <is>
-          <t>Carrot.png</t>
+          <t>carrot.png</t>
         </is>
       </c>
       <c r="I34" s="28" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>Onion.png</t>
+          <t>onion.png</t>
         </is>
       </c>
       <c r="I35" s="30" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H36" s="28" t="inlineStr">
         <is>
-          <t>Corn.png</t>
+          <t>corn.png</t>
         </is>
       </c>
       <c r="I36" s="28" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="H37" s="30" t="inlineStr">
         <is>
-          <t>Salt.png</t>
+          <t>salt.png</t>
         </is>
       </c>
       <c r="I37" s="30" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
-          <t>Sugar.png</t>
+          <t>sugar.png</t>
         </is>
       </c>
       <c r="I38" s="28" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H39" s="30" t="inlineStr">
         <is>
-          <t>Tea.png</t>
+          <t>tea.png</t>
         </is>
       </c>
       <c r="I39" s="30" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="H40" s="28" t="inlineStr">
         <is>
-          <t>Coffee.png</t>
+          <t>coffee.png</t>
         </is>
       </c>
       <c r="I40" s="28" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>Cream.png</t>
+          <t>cream.png</t>
         </is>
       </c>
       <c r="I41" s="30" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="H42" s="28" t="inlineStr">
         <is>
-          <t>Honey.png</t>
+          <t>honey.png</t>
         </is>
       </c>
       <c r="I42" s="28" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
-          <t>Pie.png</t>
+          <t>pie.png</t>
         </is>
       </c>
       <c r="I43" s="30" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
-          <t>Donut.png</t>
+          <t>donut.png</t>
         </is>
       </c>
       <c r="I44" s="28" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>Sandwich.png</t>
+          <t>sandwich.png</t>
         </is>
       </c>
       <c r="I45" s="30" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H46" s="28" t="inlineStr">
         <is>
-          <t>Sausage.png</t>
+          <t>sausage.png</t>
         </is>
       </c>
       <c r="I46" s="28" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H47" s="30" t="inlineStr">
         <is>
-          <t>Pork.png</t>
+          <t>pork.png</t>
         </is>
       </c>
       <c r="I47" s="30" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
-          <t>Beef.png</t>
+          <t>beef.png</t>
         </is>
       </c>
       <c r="I48" s="28" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H49" s="30" t="inlineStr">
         <is>
-          <t>Jam.png</t>
+          <t>jam.png</t>
         </is>
       </c>
       <c r="I49" s="30" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H50" s="28" t="inlineStr">
         <is>
-          <t>Oil.png</t>
+          <t>oil.png</t>
         </is>
       </c>
       <c r="I50" s="28" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="H51" s="30" t="inlineStr">
         <is>
-          <t>Bacon.png</t>
+          <t>bacon.png</t>
         </is>
       </c>
       <c r="I51" s="30" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H52" s="28" t="inlineStr">
         <is>
-          <t>Bagel.png</t>
+          <t>bagel.png</t>
         </is>
       </c>
       <c r="I52" s="28" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" s="30" t="inlineStr">
         <is>
-          <t>Bean.png</t>
+          <t>bean.png</t>
         </is>
       </c>
       <c r="I53" s="30" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
-          <t>Berry.png</t>
+          <t>berry.png</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="H55" s="30" t="inlineStr">
         <is>
-          <t>Biscuit.png</t>
+          <t>biscuit.png</t>
         </is>
       </c>
       <c r="I55" s="30" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="H56" s="28" t="inlineStr">
         <is>
-          <t>Coconut.png</t>
+          <t>coconut.png</t>
         </is>
       </c>
       <c r="I56" s="28" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H57" s="30" t="inlineStr">
         <is>
-          <t>Jelly.png</t>
+          <t>jelly.png</t>
         </is>
       </c>
       <c r="I57" s="30" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="H58" s="28" t="inlineStr">
         <is>
-          <t>Mango.png</t>
+          <t>mango.png</t>
         </is>
       </c>
       <c r="I58" s="28" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="H59" s="30" t="inlineStr">
         <is>
-          <t>Kiwi.png</t>
+          <t>kiwi.png</t>
         </is>
       </c>
       <c r="I59" s="30" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="H60" s="28" t="inlineStr">
         <is>
-          <t>Plum.png</t>
+          <t>plum.png</t>
         </is>
       </c>
       <c r="I60" s="28" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="H61" s="30" t="inlineStr">
         <is>
-          <t>Blueberry.png</t>
+          <t>blueberry.png</t>
         </is>
       </c>
       <c r="I61" s="30" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="H62" s="28" t="inlineStr">
         <is>
-          <t>Chestnut.png</t>
+          <t>chestnut.png</t>
         </is>
       </c>
       <c r="I62" s="28" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="H63" s="30" t="inlineStr">
         <is>
-          <t>Walnut.png</t>
+          <t>walnut.png</t>
         </is>
       </c>
       <c r="I63" s="30" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="H64" s="28" t="inlineStr">
         <is>
-          <t>Peanut.png</t>
+          <t>peanut.png</t>
         </is>
       </c>
       <c r="I64" s="28" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H65" s="30" t="inlineStr">
         <is>
-          <t>Almond.png</t>
+          <t>almond.png</t>
         </is>
       </c>
       <c r="I65" s="30" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="H66" s="28" t="inlineStr">
         <is>
-          <t>Cabbage.png</t>
+          <t>cabbage.png</t>
         </is>
       </c>
       <c r="I66" s="28" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H67" s="30" t="inlineStr">
         <is>
-          <t>Lettuce.png</t>
+          <t>lettuce.png</t>
         </is>
       </c>
       <c r="I67" s="30" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Spinach.png</t>
+          <t>spinach.png</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="H69" s="30" t="inlineStr">
         <is>
-          <t>Pumpkin.png</t>
+          <t>pumpkin.png</t>
         </is>
       </c>
       <c r="I69" s="30" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>Garlic.png</t>
+          <t>garlic.png</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="H71" s="30" t="inlineStr">
         <is>
-          <t>Mushroom.png</t>
+          <t>mushroom.png</t>
         </is>
       </c>
       <c r="I71" s="30" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="H72" s="28" t="inlineStr">
         <is>
-          <t>Cucumber.png</t>
+          <t>cucumber.png</t>
         </is>
       </c>
       <c r="I72" s="28" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H73" s="30" t="inlineStr">
         <is>
-          <t>Ham.png</t>
+          <t>ham.png</t>
         </is>
       </c>
       <c r="I73" s="30" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="H74" s="28" t="inlineStr">
         <is>
-          <t>Shrimp.png</t>
+          <t>shrimp.png</t>
         </is>
       </c>
       <c r="I74" s="28" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="H75" s="30" t="inlineStr">
         <is>
-          <t>Tuna.png</t>
+          <t>tuna.png</t>
         </is>
       </c>
       <c r="I75" s="30" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H76" s="28" t="inlineStr">
         <is>
-          <t>Seaweed.png</t>
+          <t>seaweed.png</t>
         </is>
       </c>
       <c r="I76" s="28" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="H77" s="30" t="inlineStr">
         <is>
-          <t>Tofu.png</t>
+          <t>tofu.png</t>
         </is>
       </c>
       <c r="I77" s="30" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Dumpling.png</t>
+          <t>dumpling.png</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="H79" s="30" t="inlineStr">
         <is>
-          <t>Pancake.png</t>
+          <t>pancake.png</t>
         </is>
       </c>
       <c r="I79" s="30" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="H80" s="28" t="inlineStr">
         <is>
-          <t>Yogurt.png</t>
+          <t>yogurt.png</t>
         </is>
       </c>
       <c r="I80" s="28" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H81" s="30" t="inlineStr">
         <is>
-          <t>Flour.png</t>
+          <t>flour.png</t>
         </is>
       </c>
       <c r="I81" s="30" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H82" s="28" t="inlineStr">
         <is>
-          <t>Pepper.png</t>
+          <t>pepper.png</t>
         </is>
       </c>
       <c r="I82" s="28" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="H83" s="30" t="inlineStr">
         <is>
-          <t>Sauce.png</t>
+          <t>sauce.png</t>
         </is>
       </c>
       <c r="I83" s="30" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="H84" s="28" t="inlineStr">
         <is>
-          <t>Stew.png</t>
+          <t>stew.png</t>
         </is>
       </c>
       <c r="I84" s="28" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H85" s="30" t="inlineStr">
         <is>
-          <t>Cereal.png</t>
+          <t>cereal.png</t>
         </is>
       </c>
       <c r="I85" s="30" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="H86" s="28" t="inlineStr">
         <is>
-          <t>Dog.png</t>
+          <t>dog.png</t>
         </is>
       </c>
       <c r="I86" s="28" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="H87" s="30" t="inlineStr">
         <is>
-          <t>Cat.png</t>
+          <t>cat.png</t>
         </is>
       </c>
       <c r="I87" s="30" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="H88" s="28" t="inlineStr">
         <is>
-          <t>Bird.png</t>
+          <t>bird.png</t>
         </is>
       </c>
       <c r="I88" s="28" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H89" s="30" t="inlineStr">
         <is>
-          <t>Duck.png</t>
+          <t>duck.png</t>
         </is>
       </c>
       <c r="I89" s="30" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="H90" s="28" t="inlineStr">
         <is>
-          <t>Chicken.png</t>
+          <t>chicken.png</t>
         </is>
       </c>
       <c r="I90" s="28" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H91" s="30" t="inlineStr">
         <is>
-          <t>Pig.png</t>
+          <t>pig.png</t>
         </is>
       </c>
       <c r="I91" s="30" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="H92" s="28" t="inlineStr">
         <is>
-          <t>Cow.png</t>
+          <t>cow.png</t>
         </is>
       </c>
       <c r="I92" s="28" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="H93" s="30" t="inlineStr">
         <is>
-          <t>Horse.png</t>
+          <t>horse.png</t>
         </is>
       </c>
       <c r="I93" s="30" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>Sheep.png</t>
+          <t>sheep.png</t>
         </is>
       </c>
       <c r="I94" s="28" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H95" s="30" t="inlineStr">
         <is>
-          <t>Rabbit.png</t>
+          <t>rabbit.png</t>
         </is>
       </c>
       <c r="I95" s="30" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H96" s="28" t="inlineStr">
         <is>
-          <t>Bear.png</t>
+          <t>bear.png</t>
         </is>
       </c>
       <c r="I96" s="28" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="H97" s="30" t="inlineStr">
         <is>
-          <t>Lion.png</t>
+          <t>lion.png</t>
         </is>
       </c>
       <c r="I97" s="30" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="H98" s="28" t="inlineStr">
         <is>
-          <t>Tiger.png</t>
+          <t>tiger.png</t>
         </is>
       </c>
       <c r="I98" s="28" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="H99" s="30" t="inlineStr">
         <is>
-          <t>Elephant.png</t>
+          <t>elephant.png</t>
         </is>
       </c>
       <c r="I99" s="30" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H100" s="28" t="inlineStr">
         <is>
-          <t>Giraffe.png</t>
+          <t>giraffe.png</t>
         </is>
       </c>
       <c r="I100" s="28" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="H101" s="30" t="inlineStr">
         <is>
-          <t>Monkey.png</t>
+          <t>monkey.png</t>
         </is>
       </c>
       <c r="I101" s="30" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="H102" s="28" t="inlineStr">
         <is>
-          <t>Fox.png</t>
+          <t>fox.png</t>
         </is>
       </c>
       <c r="I102" s="28" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="H103" s="30" t="inlineStr">
         <is>
-          <t>Frog.png</t>
+          <t>frog.png</t>
         </is>
       </c>
       <c r="I103" s="30" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H104" s="28" t="inlineStr">
         <is>
-          <t>Snake.png</t>
+          <t>snake.png</t>
         </is>
       </c>
       <c r="I104" s="28" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H105" s="30" t="inlineStr">
         <is>
-          <t>Turtle.png</t>
+          <t>turtle.png</t>
         </is>
       </c>
       <c r="I105" s="30" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="H106" s="28" t="inlineStr">
         <is>
-          <t>Whale.png</t>
+          <t>whale.png</t>
         </is>
       </c>
       <c r="I106" s="28" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="H107" s="30" t="inlineStr">
         <is>
-          <t>Dolphin.png</t>
+          <t>dolphin.png</t>
         </is>
       </c>
       <c r="I107" s="30" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="H108" s="28" t="inlineStr">
         <is>
-          <t>Shark.png</t>
+          <t>shark.png</t>
         </is>
       </c>
       <c r="I108" s="28" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H109" s="30" t="inlineStr">
         <is>
-          <t>Mouse.png</t>
+          <t>mouse.png</t>
         </is>
       </c>
       <c r="I109" s="30" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H110" s="28" t="inlineStr">
         <is>
-          <t>Butterfly.png</t>
+          <t>butterfly.png</t>
         </is>
       </c>
       <c r="I110" s="28" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="H111" s="30" t="inlineStr">
         <is>
-          <t>Bee.png</t>
+          <t>bee.png</t>
         </is>
       </c>
       <c r="I111" s="30" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>Ant.png</t>
+          <t>ant.png</t>
         </is>
       </c>
       <c r="I112" s="28" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H113" s="30" t="inlineStr">
         <is>
-          <t>Spider.png</t>
+          <t>spider.png</t>
         </is>
       </c>
       <c r="I113" s="30" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="H114" s="28" t="inlineStr">
         <is>
-          <t>Penguin.png</t>
+          <t>penguin.png</t>
         </is>
       </c>
       <c r="I114" s="28" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="H115" s="30" t="inlineStr">
         <is>
-          <t>Panda.png</t>
+          <t>panda.png</t>
         </is>
       </c>
       <c r="I115" s="30" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="H116" s="28" t="inlineStr">
         <is>
-          <t>Wolf.png</t>
+          <t>wolf.png</t>
         </is>
       </c>
       <c r="I116" s="28" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="H117" s="30" t="inlineStr">
         <is>
-          <t>Deer.png</t>
+          <t>deer.png</t>
         </is>
       </c>
       <c r="I117" s="30" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H118" s="28" t="inlineStr">
         <is>
-          <t>Zebra.png</t>
+          <t>zebra.png</t>
         </is>
       </c>
       <c r="I118" s="28" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="H119" s="30" t="inlineStr">
         <is>
-          <t>Koala.png</t>
+          <t>koala.png</t>
         </is>
       </c>
       <c r="I119" s="30" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="H120" s="28" t="inlineStr">
         <is>
-          <t>Owl.png</t>
+          <t>owl.png</t>
         </is>
       </c>
       <c r="I120" s="28" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="H121" s="30" t="inlineStr">
         <is>
-          <t>Eagle.png</t>
+          <t>eagle.png</t>
         </is>
       </c>
       <c r="I121" s="30" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="H122" s="28" t="inlineStr">
         <is>
-          <t>Bat.png</t>
+          <t>bat.png</t>
         </is>
       </c>
       <c r="I122" s="28" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="H123" s="30" t="inlineStr">
         <is>
-          <t>Crab.png</t>
+          <t>crab.png</t>
         </is>
       </c>
       <c r="I123" s="30" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="H124" s="28" t="inlineStr">
         <is>
-          <t>Octopus.png</t>
+          <t>octopus.png</t>
         </is>
       </c>
       <c r="I124" s="28" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="H125" s="30" t="inlineStr">
         <is>
-          <t>Camel.png</t>
+          <t>camel.png</t>
         </is>
       </c>
       <c r="I125" s="30" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="H126" s="28" t="inlineStr">
         <is>
-          <t>Goat.png</t>
+          <t>goat.png</t>
         </is>
       </c>
       <c r="I126" s="28" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="H127" s="30" t="inlineStr">
         <is>
-          <t>Donkey.png</t>
+          <t>donkey.png</t>
         </is>
       </c>
       <c r="I127" s="30" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="H128" s="28" t="inlineStr">
         <is>
-          <t>Beak.png</t>
+          <t>beak.png</t>
         </is>
       </c>
       <c r="I128" s="28" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="H129" s="30" t="inlineStr">
         <is>
-          <t>Beaver.png</t>
+          <t>beaver.png</t>
         </is>
       </c>
       <c r="I129" s="30" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="H130" s="28" t="inlineStr">
         <is>
-          <t>Bug.png</t>
+          <t>bug.png</t>
         </is>
       </c>
       <c r="I130" s="28" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="H131" s="30" t="inlineStr">
         <is>
-          <t>Calf.png</t>
+          <t>calf.png</t>
         </is>
       </c>
       <c r="I131" s="30" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="H132" s="28" t="inlineStr">
         <is>
-          <t>Dinosaur.png</t>
+          <t>dinosaur.png</t>
         </is>
       </c>
       <c r="I132" s="28" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="H133" s="30" t="inlineStr">
         <is>
-          <t>Insect.png</t>
+          <t>insect.png</t>
         </is>
       </c>
       <c r="I133" s="30" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H134" s="28" t="inlineStr">
         <is>
-          <t>Kangaroo.png</t>
+          <t>kangaroo.png</t>
         </is>
       </c>
       <c r="I134" s="28" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="H135" s="30" t="inlineStr">
         <is>
-          <t>Kitten.png</t>
+          <t>kitten.png</t>
         </is>
       </c>
       <c r="I135" s="30" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="H136" s="28" t="inlineStr">
         <is>
-          <t>Lizard.png</t>
+          <t>lizard.png</t>
         </is>
       </c>
       <c r="I136" s="28" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H137" s="30" t="inlineStr">
         <is>
-          <t>Squirrel.png</t>
+          <t>squirrel.png</t>
         </is>
       </c>
       <c r="I137" s="30" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="H138" s="28" t="inlineStr">
         <is>
-          <t>Rat.png</t>
+          <t>rat.png</t>
         </is>
       </c>
       <c r="I138" s="28" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="H139" s="30" t="inlineStr">
         <is>
-          <t>Hamster.png</t>
+          <t>hamster.png</t>
         </is>
       </c>
       <c r="I139" s="30" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="H140" s="28" t="inlineStr">
         <is>
-          <t>Crocodile.png</t>
+          <t>crocodile.png</t>
         </is>
       </c>
       <c r="I140" s="28" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="H141" s="30" t="inlineStr">
         <is>
-          <t>Jellyfish.png</t>
+          <t>jellyfish.png</t>
         </is>
       </c>
       <c r="I141" s="30" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="H142" s="28" t="inlineStr">
         <is>
-          <t>Starfish.png</t>
+          <t>starfish.png</t>
         </is>
       </c>
       <c r="I142" s="28" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="H143" s="30" t="inlineStr">
         <is>
-          <t>Seal.png</t>
+          <t>seal.png</t>
         </is>
       </c>
       <c r="I143" s="30" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="H144" s="28" t="inlineStr">
         <is>
-          <t>Crow.png</t>
+          <t>crow.png</t>
         </is>
       </c>
       <c r="I144" s="28" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="H145" s="30" t="inlineStr">
         <is>
-          <t>Sparrow.png</t>
+          <t>sparrow.png</t>
         </is>
       </c>
       <c r="I145" s="30" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H146" s="28" t="inlineStr">
         <is>
-          <t>Pigeon.png</t>
+          <t>pigeon.png</t>
         </is>
       </c>
       <c r="I146" s="28" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="H147" s="30" t="inlineStr">
         <is>
-          <t>Parrot.png</t>
+          <t>parrot.png</t>
         </is>
       </c>
       <c r="I147" s="30" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="H148" s="28" t="inlineStr">
         <is>
-          <t>Peacock.png</t>
+          <t>peacock.png</t>
         </is>
       </c>
       <c r="I148" s="28" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="H149" s="30" t="inlineStr">
         <is>
-          <t>Swan.png</t>
+          <t>swan.png</t>
         </is>
       </c>
       <c r="I149" s="30" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="H150" s="28" t="inlineStr">
         <is>
-          <t>Goose.png</t>
+          <t>goose.png</t>
         </is>
       </c>
       <c r="I150" s="28" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="H151" s="30" t="inlineStr">
         <is>
-          <t>Hippo.png</t>
+          <t>hippo.png</t>
         </is>
       </c>
       <c r="I151" s="30" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="H152" s="28" t="inlineStr">
         <is>
-          <t>Snail.png</t>
+          <t>snail.png</t>
         </is>
       </c>
       <c r="I152" s="28" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H153" s="30" t="inlineStr">
         <is>
-          <t>Worm.png</t>
+          <t>worm.png</t>
         </is>
       </c>
       <c r="I153" s="30" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="H154" s="28" t="inlineStr">
         <is>
-          <t>Beetle.png</t>
+          <t>beetle.png</t>
         </is>
       </c>
       <c r="I154" s="28" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H155" s="30" t="inlineStr">
         <is>
-          <t>Grasshopper.png</t>
+          <t>grasshopper.png</t>
         </is>
       </c>
       <c r="I155" s="30" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="H156" s="28" t="inlineStr">
         <is>
-          <t>Dragonfly.png</t>
+          <t>dragonfly.png</t>
         </is>
       </c>
       <c r="I156" s="28" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="H157" s="30" t="inlineStr">
         <is>
-          <t>Firefly.png</t>
+          <t>firefly.png</t>
         </is>
       </c>
       <c r="I157" s="30" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="H158" s="28" t="inlineStr">
         <is>
-          <t>Mosquito.png</t>
+          <t>mosquito.png</t>
         </is>
       </c>
       <c r="I158" s="28" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="H159" s="30" t="inlineStr">
         <is>
-          <t>Caterpillar.png</t>
+          <t>caterpillar.png</t>
         </is>
       </c>
       <c r="I159" s="30" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="H160" s="28" t="inlineStr">
         <is>
-          <t>Moth.png</t>
+          <t>moth.png</t>
         </is>
       </c>
       <c r="I160" s="28" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="H161" s="30" t="inlineStr">
         <is>
-          <t>Ladybug.png</t>
+          <t>ladybug.png</t>
         </is>
       </c>
       <c r="I161" s="30" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="H162" s="28" t="inlineStr">
         <is>
-          <t>Wing.png</t>
+          <t>wing.png</t>
         </is>
       </c>
       <c r="I162" s="28" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="H163" s="30" t="inlineStr">
         <is>
-          <t>Tail.png</t>
+          <t>tail.png</t>
         </is>
       </c>
       <c r="I163" s="30" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="H164" s="28" t="inlineStr">
         <is>
-          <t>Paw.png</t>
+          <t>paw.png</t>
         </is>
       </c>
       <c r="I164" s="28" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="H165" s="30" t="inlineStr">
         <is>
-          <t>Father.png</t>
+          <t>father.png</t>
         </is>
       </c>
       <c r="I165" s="30" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="H166" s="28" t="inlineStr">
         <is>
-          <t>Mother.png</t>
+          <t>mother.png</t>
         </is>
       </c>
       <c r="I166" s="28" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="H167" s="30" t="inlineStr">
         <is>
-          <t>Brother.png</t>
+          <t>brother.png</t>
         </is>
       </c>
       <c r="I167" s="30" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="H168" s="28" t="inlineStr">
         <is>
-          <t>Sister.png</t>
+          <t>sister.png</t>
         </is>
       </c>
       <c r="I168" s="28" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H169" s="30" t="inlineStr">
         <is>
-          <t>Baby.png</t>
+          <t>baby.png</t>
         </is>
       </c>
       <c r="I169" s="30" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="H170" s="28" t="inlineStr">
         <is>
-          <t>Grandfather.png</t>
+          <t>grandfather.png</t>
         </is>
       </c>
       <c r="I170" s="28" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H171" s="30" t="inlineStr">
         <is>
-          <t>Grandmother.png</t>
+          <t>grandmother.png</t>
         </is>
       </c>
       <c r="I171" s="30" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="H172" s="28" t="inlineStr">
         <is>
-          <t>Family.png</t>
+          <t>family.png</t>
         </is>
       </c>
       <c r="I172" s="28" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="H173" s="30" t="inlineStr">
         <is>
-          <t>Friend.png</t>
+          <t>friend.png</t>
         </is>
       </c>
       <c r="I173" s="30" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H174" s="28" t="inlineStr">
         <is>
-          <t>Student.png</t>
+          <t>student.png</t>
         </is>
       </c>
       <c r="I174" s="28" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="H175" s="30" t="inlineStr">
         <is>
-          <t>Boy.png</t>
+          <t>boy.png</t>
         </is>
       </c>
       <c r="I175" s="30" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="H176" s="28" t="inlineStr">
         <is>
-          <t>Girl.png</t>
+          <t>girl.png</t>
         </is>
       </c>
       <c r="I176" s="28" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="H177" s="30" t="inlineStr">
         <is>
-          <t>Man.png</t>
+          <t>man.png</t>
         </is>
       </c>
       <c r="I177" s="30" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="H178" s="28" t="inlineStr">
         <is>
-          <t>Woman.png</t>
+          <t>woman.png</t>
         </is>
       </c>
       <c r="I178" s="28" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="H179" s="30" t="inlineStr">
         <is>
-          <t>Child.png</t>
+          <t>child.png</t>
         </is>
       </c>
       <c r="I179" s="30" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="H180" s="28" t="inlineStr">
         <is>
-          <t>Parent.png</t>
+          <t>parent.png</t>
         </is>
       </c>
       <c r="I180" s="28" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="H181" s="30" t="inlineStr">
         <is>
-          <t>King.png</t>
+          <t>king.png</t>
         </is>
       </c>
       <c r="I181" s="30" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="H182" s="28" t="inlineStr">
         <is>
-          <t>Queen.png</t>
+          <t>queen.png</t>
         </is>
       </c>
       <c r="I182" s="28" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="H183" s="30" t="inlineStr">
         <is>
-          <t>Hero.png</t>
+          <t>hero.png</t>
         </is>
       </c>
       <c r="I183" s="30" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="H184" s="28" t="inlineStr">
         <is>
-          <t>Group.png</t>
+          <t>group.png</t>
         </is>
       </c>
       <c r="I184" s="28" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="H185" s="30" t="inlineStr">
         <is>
-          <t>Party.png</t>
+          <t>party.png</t>
         </is>
       </c>
       <c r="I185" s="30" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="H186" s="28" t="inlineStr">
         <is>
-          <t>Angel.png</t>
+          <t>angel.png</t>
         </is>
       </c>
       <c r="I186" s="28" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="H187" s="30" t="inlineStr">
         <is>
-          <t>Beauty.png</t>
+          <t>beauty.png</t>
         </is>
       </c>
       <c r="I187" s="30" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="H188" s="28" t="inlineStr">
         <is>
-          <t>Cousin.png</t>
+          <t>cousin.png</t>
         </is>
       </c>
       <c r="I188" s="28" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="H189" s="30" t="inlineStr">
         <is>
-          <t>Giant.png</t>
+          <t>giant.png</t>
         </is>
       </c>
       <c r="I189" s="30" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="H190" s="28" t="inlineStr">
         <is>
-          <t>Monster.png</t>
+          <t>monster.png</t>
         </is>
       </c>
       <c r="I190" s="28" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="H191" s="30" t="inlineStr">
         <is>
-          <t>Nephew.png</t>
+          <t>nephew.png</t>
         </is>
       </c>
       <c r="I191" s="30" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="H192" s="28" t="inlineStr">
         <is>
-          <t>Niece.png</t>
+          <t>niece.png</t>
         </is>
       </c>
       <c r="I192" s="28" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="H193" s="30" t="inlineStr">
         <is>
-          <t>Twin.png</t>
+          <t>twin.png</t>
         </is>
       </c>
       <c r="I193" s="30" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H194" s="28" t="inlineStr">
         <is>
-          <t>Kid.png</t>
+          <t>kid.png</t>
         </is>
       </c>
       <c r="I194" s="28" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H195" s="30" t="inlineStr">
         <is>
-          <t>Classmate.png</t>
+          <t>classmate.png</t>
         </is>
       </c>
       <c r="I195" s="30" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="H196" s="28" t="inlineStr">
         <is>
-          <t>Roommate.png</t>
+          <t>roommate.png</t>
         </is>
       </c>
       <c r="I196" s="28" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="H197" s="30" t="inlineStr">
         <is>
-          <t>Grandchild.png</t>
+          <t>grandchild.png</t>
         </is>
       </c>
       <c r="I197" s="30" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="H198" s="28" t="inlineStr">
         <is>
-          <t>Grandson.png</t>
+          <t>grandson.png</t>
         </is>
       </c>
       <c r="I198" s="28" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H199" s="30" t="inlineStr">
         <is>
-          <t>Granddaughter.png</t>
+          <t>granddaughter.png</t>
         </is>
       </c>
       <c r="I199" s="30" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="H200" s="28" t="inlineStr">
         <is>
-          <t>Gentleman.png</t>
+          <t>gentleman.png</t>
         </is>
       </c>
       <c r="I200" s="28" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="H201" s="30" t="inlineStr">
         <is>
-          <t>Lady.png</t>
+          <t>lady.png</t>
         </is>
       </c>
       <c r="I201" s="30" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="H202" s="28" t="inlineStr">
         <is>
-          <t>Neighborhood.png</t>
+          <t>neighborhood.png</t>
         </is>
       </c>
       <c r="I202" s="28" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="H203" s="30" t="inlineStr">
         <is>
-          <t>Teacher.png</t>
+          <t>teacher.png</t>
         </is>
       </c>
       <c r="I203" s="30" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="H204" s="28" t="inlineStr">
         <is>
-          <t>Doctor.png</t>
+          <t>doctor.png</t>
         </is>
       </c>
       <c r="I204" s="28" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="H205" s="30" t="inlineStr">
         <is>
-          <t>Nurse.png</t>
+          <t>nurse.png</t>
         </is>
       </c>
       <c r="I205" s="30" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="H206" s="28" t="inlineStr">
         <is>
-          <t>Farmer.png</t>
+          <t>farmer.png</t>
         </is>
       </c>
       <c r="I206" s="28" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="H207" s="30" t="inlineStr">
         <is>
-          <t>Cook.png</t>
+          <t>cook.png</t>
         </is>
       </c>
       <c r="I207" s="30" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="H208" s="28" t="inlineStr">
         <is>
-          <t>Police.png</t>
+          <t>police.png</t>
         </is>
       </c>
       <c r="I208" s="28" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="H209" s="30" t="inlineStr">
         <is>
-          <t>Firefighter.png</t>
+          <t>firefighter.png</t>
         </is>
       </c>
       <c r="I209" s="30" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="H210" s="28" t="inlineStr">
         <is>
-          <t>Singer.png</t>
+          <t>singer.png</t>
         </is>
       </c>
       <c r="I210" s="28" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="H211" s="30" t="inlineStr">
         <is>
-          <t>Dancer.png</t>
+          <t>dancer.png</t>
         </is>
       </c>
       <c r="I211" s="30" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="H212" s="28" t="inlineStr">
         <is>
-          <t>Pilot.png</t>
+          <t>pilot.png</t>
         </is>
       </c>
       <c r="I212" s="28" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="H213" s="30" t="inlineStr">
         <is>
-          <t>Driver.png</t>
+          <t>driver.png</t>
         </is>
       </c>
       <c r="I213" s="30" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="H214" s="28" t="inlineStr">
         <is>
-          <t>Player.png</t>
+          <t>player.png</t>
         </is>
       </c>
       <c r="I214" s="28" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="H215" s="30" t="inlineStr">
         <is>
-          <t>Actor.png</t>
+          <t>actor.png</t>
         </is>
       </c>
       <c r="I215" s="30" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H216" s="28" t="inlineStr">
         <is>
-          <t>Actress.png</t>
+          <t>actress.png</t>
         </is>
       </c>
       <c r="I216" s="28" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="H217" s="30" t="inlineStr">
         <is>
-          <t>Artist.png</t>
+          <t>artist.png</t>
         </is>
       </c>
       <c r="I217" s="30" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="H218" s="28" t="inlineStr">
         <is>
-          <t>Barber.png</t>
+          <t>barber.png</t>
         </is>
       </c>
       <c r="I218" s="28" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="H219" s="30" t="inlineStr">
         <is>
-          <t>Chef.png</t>
+          <t>chef.png</t>
         </is>
       </c>
       <c r="I219" s="30" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="H220" s="28" t="inlineStr">
         <is>
-          <t>Clown.png</t>
+          <t>clown.png</t>
         </is>
       </c>
       <c r="I220" s="28" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="H221" s="30" t="inlineStr">
         <is>
-          <t>Dentist.png</t>
+          <t>dentist.png</t>
         </is>
       </c>
       <c r="I221" s="30" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="H222" s="28" t="inlineStr">
         <is>
-          <t>Vet.png</t>
+          <t>vet.png</t>
         </is>
       </c>
       <c r="I222" s="28" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="H223" s="30" t="inlineStr">
         <is>
-          <t>Baker.png</t>
+          <t>baker.png</t>
         </is>
       </c>
       <c r="I223" s="30" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="H224" s="28" t="inlineStr">
         <is>
-          <t>Tailor.png</t>
+          <t>tailor.png</t>
         </is>
       </c>
       <c r="I224" s="28" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H225" s="30" t="inlineStr">
         <is>
-          <t>Sailor.png</t>
+          <t>sailor.png</t>
         </is>
       </c>
       <c r="I225" s="30" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="H226" s="28" t="inlineStr">
         <is>
-          <t>Scientist.png</t>
+          <t>scientist.png</t>
         </is>
       </c>
       <c r="I226" s="28" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="H227" s="30" t="inlineStr">
         <is>
-          <t>Reporter.png</t>
+          <t>reporter.png</t>
         </is>
       </c>
       <c r="I227" s="30" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="H228" s="28" t="inlineStr">
         <is>
-          <t>Photographer.png</t>
+          <t>photographer.png</t>
         </is>
       </c>
       <c r="I228" s="28" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="H229" s="30" t="inlineStr">
         <is>
-          <t>Designer.png</t>
+          <t>designer.png</t>
         </is>
       </c>
       <c r="I229" s="30" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="H230" s="28" t="inlineStr">
         <is>
-          <t>Mechanic.png</t>
+          <t>mechanic.png</t>
         </is>
       </c>
       <c r="I230" s="28" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="H231" s="30" t="inlineStr">
         <is>
-          <t>Carpenter.png</t>
+          <t>carpenter.png</t>
         </is>
       </c>
       <c r="I231" s="30" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="H232" s="28" t="inlineStr">
         <is>
-          <t>Gardener.png</t>
+          <t>gardener.png</t>
         </is>
       </c>
       <c r="I232" s="28" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="H233" s="30" t="inlineStr">
         <is>
-          <t>Head.png</t>
+          <t>head.png</t>
         </is>
       </c>
       <c r="I233" s="30" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="H234" s="28" t="inlineStr">
         <is>
-          <t>Hair.png</t>
+          <t>hair.png</t>
         </is>
       </c>
       <c r="I234" s="28" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="H235" s="30" t="inlineStr">
         <is>
-          <t>Eye.png</t>
+          <t>eye.png</t>
         </is>
       </c>
       <c r="I235" s="30" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="H236" s="28" t="inlineStr">
         <is>
-          <t>Nose.png</t>
+          <t>nose.png</t>
         </is>
       </c>
       <c r="I236" s="28" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="H237" s="30" t="inlineStr">
         <is>
-          <t>Mouth.png</t>
+          <t>mouth.png</t>
         </is>
       </c>
       <c r="I237" s="30" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="H238" s="28" t="inlineStr">
         <is>
-          <t>Ear.png</t>
+          <t>ear.png</t>
         </is>
       </c>
       <c r="I238" s="28" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="H239" s="30" t="inlineStr">
         <is>
-          <t>Tooth.png</t>
+          <t>tooth.png</t>
         </is>
       </c>
       <c r="I239" s="30" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="H240" s="28" t="inlineStr">
         <is>
-          <t>Face.png</t>
+          <t>face.png</t>
         </is>
       </c>
       <c r="I240" s="28" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="H241" s="30" t="inlineStr">
         <is>
-          <t>Hand.png</t>
+          <t>hand.png</t>
         </is>
       </c>
       <c r="I241" s="30" t="inlineStr">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="H242" s="28" t="inlineStr">
         <is>
-          <t>Finger.png</t>
+          <t>finger.png</t>
         </is>
       </c>
       <c r="I242" s="28" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="H243" s="30" t="inlineStr">
         <is>
-          <t>Arm.png</t>
+          <t>arm.png</t>
         </is>
       </c>
       <c r="I243" s="30" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="H244" s="28" t="inlineStr">
         <is>
-          <t>Leg.png</t>
+          <t>leg.png</t>
         </is>
       </c>
       <c r="I244" s="28" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="H245" s="30" t="inlineStr">
         <is>
-          <t>Foot.png</t>
+          <t>foot.png</t>
         </is>
       </c>
       <c r="I245" s="30" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="H246" s="28" t="inlineStr">
         <is>
-          <t>Neck.png</t>
+          <t>neck.png</t>
         </is>
       </c>
       <c r="I246" s="28" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="H247" s="30" t="inlineStr">
         <is>
-          <t>Shoulder.png</t>
+          <t>shoulder.png</t>
         </is>
       </c>
       <c r="I247" s="30" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="H248" s="28" t="inlineStr">
         <is>
-          <t>Toe.png</t>
+          <t>toe.png</t>
         </is>
       </c>
       <c r="I248" s="28" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="H249" s="30" t="inlineStr">
         <is>
-          <t>Body.png</t>
+          <t>body.png</t>
         </is>
       </c>
       <c r="I249" s="30" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="H250" s="28" t="inlineStr">
         <is>
-          <t>Voice.png</t>
+          <t>voice.png</t>
         </is>
       </c>
       <c r="I250" s="28" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="H251" s="30" t="inlineStr">
         <is>
-          <t>Beard.png</t>
+          <t>beard.png</t>
         </is>
       </c>
       <c r="I251" s="30" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="H252" s="28" t="inlineStr">
         <is>
-          <t>Bone.png</t>
+          <t>bone.png</t>
         </is>
       </c>
       <c r="I252" s="28" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="H253" s="30" t="inlineStr">
         <is>
-          <t>Brain.png</t>
+          <t>brain.png</t>
         </is>
       </c>
       <c r="I253" s="30" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="H254" s="28" t="inlineStr">
         <is>
-          <t>Chest.png</t>
+          <t>chest.png</t>
         </is>
       </c>
       <c r="I254" s="28" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="H255" s="30" t="inlineStr">
         <is>
-          <t>Chin.png</t>
+          <t>chin.png</t>
         </is>
       </c>
       <c r="I255" s="30" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H256" s="28" t="inlineStr">
         <is>
-          <t>Claw.png</t>
+          <t>claw.png</t>
         </is>
       </c>
       <c r="I256" s="28" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="H257" s="30" t="inlineStr">
         <is>
-          <t>Feather.png</t>
+          <t>feather.png</t>
         </is>
       </c>
       <c r="I257" s="30" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="H258" s="28" t="inlineStr">
         <is>
-          <t>Fingerprint.png</t>
+          <t>fingerprint.png</t>
         </is>
       </c>
       <c r="I258" s="28" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="H259" s="30" t="inlineStr">
         <is>
-          <t>Horn.png</t>
+          <t>horn.png</t>
         </is>
       </c>
       <c r="I259" s="30" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="H260" s="28" t="inlineStr">
         <is>
-          <t>Forehead.png</t>
+          <t>forehead.png</t>
         </is>
       </c>
       <c r="I260" s="28" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="H261" s="30" t="inlineStr">
         <is>
-          <t>Cheek.png</t>
+          <t>cheek.png</t>
         </is>
       </c>
       <c r="I261" s="30" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="H262" s="28" t="inlineStr">
         <is>
-          <t>Throat.png</t>
+          <t>throat.png</t>
         </is>
       </c>
       <c r="I262" s="28" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="H263" s="30" t="inlineStr">
         <is>
-          <t>Elbow.png</t>
+          <t>elbow.png</t>
         </is>
       </c>
       <c r="I263" s="30" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="H264" s="28" t="inlineStr">
         <is>
-          <t>Wrist.png</t>
+          <t>wrist.png</t>
         </is>
       </c>
       <c r="I264" s="28" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="H265" s="30" t="inlineStr">
         <is>
-          <t>Palm.png</t>
+          <t>palm.png</t>
         </is>
       </c>
       <c r="I265" s="30" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="H266" s="28" t="inlineStr">
         <is>
-          <t>Thumb.png</t>
+          <t>thumb.png</t>
         </is>
       </c>
       <c r="I266" s="28" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="H267" s="30" t="inlineStr">
         <is>
-          <t>Waist.png</t>
+          <t>waist.png</t>
         </is>
       </c>
       <c r="I267" s="30" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="H268" s="28" t="inlineStr">
         <is>
-          <t>Hip.png</t>
+          <t>hip.png</t>
         </is>
       </c>
       <c r="I268" s="28" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="H269" s="30" t="inlineStr">
         <is>
-          <t>Thigh.png</t>
+          <t>thigh.png</t>
         </is>
       </c>
       <c r="I269" s="30" t="inlineStr">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="H270" s="28" t="inlineStr">
         <is>
-          <t>Cap.png</t>
+          <t>cap.png</t>
         </is>
       </c>
       <c r="I270" s="28" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="H271" s="30" t="inlineStr">
         <is>
-          <t>Hat.png</t>
+          <t>hat.png</t>
         </is>
       </c>
       <c r="I271" s="30" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="H272" s="28" t="inlineStr">
         <is>
-          <t>Shirt.png</t>
+          <t>shirt.png</t>
         </is>
       </c>
       <c r="I272" s="28" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="H273" s="30" t="inlineStr">
         <is>
-          <t>Pants.png</t>
+          <t>pants.png</t>
         </is>
       </c>
       <c r="I273" s="30" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="H274" s="28" t="inlineStr">
         <is>
-          <t>Shoes.png</t>
+          <t>shoes.png</t>
         </is>
       </c>
       <c r="I274" s="28" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="H275" s="30" t="inlineStr">
         <is>
-          <t>Pocket.png</t>
+          <t>pocket.png</t>
         </is>
       </c>
       <c r="I275" s="30" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="H276" s="28" t="inlineStr">
         <is>
-          <t>Apron.png</t>
+          <t>apron.png</t>
         </is>
       </c>
       <c r="I276" s="28" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H277" s="30" t="inlineStr">
         <is>
-          <t>Badge.png</t>
+          <t>badge.png</t>
         </is>
       </c>
       <c r="I277" s="30" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="H278" s="28" t="inlineStr">
         <is>
-          <t>Belt.png</t>
+          <t>belt.png</t>
         </is>
       </c>
       <c r="I278" s="28" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="H279" s="30" t="inlineStr">
         <is>
-          <t>Blouse.png</t>
+          <t>blouse.png</t>
         </is>
       </c>
       <c r="I279" s="30" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="H280" s="28" t="inlineStr">
         <is>
-          <t>Coat.png</t>
+          <t>coat.png</t>
         </is>
       </c>
       <c r="I280" s="28" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="H281" s="30" t="inlineStr">
         <is>
-          <t>Collar.png</t>
+          <t>collar.png</t>
         </is>
       </c>
       <c r="I281" s="30" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="H282" s="28" t="inlineStr">
         <is>
-          <t>Crown.png</t>
+          <t>crown.png</t>
         </is>
       </c>
       <c r="I282" s="28" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="H283" s="30" t="inlineStr">
         <is>
-          <t>Dress.png</t>
+          <t>dress.png</t>
         </is>
       </c>
       <c r="I283" s="30" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="H284" s="28" t="inlineStr">
         <is>
-          <t>Glove.png</t>
+          <t>glove.png</t>
         </is>
       </c>
       <c r="I284" s="28" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="H285" s="30" t="inlineStr">
         <is>
-          <t>Helmet.png</t>
+          <t>helmet.png</t>
         </is>
       </c>
       <c r="I285" s="30" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="H286" s="28" t="inlineStr">
         <is>
-          <t>Jacket.png</t>
+          <t>jacket.png</t>
         </is>
       </c>
       <c r="I286" s="28" t="inlineStr">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="H287" s="30" t="inlineStr">
         <is>
-          <t>Skirt.png</t>
+          <t>skirt.png</t>
         </is>
       </c>
       <c r="I287" s="30" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="H288" s="28" t="inlineStr">
         <is>
-          <t>Sweater.png</t>
+          <t>sweater.png</t>
         </is>
       </c>
       <c r="I288" s="28" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="H289" s="30" t="inlineStr">
         <is>
-          <t>Vest.png</t>
+          <t>vest.png</t>
         </is>
       </c>
       <c r="I289" s="30" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="H290" s="28" t="inlineStr">
         <is>
-          <t>Jeans.png</t>
+          <t>jeans.png</t>
         </is>
       </c>
       <c r="I290" s="28" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="H291" s="30" t="inlineStr">
         <is>
-          <t>Shorts.png</t>
+          <t>shorts.png</t>
         </is>
       </c>
       <c r="I291" s="30" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="H292" s="28" t="inlineStr">
         <is>
-          <t>Boots.png</t>
+          <t>boots.png</t>
         </is>
       </c>
       <c r="I292" s="28" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="H293" s="30" t="inlineStr">
         <is>
-          <t>Sandals.png</t>
+          <t>sandals.png</t>
         </is>
       </c>
       <c r="I293" s="30" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="H294" s="28" t="inlineStr">
         <is>
-          <t>Sneakers.png</t>
+          <t>sneakers.png</t>
         </is>
       </c>
       <c r="I294" s="28" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="H295" s="30" t="inlineStr">
         <is>
-          <t>Slippers.png</t>
+          <t>slippers.png</t>
         </is>
       </c>
       <c r="I295" s="30" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="H296" s="28" t="inlineStr">
         <is>
-          <t>Gloves.png</t>
+          <t>gloves.png</t>
         </is>
       </c>
       <c r="I296" s="28" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="H297" s="30" t="inlineStr">
         <is>
-          <t>School.png</t>
+          <t>school.png</t>
         </is>
       </c>
       <c r="I297" s="30" t="inlineStr">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="H298" s="28" t="inlineStr">
         <is>
-          <t>Book.png</t>
+          <t>book.png</t>
         </is>
       </c>
       <c r="I298" s="28" t="inlineStr">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="H299" s="30" t="inlineStr">
         <is>
-          <t>Pencil.png</t>
+          <t>pencil.png</t>
         </is>
       </c>
       <c r="I299" s="30" t="inlineStr">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="H300" s="28" t="inlineStr">
         <is>
-          <t>Pen.png</t>
+          <t>pen.png</t>
         </is>
       </c>
       <c r="I300" s="28" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="H301" s="30" t="inlineStr">
         <is>
-          <t>Eraser.png</t>
+          <t>eraser.png</t>
         </is>
       </c>
       <c r="I301" s="30" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="H302" s="28" t="inlineStr">
         <is>
-          <t>Ruler.png</t>
+          <t>ruler.png</t>
         </is>
       </c>
       <c r="I302" s="28" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="H303" s="30" t="inlineStr">
         <is>
-          <t>Crayon.png</t>
+          <t>crayon.png</t>
         </is>
       </c>
       <c r="I303" s="30" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="H304" s="28" t="inlineStr">
         <is>
-          <t>Scissors.png</t>
+          <t>scissors.png</t>
         </is>
       </c>
       <c r="I304" s="28" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="H305" s="30" t="inlineStr">
         <is>
-          <t>Glue.png</t>
+          <t>glue.png</t>
         </is>
       </c>
       <c r="I305" s="30" t="inlineStr">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="H306" s="28" t="inlineStr">
         <is>
-          <t>Notebook.png</t>
+          <t>notebook.png</t>
         </is>
       </c>
       <c r="I306" s="28" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="H307" s="30" t="inlineStr">
         <is>
-          <t>Bag.png</t>
+          <t>bag.png</t>
         </is>
       </c>
       <c r="I307" s="30" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H308" s="28" t="inlineStr">
         <is>
-          <t>Desk.png</t>
+          <t>desk.png</t>
         </is>
       </c>
       <c r="I308" s="28" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="H309" s="30" t="inlineStr">
         <is>
-          <t>Chair.png</t>
+          <t>chair.png</t>
         </is>
       </c>
       <c r="I309" s="30" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="H310" s="28" t="inlineStr">
         <is>
-          <t>Classroom.png</t>
+          <t>classroom.png</t>
         </is>
       </c>
       <c r="I310" s="28" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="H311" s="30" t="inlineStr">
         <is>
-          <t>Blackboard.png</t>
+          <t>blackboard.png</t>
         </is>
       </c>
       <c r="I311" s="30" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="H312" s="28" t="inlineStr">
         <is>
-          <t>Computer.png</t>
+          <t>computer.png</t>
         </is>
       </c>
       <c r="I312" s="28" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="H313" s="30" t="inlineStr">
         <is>
-          <t>Paper.png</t>
+          <t>paper.png</t>
         </is>
       </c>
       <c r="I313" s="30" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="H314" s="28" t="inlineStr">
         <is>
-          <t>Board.png</t>
+          <t>board.png</t>
         </is>
       </c>
       <c r="I314" s="28" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="H315" s="30" t="inlineStr">
         <is>
-          <t>Art.png</t>
+          <t>art.png</t>
         </is>
       </c>
       <c r="I315" s="30" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="H316" s="28" t="inlineStr">
         <is>
-          <t>Math.png</t>
+          <t>math.png</t>
         </is>
       </c>
       <c r="I316" s="28" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H317" s="30" t="inlineStr">
         <is>
-          <t>Science.png</t>
+          <t>science.png</t>
         </is>
       </c>
       <c r="I317" s="30" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="H318" s="28" t="inlineStr">
         <is>
-          <t>History.png</t>
+          <t>history.png</t>
         </is>
       </c>
       <c r="I318" s="28" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="H319" s="30" t="inlineStr">
         <is>
-          <t>English.png</t>
+          <t>english.png</t>
         </is>
       </c>
       <c r="I319" s="30" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="H320" s="28" t="inlineStr">
         <is>
-          <t>Class.png</t>
+          <t>class.png</t>
         </is>
       </c>
       <c r="I320" s="28" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="H321" s="30" t="inlineStr">
         <is>
-          <t>Lesson.png</t>
+          <t>lesson.png</t>
         </is>
       </c>
       <c r="I321" s="30" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="H322" s="28" t="inlineStr">
         <is>
-          <t>Grade.png</t>
+          <t>grade.png</t>
         </is>
       </c>
       <c r="I322" s="28" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="H323" s="30" t="inlineStr">
         <is>
-          <t>Test.png</t>
+          <t>test.png</t>
         </is>
       </c>
       <c r="I323" s="30" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="H324" s="28" t="inlineStr">
         <is>
-          <t>Score.png</t>
+          <t>score.png</t>
         </is>
       </c>
       <c r="I324" s="28" t="inlineStr">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="H325" s="30" t="inlineStr">
         <is>
-          <t>Chalk.png</t>
+          <t>chalk.png</t>
         </is>
       </c>
       <c r="I325" s="30" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="H326" s="28" t="inlineStr">
         <is>
-          <t>Comic.png</t>
+          <t>comic.png</t>
         </is>
       </c>
       <c r="I326" s="28" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="H327" s="30" t="inlineStr">
         <is>
-          <t>Cube.png</t>
+          <t>cube.png</t>
         </is>
       </c>
       <c r="I327" s="30" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="H328" s="28" t="inlineStr">
         <is>
-          <t>Diary.png</t>
+          <t>diary.png</t>
         </is>
       </c>
       <c r="I328" s="28" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="H329" s="30" t="inlineStr">
         <is>
-          <t>Dictionary.png</t>
+          <t>dictionary.png</t>
         </is>
       </c>
       <c r="I329" s="30" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="H330" s="28" t="inlineStr">
         <is>
-          <t>Globe.png</t>
+          <t>globe.png</t>
         </is>
       </c>
       <c r="I330" s="28" t="inlineStr">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="H331" s="30" t="inlineStr">
         <is>
-          <t>Grammar.png</t>
+          <t>grammar.png</t>
         </is>
       </c>
       <c r="I331" s="30" t="inlineStr">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="H332" s="28" t="inlineStr">
         <is>
-          <t>Magnet.png</t>
+          <t>magnet.png</t>
         </is>
       </c>
       <c r="I332" s="28" t="inlineStr">
@@ -18818,7 +18818,7 @@
       </c>
       <c r="H333" s="30" t="inlineStr">
         <is>
-          <t>Playground.png</t>
+          <t>playground.png</t>
         </is>
       </c>
       <c r="I333" s="30" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="H334" s="28" t="inlineStr">
         <is>
-          <t>Gym.png</t>
+          <t>gym.png</t>
         </is>
       </c>
       <c r="I334" s="28" t="inlineStr">
@@ -18928,7 +18928,7 @@
       </c>
       <c r="H335" s="30" t="inlineStr">
         <is>
-          <t>Cafeteria.png</t>
+          <t>cafeteria.png</t>
         </is>
       </c>
       <c r="I335" s="30" t="inlineStr">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="H336" s="28" t="inlineStr">
         <is>
-          <t>Homework.png</t>
+          <t>homework.png</t>
         </is>
       </c>
       <c r="I336" s="28" t="inlineStr">
@@ -19038,7 +19038,7 @@
       </c>
       <c r="H337" s="30" t="inlineStr">
         <is>
-          <t>Workbook.png</t>
+          <t>workbook.png</t>
         </is>
       </c>
       <c r="I337" s="30" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H338" s="28" t="inlineStr">
         <is>
-          <t>Stapler.png</t>
+          <t>stapler.png</t>
         </is>
       </c>
       <c r="I338" s="28" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="H339" s="30" t="inlineStr">
         <is>
-          <t>Marker.png</t>
+          <t>marker.png</t>
         </is>
       </c>
       <c r="I339" s="30" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="H340" s="28" t="inlineStr">
         <is>
-          <t>Highlighter.png</t>
+          <t>highlighter.png</t>
         </is>
       </c>
       <c r="I340" s="28" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="H341" s="30" t="inlineStr">
         <is>
-          <t>Whiteboard.png</t>
+          <t>whiteboard.png</t>
         </is>
       </c>
       <c r="I341" s="30" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="H342" s="28" t="inlineStr">
         <is>
-          <t>Locker.png</t>
+          <t>locker.png</t>
         </is>
       </c>
       <c r="I342" s="28" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="H343" s="30" t="inlineStr">
         <is>
-          <t>Sharpener.png</t>
+          <t>sharpener.png</t>
         </is>
       </c>
       <c r="I343" s="30" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="H344" s="28" t="inlineStr">
         <is>
-          <t>Calculator.png</t>
+          <t>calculator.png</t>
         </is>
       </c>
       <c r="I344" s="28" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="H345" s="30" t="inlineStr">
         <is>
-          <t>Bell.png</t>
+          <t>bell.png</t>
         </is>
       </c>
       <c r="I345" s="30" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="H346" s="28" t="inlineStr">
         <is>
-          <t>Chart.png</t>
+          <t>chart.png</t>
         </is>
       </c>
       <c r="I346" s="28" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="H347" s="30" t="inlineStr">
         <is>
-          <t>Model.png</t>
+          <t>model.png</t>
         </is>
       </c>
       <c r="I347" s="30" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="H348" s="28" t="inlineStr">
         <is>
-          <t>Timetable.png</t>
+          <t>timetable.png</t>
         </is>
       </c>
       <c r="I348" s="28" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="H349" s="30" t="inlineStr">
         <is>
-          <t>Clock.png</t>
+          <t>clock.png</t>
         </is>
       </c>
       <c r="I349" s="30" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="H350" s="28" t="inlineStr">
         <is>
-          <t>Home.png</t>
+          <t>home.png</t>
         </is>
       </c>
       <c r="I350" s="28" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="H351" s="30" t="inlineStr">
         <is>
-          <t>House.png</t>
+          <t>house.png</t>
         </is>
       </c>
       <c r="I351" s="30" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="H352" s="28" t="inlineStr">
         <is>
-          <t>Door.png</t>
+          <t>door.png</t>
         </is>
       </c>
       <c r="I352" s="28" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="H353" s="30" t="inlineStr">
         <is>
-          <t>Window.png</t>
+          <t>window.png</t>
         </is>
       </c>
       <c r="I353" s="30" t="inlineStr">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="H354" s="28" t="inlineStr">
         <is>
-          <t>Room.png</t>
+          <t>room.png</t>
         </is>
       </c>
       <c r="I354" s="28" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="H355" s="30" t="inlineStr">
         <is>
-          <t>Bed.png</t>
+          <t>bed.png</t>
         </is>
       </c>
       <c r="I355" s="30" t="inlineStr">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="H356" s="28" t="inlineStr">
         <is>
-          <t>Table.png</t>
+          <t>table.png</t>
         </is>
       </c>
       <c r="I356" s="28" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="H357" s="30" t="inlineStr">
         <is>
-          <t>Cup.png</t>
+          <t>cup.png</t>
         </is>
       </c>
       <c r="I357" s="30" t="inlineStr">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="H358" s="28" t="inlineStr">
         <is>
-          <t>Spoon.png</t>
+          <t>spoon.png</t>
         </is>
       </c>
       <c r="I358" s="28" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="H359" s="30" t="inlineStr">
         <is>
-          <t>Fork.png</t>
+          <t>fork.png</t>
         </is>
       </c>
       <c r="I359" s="30" t="inlineStr">
@@ -20303,7 +20303,7 @@
       </c>
       <c r="H360" s="28" t="inlineStr">
         <is>
-          <t>Plate.png</t>
+          <t>plate.png</t>
         </is>
       </c>
       <c r="I360" s="28" t="inlineStr">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="H361" s="30" t="inlineStr">
         <is>
-          <t>Towel.png</t>
+          <t>towel.png</t>
         </is>
       </c>
       <c r="I361" s="30" t="inlineStr">
@@ -20413,7 +20413,7 @@
       </c>
       <c r="H362" s="28" t="inlineStr">
         <is>
-          <t>Soap.png</t>
+          <t>soap.png</t>
         </is>
       </c>
       <c r="I362" s="28" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="H363" s="30" t="inlineStr">
         <is>
-          <t>Key.png</t>
+          <t>key.png</t>
         </is>
       </c>
       <c r="I363" s="30" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="H364" s="28" t="inlineStr">
         <is>
-          <t>Phone.png</t>
+          <t>phone.png</t>
         </is>
       </c>
       <c r="I364" s="28" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="H365" s="30" t="inlineStr">
         <is>
-          <t>Television.png</t>
+          <t>television.png</t>
         </is>
       </c>
       <c r="I365" s="30" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="H366" s="28" t="inlineStr">
         <is>
-          <t>Toy.png</t>
+          <t>toy.png</t>
         </is>
       </c>
       <c r="I366" s="28" t="inlineStr">
@@ -20688,7 +20688,7 @@
       </c>
       <c r="H367" s="30" t="inlineStr">
         <is>
-          <t>Doll.png</t>
+          <t>doll.png</t>
         </is>
       </c>
       <c r="I367" s="30" t="inlineStr">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="H368" s="28" t="inlineStr">
         <is>
-          <t>Umbrella.png</t>
+          <t>umbrella.png</t>
         </is>
       </c>
       <c r="I368" s="28" t="inlineStr">
@@ -20798,7 +20798,7 @@
       </c>
       <c r="H369" s="30" t="inlineStr">
         <is>
-          <t>Watch.png</t>
+          <t>watch.png</t>
         </is>
       </c>
       <c r="I369" s="30" t="inlineStr">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="H370" s="28" t="inlineStr">
         <is>
-          <t>Calendar.png</t>
+          <t>calendar.png</t>
         </is>
       </c>
       <c r="I370" s="28" t="inlineStr">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="H371" s="30" t="inlineStr">
         <is>
-          <t>Map.png</t>
+          <t>map.png</t>
         </is>
       </c>
       <c r="I371" s="30" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="H372" s="28" t="inlineStr">
         <is>
-          <t>Box.png</t>
+          <t>box.png</t>
         </is>
       </c>
       <c r="I372" s="28" t="inlineStr">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="H373" s="30" t="inlineStr">
         <is>
-          <t>Radio.png</t>
+          <t>radio.png</t>
         </is>
       </c>
       <c r="I373" s="30" t="inlineStr">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="H374" s="28" t="inlineStr">
         <is>
-          <t>Camera.png</t>
+          <t>camera.png</t>
         </is>
       </c>
       <c r="I374" s="28" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="H375" s="30" t="inlineStr">
         <is>
-          <t>Mirror.png</t>
+          <t>mirror.png</t>
         </is>
       </c>
       <c r="I375" s="30" t="inlineStr">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="H376" s="28" t="inlineStr">
         <is>
-          <t>Glass.png</t>
+          <t>glass.png</t>
         </is>
       </c>
       <c r="I376" s="28" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="H377" s="30" t="inlineStr">
         <is>
-          <t>Bowl.png</t>
+          <t>bowl.png</t>
         </is>
       </c>
       <c r="I377" s="30" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H378" s="28" t="inlineStr">
         <is>
-          <t>Kitchen.png</t>
+          <t>kitchen.png</t>
         </is>
       </c>
       <c r="I378" s="28" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="H379" s="30" t="inlineStr">
         <is>
-          <t>Gift.png</t>
+          <t>gift.png</t>
         </is>
       </c>
       <c r="I379" s="30" t="inlineStr">
@@ -21403,7 +21403,7 @@
       </c>
       <c r="H380" s="28" t="inlineStr">
         <is>
-          <t>Present.png</t>
+          <t>present.png</t>
         </is>
       </c>
       <c r="I380" s="28" t="inlineStr">
@@ -21458,7 +21458,7 @@
       </c>
       <c r="H381" s="30" t="inlineStr">
         <is>
-          <t>Basket.png</t>
+          <t>basket.png</t>
         </is>
       </c>
       <c r="I381" s="30" t="inlineStr">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="H382" s="28" t="inlineStr">
         <is>
-          <t>Letter.png</t>
+          <t>letter.png</t>
         </is>
       </c>
       <c r="I382" s="28" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="H383" s="30" t="inlineStr">
         <is>
-          <t>Email.png</t>
+          <t>email.png</t>
         </is>
       </c>
       <c r="I383" s="30" t="inlineStr">
@@ -21623,7 +21623,7 @@
       </c>
       <c r="H384" s="28" t="inlineStr">
         <is>
-          <t>Message.png</t>
+          <t>message.png</t>
         </is>
       </c>
       <c r="I384" s="28" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="H385" s="30" t="inlineStr">
         <is>
-          <t>News.png</t>
+          <t>news.png</t>
         </is>
       </c>
       <c r="I385" s="30" t="inlineStr">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="H386" s="28" t="inlineStr">
         <is>
-          <t>Story.png</t>
+          <t>story.png</t>
         </is>
       </c>
       <c r="I386" s="28" t="inlineStr">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="H387" s="30" t="inlineStr">
         <is>
-          <t>Novel.png</t>
+          <t>novel.png</t>
         </is>
       </c>
       <c r="I387" s="30" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="H388" s="28" t="inlineStr">
         <is>
-          <t>Poem.png</t>
+          <t>poem.png</t>
         </is>
       </c>
       <c r="I388" s="28" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="H389" s="30" t="inlineStr">
         <is>
-          <t>Picture.png</t>
+          <t>picture.png</t>
         </is>
       </c>
       <c r="I389" s="30" t="inlineStr">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="H390" s="28" t="inlineStr">
         <is>
-          <t>Photo.png</t>
+          <t>photo.png</t>
         </is>
       </c>
       <c r="I390" s="28" t="inlineStr">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="H391" s="30" t="inlineStr">
         <is>
-          <t>Film.png</t>
+          <t>film.png</t>
         </is>
       </c>
       <c r="I391" s="30" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="H392" s="28" t="inlineStr">
         <is>
-          <t>Yard.png</t>
+          <t>yard.png</t>
         </is>
       </c>
       <c r="I392" s="28" t="inlineStr">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="H393" s="30" t="inlineStr">
         <is>
-          <t>Antenna.png</t>
+          <t>antenna.png</t>
         </is>
       </c>
       <c r="I393" s="30" t="inlineStr">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="H394" s="28" t="inlineStr">
         <is>
-          <t>Arrow.png</t>
+          <t>arrow.png</t>
         </is>
       </c>
       <c r="I394" s="28" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="H395" s="30" t="inlineStr">
         <is>
-          <t>Axe.png</t>
+          <t>axe.png</t>
         </is>
       </c>
       <c r="I395" s="30" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="H396" s="28" t="inlineStr">
         <is>
-          <t>Balcony.png</t>
+          <t>balcony.png</t>
         </is>
       </c>
       <c r="I396" s="28" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="H397" s="30" t="inlineStr">
         <is>
-          <t>Balloon.png</t>
+          <t>balloon.png</t>
         </is>
       </c>
       <c r="I397" s="30" t="inlineStr">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="H398" s="28" t="inlineStr">
         <is>
-          <t>Bandage.png</t>
+          <t>bandage.png</t>
         </is>
       </c>
       <c r="I398" s="28" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H399" s="30" t="inlineStr">
         <is>
-          <t>Barrel.png</t>
+          <t>barrel.png</t>
         </is>
       </c>
       <c r="I399" s="30" t="inlineStr">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="H400" s="28" t="inlineStr">
         <is>
-          <t>Basement.png</t>
+          <t>basement.png</t>
         </is>
       </c>
       <c r="I400" s="28" t="inlineStr">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="H401" s="30" t="inlineStr">
         <is>
-          <t>Battery.png</t>
+          <t>battery.png</t>
         </is>
       </c>
       <c r="I401" s="30" t="inlineStr">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="H402" s="28" t="inlineStr">
         <is>
-          <t>Bench.png</t>
+          <t>bench.png</t>
         </is>
       </c>
       <c r="I402" s="28" t="inlineStr">
@@ -22668,7 +22668,7 @@
       </c>
       <c r="H403" s="30" t="inlineStr">
         <is>
-          <t>Bin.png</t>
+          <t>bin.png</t>
         </is>
       </c>
       <c r="I403" s="30" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="H404" s="28" t="inlineStr">
         <is>
-          <t>Bottle.png</t>
+          <t>bottle.png</t>
         </is>
       </c>
       <c r="I404" s="28" t="inlineStr">
@@ -22778,7 +22778,7 @@
       </c>
       <c r="H405" s="30" t="inlineStr">
         <is>
-          <t>Brick.png</t>
+          <t>brick.png</t>
         </is>
       </c>
       <c r="I405" s="30" t="inlineStr">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="H406" s="28" t="inlineStr">
         <is>
-          <t>Broom.png</t>
+          <t>broom.png</t>
         </is>
       </c>
       <c r="I406" s="28" t="inlineStr">
@@ -22888,7 +22888,7 @@
       </c>
       <c r="H407" s="30" t="inlineStr">
         <is>
-          <t>Bucket.png</t>
+          <t>bucket.png</t>
         </is>
       </c>
       <c r="I407" s="30" t="inlineStr">
@@ -22943,7 +22943,7 @@
       </c>
       <c r="H408" s="28" t="inlineStr">
         <is>
-          <t>Bulb.png</t>
+          <t>bulb.png</t>
         </is>
       </c>
       <c r="I408" s="28" t="inlineStr">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="H409" s="30" t="inlineStr">
         <is>
-          <t>Cable.png</t>
+          <t>cable.png</t>
         </is>
       </c>
       <c r="I409" s="30" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="H410" s="28" t="inlineStr">
         <is>
-          <t>Cage.png</t>
+          <t>cage.png</t>
         </is>
       </c>
       <c r="I410" s="28" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="H411" s="30" t="inlineStr">
         <is>
-          <t>Candle.png</t>
+          <t>candle.png</t>
         </is>
       </c>
       <c r="I411" s="30" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="H412" s="28" t="inlineStr">
         <is>
-          <t>Chimney.png</t>
+          <t>chimney.png</t>
         </is>
       </c>
       <c r="I412" s="28" t="inlineStr">
@@ -23218,7 +23218,7 @@
       </c>
       <c r="H413" s="30" t="inlineStr">
         <is>
-          <t>Compass.png</t>
+          <t>compass.png</t>
         </is>
       </c>
       <c r="I413" s="30" t="inlineStr">
@@ -23273,7 +23273,7 @@
       </c>
       <c r="H414" s="28" t="inlineStr">
         <is>
-          <t>Cottage.png</t>
+          <t>cottage.png</t>
         </is>
       </c>
       <c r="I414" s="28" t="inlineStr">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="H415" s="30" t="inlineStr">
         <is>
-          <t>Curtain.png</t>
+          <t>curtain.png</t>
         </is>
       </c>
       <c r="I415" s="30" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="H416" s="28" t="inlineStr">
         <is>
-          <t>Cushion.png</t>
+          <t>cushion.png</t>
         </is>
       </c>
       <c r="I416" s="28" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="H417" s="30" t="inlineStr">
         <is>
-          <t>Drawer.png</t>
+          <t>drawer.png</t>
         </is>
       </c>
       <c r="I417" s="30" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="H418" s="28" t="inlineStr">
         <is>
-          <t>Drill.png</t>
+          <t>drill.png</t>
         </is>
       </c>
       <c r="I418" s="28" t="inlineStr">
@@ -23548,7 +23548,7 @@
       </c>
       <c r="H419" s="30" t="inlineStr">
         <is>
-          <t>Envelope.png</t>
+          <t>envelope.png</t>
         </is>
       </c>
       <c r="I419" s="30" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="H420" s="28" t="inlineStr">
         <is>
-          <t>Fence.png</t>
+          <t>fence.png</t>
         </is>
       </c>
       <c r="I420" s="28" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="H421" s="30" t="inlineStr">
         <is>
-          <t>Flashlight.png</t>
+          <t>flashlight.png</t>
         </is>
       </c>
       <c r="I421" s="30" t="inlineStr">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="H422" s="28" t="inlineStr">
         <is>
-          <t>Frame.png</t>
+          <t>frame.png</t>
         </is>
       </c>
       <c r="I422" s="28" t="inlineStr">
@@ -23768,7 +23768,7 @@
       </c>
       <c r="H423" s="30" t="inlineStr">
         <is>
-          <t>Garbage.png</t>
+          <t>garbage.png</t>
         </is>
       </c>
       <c r="I423" s="30" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="H424" s="28" t="inlineStr">
         <is>
-          <t>Hammer.png</t>
+          <t>hammer.png</t>
         </is>
       </c>
       <c r="I424" s="28" t="inlineStr">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="H425" s="30" t="inlineStr">
         <is>
-          <t>Kettle.png</t>
+          <t>kettle.png</t>
         </is>
       </c>
       <c r="I425" s="30" t="inlineStr">
@@ -23933,7 +23933,7 @@
       </c>
       <c r="H426" s="28" t="inlineStr">
         <is>
-          <t>Ladder.png</t>
+          <t>ladder.png</t>
         </is>
       </c>
       <c r="I426" s="28" t="inlineStr">
@@ -23988,7 +23988,7 @@
       </c>
       <c r="H427" s="30" t="inlineStr">
         <is>
-          <t>Lantern.png</t>
+          <t>lantern.png</t>
         </is>
       </c>
       <c r="I427" s="30" t="inlineStr">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="H428" s="28" t="inlineStr">
         <is>
-          <t>Lock.png</t>
+          <t>lock.png</t>
         </is>
       </c>
       <c r="I428" s="28" t="inlineStr">
@@ -24098,7 +24098,7 @@
       </c>
       <c r="H429" s="30" t="inlineStr">
         <is>
-          <t>Mailbox.png</t>
+          <t>mailbox.png</t>
         </is>
       </c>
       <c r="I429" s="30" t="inlineStr">
@@ -24153,7 +24153,7 @@
       </c>
       <c r="H430" s="28" t="inlineStr">
         <is>
-          <t>Needle.png</t>
+          <t>needle.png</t>
         </is>
       </c>
       <c r="I430" s="28" t="inlineStr">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="H431" s="30" t="inlineStr">
         <is>
-          <t>Attic.png</t>
+          <t>attic.png</t>
         </is>
       </c>
       <c r="I431" s="30" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="H432" s="28" t="inlineStr">
         <is>
-          <t>Garage.png</t>
+          <t>garage.png</t>
         </is>
       </c>
       <c r="I432" s="28" t="inlineStr">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="H433" s="30" t="inlineStr">
         <is>
-          <t>Fireplace.png</t>
+          <t>fireplace.png</t>
         </is>
       </c>
       <c r="I433" s="30" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H434" s="28" t="inlineStr">
         <is>
-          <t>Faucet.png</t>
+          <t>faucet.png</t>
         </is>
       </c>
       <c r="I434" s="28" t="inlineStr">
@@ -24428,7 +24428,7 @@
       </c>
       <c r="H435" s="30" t="inlineStr">
         <is>
-          <t>Bathtub.png</t>
+          <t>bathtub.png</t>
         </is>
       </c>
       <c r="I435" s="30" t="inlineStr">
@@ -24483,7 +24483,7 @@
       </c>
       <c r="H436" s="28" t="inlineStr">
         <is>
-          <t>Shower.png</t>
+          <t>shower.png</t>
         </is>
       </c>
       <c r="I436" s="28" t="inlineStr">
@@ -24538,7 +24538,7 @@
       </c>
       <c r="H437" s="30" t="inlineStr">
         <is>
-          <t>Toilet.png</t>
+          <t>toilet.png</t>
         </is>
       </c>
       <c r="I437" s="30" t="inlineStr">
@@ -24593,7 +24593,7 @@
       </c>
       <c r="H438" s="28" t="inlineStr">
         <is>
-          <t>Closet.png</t>
+          <t>closet.png</t>
         </is>
       </c>
       <c r="I438" s="28" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H439" s="30" t="inlineStr">
         <is>
-          <t>Mattress.png</t>
+          <t>mattress.png</t>
         </is>
       </c>
       <c r="I439" s="30" t="inlineStr">
@@ -24703,7 +24703,7 @@
       </c>
       <c r="H440" s="28" t="inlineStr">
         <is>
-          <t>Quilt.png</t>
+          <t>quilt.png</t>
         </is>
       </c>
       <c r="I440" s="28" t="inlineStr">
@@ -24758,7 +24758,7 @@
       </c>
       <c r="H441" s="30" t="inlineStr">
         <is>
-          <t>Vacuum.png</t>
+          <t>vacuum.png</t>
         </is>
       </c>
       <c r="I441" s="30" t="inlineStr">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="H442" s="28" t="inlineStr">
         <is>
-          <t>Stove.png</t>
+          <t>stove.png</t>
         </is>
       </c>
       <c r="I442" s="28" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="H443" s="30" t="inlineStr">
         <is>
-          <t>Oven.png</t>
+          <t>oven.png</t>
         </is>
       </c>
       <c r="I443" s="30" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="H444" s="28" t="inlineStr">
         <is>
-          <t>Microwave.png</t>
+          <t>microwave.png</t>
         </is>
       </c>
       <c r="I444" s="28" t="inlineStr">
@@ -24978,7 +24978,7 @@
       </c>
       <c r="H445" s="30" t="inlineStr">
         <is>
-          <t>Freezer.png</t>
+          <t>freezer.png</t>
         </is>
       </c>
       <c r="I445" s="30" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="H446" s="28" t="inlineStr">
         <is>
-          <t>Toaster.png</t>
+          <t>toaster.png</t>
         </is>
       </c>
       <c r="I446" s="28" t="inlineStr">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="H447" s="30" t="inlineStr">
         <is>
-          <t>Teapot.png</t>
+          <t>teapot.png</t>
         </is>
       </c>
       <c r="I447" s="30" t="inlineStr">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="H448" s="28" t="inlineStr">
         <is>
-          <t>Mug.png</t>
+          <t>mug.png</t>
         </is>
       </c>
       <c r="I448" s="28" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="H449" s="30" t="inlineStr">
         <is>
-          <t>Chopsticks.png</t>
+          <t>chopsticks.png</t>
         </is>
       </c>
       <c r="I449" s="30" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="H450" s="28" t="inlineStr">
         <is>
-          <t>Thermos.png</t>
+          <t>thermos.png</t>
         </is>
       </c>
       <c r="I450" s="28" t="inlineStr">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="H451" s="30" t="inlineStr">
         <is>
-          <t>Speaker.png</t>
+          <t>speaker.png</t>
         </is>
       </c>
       <c r="I451" s="30" t="inlineStr">
@@ -25363,7 +25363,7 @@
       </c>
       <c r="H452" s="28" t="inlineStr">
         <is>
-          <t>Headphone.png</t>
+          <t>headphone.png</t>
         </is>
       </c>
       <c r="I452" s="28" t="inlineStr">
@@ -25418,7 +25418,7 @@
       </c>
       <c r="H453" s="30" t="inlineStr">
         <is>
-          <t>Park.png</t>
+          <t>park.png</t>
         </is>
       </c>
       <c r="I453" s="30" t="inlineStr">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="H454" s="28" t="inlineStr">
         <is>
-          <t>Zoo.png</t>
+          <t>zoo.png</t>
         </is>
       </c>
       <c r="I454" s="28" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="H455" s="30" t="inlineStr">
         <is>
-          <t>Hospital.png</t>
+          <t>hospital.png</t>
         </is>
       </c>
       <c r="I455" s="30" t="inlineStr">
@@ -25583,7 +25583,7 @@
       </c>
       <c r="H456" s="28" t="inlineStr">
         <is>
-          <t>Store.png</t>
+          <t>store.png</t>
         </is>
       </c>
       <c r="I456" s="28" t="inlineStr">
@@ -25638,7 +25638,7 @@
       </c>
       <c r="H457" s="30" t="inlineStr">
         <is>
-          <t>Library.png</t>
+          <t>library.png</t>
         </is>
       </c>
       <c r="I457" s="30" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="H458" s="28" t="inlineStr">
         <is>
-          <t>Bank.png</t>
+          <t>bank.png</t>
         </is>
       </c>
       <c r="I458" s="28" t="inlineStr">
@@ -25748,7 +25748,7 @@
       </c>
       <c r="H459" s="30" t="inlineStr">
         <is>
-          <t>Station.png</t>
+          <t>station.png</t>
         </is>
       </c>
       <c r="I459" s="30" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H460" s="28" t="inlineStr">
         <is>
-          <t>Airport.png</t>
+          <t>airport.png</t>
         </is>
       </c>
       <c r="I460" s="28" t="inlineStr">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="H461" s="30" t="inlineStr">
         <is>
-          <t>Hotel.png</t>
+          <t>hotel.png</t>
         </is>
       </c>
       <c r="I461" s="30" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="H462" s="28" t="inlineStr">
         <is>
-          <t>Market.png</t>
+          <t>market.png</t>
         </is>
       </c>
       <c r="I462" s="28" t="inlineStr">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="H463" s="30" t="inlineStr">
         <is>
-          <t>Shop.png</t>
+          <t>shop.png</t>
         </is>
       </c>
       <c r="I463" s="30" t="inlineStr">
@@ -26023,7 +26023,7 @@
       </c>
       <c r="H464" s="28" t="inlineStr">
         <is>
-          <t>Stage.png</t>
+          <t>stage.png</t>
         </is>
       </c>
       <c r="I464" s="28" t="inlineStr">
@@ -26078,7 +26078,7 @@
       </c>
       <c r="H465" s="30" t="inlineStr">
         <is>
-          <t>Farm.png</t>
+          <t>farm.png</t>
         </is>
       </c>
       <c r="I465" s="30" t="inlineStr">
@@ -26133,7 +26133,7 @@
       </c>
       <c r="H466" s="28" t="inlineStr">
         <is>
-          <t>Arch.png</t>
+          <t>arch.png</t>
         </is>
       </c>
       <c r="I466" s="28" t="inlineStr">
@@ -26188,7 +26188,7 @@
       </c>
       <c r="H467" s="30" t="inlineStr">
         <is>
-          <t>Barn.png</t>
+          <t>barn.png</t>
         </is>
       </c>
       <c r="I467" s="30" t="inlineStr">
@@ -26243,7 +26243,7 @@
       </c>
       <c r="H468" s="28" t="inlineStr">
         <is>
-          <t>Castle.png</t>
+          <t>castle.png</t>
         </is>
       </c>
       <c r="I468" s="28" t="inlineStr">
@@ -26298,7 +26298,7 @@
       </c>
       <c r="H469" s="30" t="inlineStr">
         <is>
-          <t>Flagpole.png</t>
+          <t>flagpole.png</t>
         </is>
       </c>
       <c r="I469" s="30" t="inlineStr">
@@ -26353,7 +26353,7 @@
       </c>
       <c r="H470" s="28" t="inlineStr">
         <is>
-          <t>Fountain.png</t>
+          <t>fountain.png</t>
         </is>
       </c>
       <c r="I470" s="28" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="H471" s="30" t="inlineStr">
         <is>
-          <t>Graveyard.png</t>
+          <t>graveyard.png</t>
         </is>
       </c>
       <c r="I471" s="30" t="inlineStr">
@@ -26463,7 +26463,7 @@
       </c>
       <c r="H472" s="28" t="inlineStr">
         <is>
-          <t>Museum.png</t>
+          <t>museum.png</t>
         </is>
       </c>
       <c r="I472" s="28" t="inlineStr">
@@ -26518,7 +26518,7 @@
       </c>
       <c r="H473" s="30" t="inlineStr">
         <is>
-          <t>Church.png</t>
+          <t>church.png</t>
         </is>
       </c>
       <c r="I473" s="30" t="inlineStr">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="H474" s="28" t="inlineStr">
         <is>
-          <t>Temple.png</t>
+          <t>temple.png</t>
         </is>
       </c>
       <c r="I474" s="28" t="inlineStr">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="H475" s="30" t="inlineStr">
         <is>
-          <t>Palace.png</t>
+          <t>palace.png</t>
         </is>
       </c>
       <c r="I475" s="30" t="inlineStr">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="H476" s="28" t="inlineStr">
         <is>
-          <t>Theater.png</t>
+          <t>theater.png</t>
         </is>
       </c>
       <c r="I476" s="28" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="H477" s="30" t="inlineStr">
         <is>
-          <t>Cinema.png</t>
+          <t>cinema.png</t>
         </is>
       </c>
       <c r="I477" s="30" t="inlineStr">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="H478" s="28" t="inlineStr">
         <is>
-          <t>Stadium.png</t>
+          <t>stadium.png</t>
         </is>
       </c>
       <c r="I478" s="28" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H479" s="30" t="inlineStr">
         <is>
-          <t>Mall.png</t>
+          <t>mall.png</t>
         </is>
       </c>
       <c r="I479" s="30" t="inlineStr">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="H480" s="28" t="inlineStr">
         <is>
-          <t>Supermarket.png</t>
+          <t>supermarket.png</t>
         </is>
       </c>
       <c r="I480" s="28" t="inlineStr">
@@ -26958,7 +26958,7 @@
       </c>
       <c r="H481" s="30" t="inlineStr">
         <is>
-          <t>Bakery.png</t>
+          <t>bakery.png</t>
         </is>
       </c>
       <c r="I481" s="30" t="inlineStr">
@@ -27013,7 +27013,7 @@
       </c>
       <c r="H482" s="28" t="inlineStr">
         <is>
-          <t>Restaurant.png</t>
+          <t>restaurant.png</t>
         </is>
       </c>
       <c r="I482" s="28" t="inlineStr">
@@ -27068,7 +27068,7 @@
       </c>
       <c r="H483" s="30" t="inlineStr">
         <is>
-          <t>Cafe.png</t>
+          <t>cafe.png</t>
         </is>
       </c>
       <c r="I483" s="30" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="H484" s="28" t="inlineStr">
         <is>
-          <t>Factory.png</t>
+          <t>factory.png</t>
         </is>
       </c>
       <c r="I484" s="28" t="inlineStr">
@@ -27178,7 +27178,7 @@
       </c>
       <c r="H485" s="30" t="inlineStr">
         <is>
-          <t>Office.png</t>
+          <t>office.png</t>
         </is>
       </c>
       <c r="I485" s="30" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="H486" s="28" t="inlineStr">
         <is>
-          <t>Village.png</t>
+          <t>village.png</t>
         </is>
       </c>
       <c r="I486" s="28" t="inlineStr">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="H487" s="30" t="inlineStr">
         <is>
-          <t>Car.png</t>
+          <t>car.png</t>
         </is>
       </c>
       <c r="I487" s="30" t="inlineStr">
@@ -27343,7 +27343,7 @@
       </c>
       <c r="H488" s="28" t="inlineStr">
         <is>
-          <t>Bus.png</t>
+          <t>bus.png</t>
         </is>
       </c>
       <c r="I488" s="28" t="inlineStr">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="H489" s="30" t="inlineStr">
         <is>
-          <t>Train.png</t>
+          <t>train.png</t>
         </is>
       </c>
       <c r="I489" s="30" t="inlineStr">
@@ -27453,7 +27453,7 @@
       </c>
       <c r="H490" s="28" t="inlineStr">
         <is>
-          <t>Subway.png</t>
+          <t>subway.png</t>
         </is>
       </c>
       <c r="I490" s="28" t="inlineStr">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="H491" s="30" t="inlineStr">
         <is>
-          <t>Airplane.png</t>
+          <t>airplane.png</t>
         </is>
       </c>
       <c r="I491" s="30" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="H492" s="28" t="inlineStr">
         <is>
-          <t>Ship.png</t>
+          <t>ship.png</t>
         </is>
       </c>
       <c r="I492" s="28" t="inlineStr">
@@ -27618,7 +27618,7 @@
       </c>
       <c r="H493" s="30" t="inlineStr">
         <is>
-          <t>Boat.png</t>
+          <t>boat.png</t>
         </is>
       </c>
       <c r="I493" s="30" t="inlineStr">
@@ -27673,7 +27673,7 @@
       </c>
       <c r="H494" s="28" t="inlineStr">
         <is>
-          <t>Bicycle.png</t>
+          <t>bicycle.png</t>
         </is>
       </c>
       <c r="I494" s="28" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="H495" s="30" t="inlineStr">
         <is>
-          <t>Taxi.png</t>
+          <t>taxi.png</t>
         </is>
       </c>
       <c r="I495" s="30" t="inlineStr">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="H496" s="28" t="inlineStr">
         <is>
-          <t>Truck.png</t>
+          <t>truck.png</t>
         </is>
       </c>
       <c r="I496" s="28" t="inlineStr">
@@ -27838,7 +27838,7 @@
       </c>
       <c r="H497" s="30" t="inlineStr">
         <is>
-          <t>Motorcycle.png</t>
+          <t>motorcycle.png</t>
         </is>
       </c>
       <c r="I497" s="30" t="inlineStr">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="H498" s="28" t="inlineStr">
         <is>
-          <t>Road.png</t>
+          <t>road.png</t>
         </is>
       </c>
       <c r="I498" s="28" t="inlineStr">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="H499" s="30" t="inlineStr">
         <is>
-          <t>Bike.png</t>
+          <t>bike.png</t>
         </is>
       </c>
       <c r="I499" s="30" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="H500" s="28" t="inlineStr">
         <is>
-          <t>Street.png</t>
+          <t>street.png</t>
         </is>
       </c>
       <c r="I500" s="28" t="inlineStr">
@@ -28058,7 +28058,7 @@
       </c>
       <c r="H501" s="30" t="inlineStr">
         <is>
-          <t>Bridge.png</t>
+          <t>bridge.png</t>
         </is>
       </c>
       <c r="I501" s="30" t="inlineStr">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="H502" s="28" t="inlineStr">
         <is>
-          <t>Trip.png</t>
+          <t>trip.png</t>
         </is>
       </c>
       <c r="I502" s="28" t="inlineStr">
@@ -28168,7 +28168,7 @@
       </c>
       <c r="H503" s="30" t="inlineStr">
         <is>
-          <t>Avenue.png</t>
+          <t>avenue.png</t>
         </is>
       </c>
       <c r="I503" s="30" t="inlineStr">
@@ -28223,7 +28223,7 @@
       </c>
       <c r="H504" s="28" t="inlineStr">
         <is>
-          <t>Engine.png</t>
+          <t>engine.png</t>
         </is>
       </c>
       <c r="I504" s="28" t="inlineStr">
@@ -28278,7 +28278,7 @@
       </c>
       <c r="H505" s="30" t="inlineStr">
         <is>
-          <t>Highway.png</t>
+          <t>highway.png</t>
         </is>
       </c>
       <c r="I505" s="30" t="inlineStr">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="H506" s="28" t="inlineStr">
         <is>
-          <t>Van.png</t>
+          <t>van.png</t>
         </is>
       </c>
       <c r="I506" s="28" t="inlineStr">
@@ -28388,7 +28388,7 @@
       </c>
       <c r="H507" s="30" t="inlineStr">
         <is>
-          <t>Scooter.png</t>
+          <t>scooter.png</t>
         </is>
       </c>
       <c r="I507" s="30" t="inlineStr">
@@ -28443,7 +28443,7 @@
       </c>
       <c r="H508" s="28" t="inlineStr">
         <is>
-          <t>Helicopter.png</t>
+          <t>helicopter.png</t>
         </is>
       </c>
       <c r="I508" s="28" t="inlineStr">
@@ -28498,7 +28498,7 @@
       </c>
       <c r="H509" s="30" t="inlineStr">
         <is>
-          <t>Ferry.png</t>
+          <t>ferry.png</t>
         </is>
       </c>
       <c r="I509" s="30" t="inlineStr">
@@ -28553,7 +28553,7 @@
       </c>
       <c r="H510" s="28" t="inlineStr">
         <is>
-          <t>Sailboat.png</t>
+          <t>sailboat.png</t>
         </is>
       </c>
       <c r="I510" s="28" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="H511" s="30" t="inlineStr">
         <is>
-          <t>Tractor.png</t>
+          <t>tractor.png</t>
         </is>
       </c>
       <c r="I511" s="30" t="inlineStr">
@@ -28663,7 +28663,7 @@
       </c>
       <c r="H512" s="28" t="inlineStr">
         <is>
-          <t>Ambulance.png</t>
+          <t>ambulance.png</t>
         </is>
       </c>
       <c r="I512" s="28" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="H513" s="30" t="inlineStr">
         <is>
-          <t>Wagon.png</t>
+          <t>wagon.png</t>
         </is>
       </c>
       <c r="I513" s="30" t="inlineStr">
@@ -28773,7 +28773,7 @@
       </c>
       <c r="H514" s="28" t="inlineStr">
         <is>
-          <t>Stroller.png</t>
+          <t>stroller.png</t>
         </is>
       </c>
       <c r="I514" s="28" t="inlineStr">
@@ -28828,7 +28828,7 @@
       </c>
       <c r="H515" s="30" t="inlineStr">
         <is>
-          <t>Harbor.png</t>
+          <t>harbor.png</t>
         </is>
       </c>
       <c r="I515" s="30" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="H516" s="28" t="inlineStr">
         <is>
-          <t>Sun.png</t>
+          <t>sun.png</t>
         </is>
       </c>
       <c r="I516" s="28" t="inlineStr">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="H517" s="30" t="inlineStr">
         <is>
-          <t>Moon.png</t>
+          <t>moon.png</t>
         </is>
       </c>
       <c r="I517" s="30" t="inlineStr">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="H518" s="28" t="inlineStr">
         <is>
-          <t>Star.png</t>
+          <t>star.png</t>
         </is>
       </c>
       <c r="I518" s="28" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="H519" s="30" t="inlineStr">
         <is>
-          <t>Sky.png</t>
+          <t>sky.png</t>
         </is>
       </c>
       <c r="I519" s="30" t="inlineStr">
@@ -29103,7 +29103,7 @@
       </c>
       <c r="H520" s="28" t="inlineStr">
         <is>
-          <t>Cloud.png</t>
+          <t>cloud.png</t>
         </is>
       </c>
       <c r="I520" s="28" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H521" s="30" t="inlineStr">
         <is>
-          <t>Rain.png</t>
+          <t>rain.png</t>
         </is>
       </c>
       <c r="I521" s="30" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="H522" s="28" t="inlineStr">
         <is>
-          <t>Snow.png</t>
+          <t>snow.png</t>
         </is>
       </c>
       <c r="I522" s="28" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="H523" s="30" t="inlineStr">
         <is>
-          <t>Wind.png</t>
+          <t>wind.png</t>
         </is>
       </c>
       <c r="I523" s="30" t="inlineStr">
@@ -29323,7 +29323,7 @@
       </c>
       <c r="H524" s="28" t="inlineStr">
         <is>
-          <t>Rainbow.png</t>
+          <t>rainbow.png</t>
         </is>
       </c>
       <c r="I524" s="28" t="inlineStr">
@@ -29378,7 +29378,7 @@
       </c>
       <c r="H525" s="30" t="inlineStr">
         <is>
-          <t>Tree.png</t>
+          <t>tree.png</t>
         </is>
       </c>
       <c r="I525" s="30" t="inlineStr">
@@ -29433,7 +29433,7 @@
       </c>
       <c r="H526" s="28" t="inlineStr">
         <is>
-          <t>Flower.png</t>
+          <t>flower.png</t>
         </is>
       </c>
       <c r="I526" s="28" t="inlineStr">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="H527" s="30" t="inlineStr">
         <is>
-          <t>Grass.png</t>
+          <t>grass.png</t>
         </is>
       </c>
       <c r="I527" s="30" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="H528" s="28" t="inlineStr">
         <is>
-          <t>Leaf.png</t>
+          <t>leaf.png</t>
         </is>
       </c>
       <c r="I528" s="28" t="inlineStr">
@@ -29598,7 +29598,7 @@
       </c>
       <c r="H529" s="30" t="inlineStr">
         <is>
-          <t>Mountain.png</t>
+          <t>mountain.png</t>
         </is>
       </c>
       <c r="I529" s="30" t="inlineStr">
@@ -29653,7 +29653,7 @@
       </c>
       <c r="H530" s="28" t="inlineStr">
         <is>
-          <t>River.png</t>
+          <t>river.png</t>
         </is>
       </c>
       <c r="I530" s="28" t="inlineStr">
@@ -29708,7 +29708,7 @@
       </c>
       <c r="H531" s="30" t="inlineStr">
         <is>
-          <t>Sea.png</t>
+          <t>sea.png</t>
         </is>
       </c>
       <c r="I531" s="30" t="inlineStr">
@@ -29763,7 +29763,7 @@
       </c>
       <c r="H532" s="28" t="inlineStr">
         <is>
-          <t>Beach.png</t>
+          <t>beach.png</t>
         </is>
       </c>
       <c r="I532" s="28" t="inlineStr">
@@ -29818,7 +29818,7 @@
       </c>
       <c r="H533" s="30" t="inlineStr">
         <is>
-          <t>Stone.png</t>
+          <t>stone.png</t>
         </is>
       </c>
       <c r="I533" s="30" t="inlineStr">
@@ -29873,7 +29873,7 @@
       </c>
       <c r="H534" s="28" t="inlineStr">
         <is>
-          <t>Fire.png</t>
+          <t>fire.png</t>
         </is>
       </c>
       <c r="I534" s="28" t="inlineStr">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="H535" s="30" t="inlineStr">
         <is>
-          <t>Sand.png</t>
+          <t>sand.png</t>
         </is>
       </c>
       <c r="I535" s="30" t="inlineStr">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="H536" s="28" t="inlineStr">
         <is>
-          <t>Ice.png</t>
+          <t>ice.png</t>
         </is>
       </c>
       <c r="I536" s="28" t="inlineStr">
@@ -30038,7 +30038,7 @@
       </c>
       <c r="H537" s="30" t="inlineStr">
         <is>
-          <t>Forest.png</t>
+          <t>forest.png</t>
         </is>
       </c>
       <c r="I537" s="30" t="inlineStr">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="H538" s="28" t="inlineStr">
         <is>
-          <t>Ocean.png</t>
+          <t>ocean.png</t>
         </is>
       </c>
       <c r="I538" s="28" t="inlineStr">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="H539" s="30" t="inlineStr">
         <is>
-          <t>Earth.png</t>
+          <t>earth.png</t>
         </is>
       </c>
       <c r="I539" s="30" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="H540" s="28" t="inlineStr">
         <is>
-          <t>Gold.png</t>
+          <t>gold.png</t>
         </is>
       </c>
       <c r="I540" s="28" t="inlineStr">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="H541" s="30" t="inlineStr">
         <is>
-          <t>Silver.png</t>
+          <t>silver.png</t>
         </is>
       </c>
       <c r="I541" s="30" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="H542" s="28" t="inlineStr">
         <is>
-          <t>Iron.png</t>
+          <t>iron.png</t>
         </is>
       </c>
       <c r="I542" s="28" t="inlineStr">
@@ -30368,7 +30368,7 @@
       </c>
       <c r="H543" s="30" t="inlineStr">
         <is>
-          <t>Lake.png</t>
+          <t>lake.png</t>
         </is>
       </c>
       <c r="I543" s="30" t="inlineStr">
@@ -30423,7 +30423,7 @@
       </c>
       <c r="H544" s="28" t="inlineStr">
         <is>
-          <t>Pond.png</t>
+          <t>pond.png</t>
         </is>
       </c>
       <c r="I544" s="28" t="inlineStr">
@@ -30478,7 +30478,7 @@
       </c>
       <c r="H545" s="30" t="inlineStr">
         <is>
-          <t>Hill.png</t>
+          <t>hill.png</t>
         </is>
       </c>
       <c r="I545" s="30" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="H546" s="28" t="inlineStr">
         <is>
-          <t>Field.png</t>
+          <t>field.png</t>
         </is>
       </c>
       <c r="I546" s="28" t="inlineStr">
@@ -30588,7 +30588,7 @@
       </c>
       <c r="H547" s="30" t="inlineStr">
         <is>
-          <t>Island.png</t>
+          <t>island.png</t>
         </is>
       </c>
       <c r="I547" s="30" t="inlineStr">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="H548" s="28" t="inlineStr">
         <is>
-          <t>Air.png</t>
+          <t>air.png</t>
         </is>
       </c>
       <c r="I548" s="28" t="inlineStr">
@@ -30698,7 +30698,7 @@
       </c>
       <c r="H549" s="30" t="inlineStr">
         <is>
-          <t>Smoke.png</t>
+          <t>smoke.png</t>
         </is>
       </c>
       <c r="I549" s="30" t="inlineStr">
@@ -30753,7 +30753,7 @@
       </c>
       <c r="H550" s="28" t="inlineStr">
         <is>
-          <t>Light.png</t>
+          <t>light.png</t>
         </is>
       </c>
       <c r="I550" s="28" t="inlineStr">
@@ -30808,7 +30808,7 @@
       </c>
       <c r="H551" s="30" t="inlineStr">
         <is>
-          <t>Shadow.png</t>
+          <t>shadow.png</t>
         </is>
       </c>
       <c r="I551" s="30" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="H552" s="28" t="inlineStr">
         <is>
-          <t>Sound.png</t>
+          <t>sound.png</t>
         </is>
       </c>
       <c r="I552" s="28" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="H553" s="30" t="inlineStr">
         <is>
-          <t>Jungle.png</t>
+          <t>jungle.png</t>
         </is>
       </c>
       <c r="I553" s="30" t="inlineStr">
@@ -30973,7 +30973,7 @@
       </c>
       <c r="H554" s="28" t="inlineStr">
         <is>
-          <t>Desert.png</t>
+          <t>desert.png</t>
         </is>
       </c>
       <c r="I554" s="28" t="inlineStr">
@@ -31028,7 +31028,7 @@
       </c>
       <c r="H555" s="30" t="inlineStr">
         <is>
-          <t>Bamboo.png</t>
+          <t>bamboo.png</t>
         </is>
       </c>
       <c r="I555" s="30" t="inlineStr">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="H556" s="28" t="inlineStr">
         <is>
-          <t>Branch.png</t>
+          <t>branch.png</t>
         </is>
       </c>
       <c r="I556" s="28" t="inlineStr">
@@ -31138,7 +31138,7 @@
       </c>
       <c r="H557" s="30" t="inlineStr">
         <is>
-          <t>Bush.png</t>
+          <t>bush.png</t>
         </is>
       </c>
       <c r="I557" s="30" t="inlineStr">
@@ -31193,7 +31193,7 @@
       </c>
       <c r="H558" s="28" t="inlineStr">
         <is>
-          <t>Cactus.png</t>
+          <t>cactus.png</t>
         </is>
       </c>
       <c r="I558" s="28" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="H559" s="30" t="inlineStr">
         <is>
-          <t>Canyon.png</t>
+          <t>canyon.png</t>
         </is>
       </c>
       <c r="I559" s="30" t="inlineStr">
@@ -31303,7 +31303,7 @@
       </c>
       <c r="H560" s="28" t="inlineStr">
         <is>
-          <t>Cave.png</t>
+          <t>cave.png</t>
         </is>
       </c>
       <c r="I560" s="28" t="inlineStr">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="H561" s="30" t="inlineStr">
         <is>
-          <t>Cliff.png</t>
+          <t>cliff.png</t>
         </is>
       </c>
       <c r="I561" s="30" t="inlineStr">
@@ -31413,7 +31413,7 @@
       </c>
       <c r="H562" s="28" t="inlineStr">
         <is>
-          <t>Cotton.png</t>
+          <t>cotton.png</t>
         </is>
       </c>
       <c r="I562" s="28" t="inlineStr">
@@ -31468,7 +31468,7 @@
       </c>
       <c r="H563" s="30" t="inlineStr">
         <is>
-          <t>Diamond.png</t>
+          <t>diamond.png</t>
         </is>
       </c>
       <c r="I563" s="30" t="inlineStr">
@@ -31523,7 +31523,7 @@
       </c>
       <c r="H564" s="28" t="inlineStr">
         <is>
-          <t>Jewel.png</t>
+          <t>jewel.png</t>
         </is>
       </c>
       <c r="I564" s="28" t="inlineStr">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="H565" s="30" t="inlineStr">
         <is>
-          <t>Lawn.png</t>
+          <t>lawn.png</t>
         </is>
       </c>
       <c r="I565" s="30" t="inlineStr">
@@ -31633,7 +31633,7 @@
       </c>
       <c r="H566" s="28" t="inlineStr">
         <is>
-          <t>Typhoon.png</t>
+          <t>typhoon.png</t>
         </is>
       </c>
       <c r="I566" s="28" t="inlineStr">
@@ -31688,7 +31688,7 @@
       </c>
       <c r="H567" s="30" t="inlineStr">
         <is>
-          <t>Tornado.png</t>
+          <t>tornado.png</t>
         </is>
       </c>
       <c r="I567" s="30" t="inlineStr">
@@ -31743,7 +31743,7 @@
       </c>
       <c r="H568" s="28" t="inlineStr">
         <is>
-          <t>Hail.png</t>
+          <t>hail.png</t>
         </is>
       </c>
       <c r="I568" s="28" t="inlineStr">
@@ -31798,7 +31798,7 @@
       </c>
       <c r="H569" s="30" t="inlineStr">
         <is>
-          <t>Puddle.png</t>
+          <t>puddle.png</t>
         </is>
       </c>
       <c r="I569" s="30" t="inlineStr">
@@ -31853,7 +31853,7 @@
       </c>
       <c r="H570" s="28" t="inlineStr">
         <is>
-          <t>Icicle.png</t>
+          <t>icicle.png</t>
         </is>
       </c>
       <c r="I570" s="28" t="inlineStr">
@@ -31908,7 +31908,7 @@
       </c>
       <c r="H571" s="30" t="inlineStr">
         <is>
-          <t>Sunrise.png</t>
+          <t>sunrise.png</t>
         </is>
       </c>
       <c r="I571" s="30" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="H572" s="28" t="inlineStr">
         <is>
-          <t>Sunset.png</t>
+          <t>sunset.png</t>
         </is>
       </c>
       <c r="I572" s="28" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="H573" s="30" t="inlineStr">
         <is>
-          <t>Dawn.png</t>
+          <t>dawn.png</t>
         </is>
       </c>
       <c r="I573" s="30" t="inlineStr">
@@ -32073,7 +32073,7 @@
       </c>
       <c r="H574" s="28" t="inlineStr">
         <is>
-          <t>Dusk.png</t>
+          <t>dusk.png</t>
         </is>
       </c>
       <c r="I574" s="28" t="inlineStr">
@@ -32128,7 +32128,7 @@
       </c>
       <c r="H575" s="30" t="inlineStr">
         <is>
-          <t>Shade.png</t>
+          <t>shade.png</t>
         </is>
       </c>
       <c r="I575" s="30" t="inlineStr">
@@ -32183,7 +32183,7 @@
       </c>
       <c r="H576" s="28" t="inlineStr">
         <is>
-          <t>Waterfall.png</t>
+          <t>waterfall.png</t>
         </is>
       </c>
       <c r="I576" s="28" t="inlineStr">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="H577" s="30" t="inlineStr">
         <is>
-          <t>Pebble.png</t>
+          <t>pebble.png</t>
         </is>
       </c>
       <c r="I577" s="30" t="inlineStr">
@@ -32293,7 +32293,7 @@
       </c>
       <c r="H578" s="28" t="inlineStr">
         <is>
-          <t>Trunk.png</t>
+          <t>trunk.png</t>
         </is>
       </c>
       <c r="I578" s="28" t="inlineStr">
@@ -32348,7 +32348,7 @@
       </c>
       <c r="H579" s="30" t="inlineStr">
         <is>
-          <t>Twig.png</t>
+          <t>twig.png</t>
         </is>
       </c>
       <c r="I579" s="30" t="inlineStr">
@@ -32403,7 +32403,7 @@
       </c>
       <c r="H580" s="28" t="inlineStr">
         <is>
-          <t>Mist.png</t>
+          <t>mist.png</t>
         </is>
       </c>
       <c r="I580" s="28" t="inlineStr">
@@ -32458,7 +32458,7 @@
       </c>
       <c r="H581" s="30" t="inlineStr">
         <is>
-          <t>Blossom.png</t>
+          <t>blossom.png</t>
         </is>
       </c>
       <c r="I581" s="30" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H582" s="28" t="inlineStr">
         <is>
-          <t>Petal.png</t>
+          <t>petal.png</t>
         </is>
       </c>
       <c r="I582" s="28" t="inlineStr">
@@ -32568,7 +32568,7 @@
       </c>
       <c r="H583" s="30" t="inlineStr">
         <is>
-          <t>Vine.png</t>
+          <t>vine.png</t>
         </is>
       </c>
       <c r="I583" s="30" t="inlineStr">
@@ -32623,7 +32623,7 @@
       </c>
       <c r="H584" s="28" t="inlineStr">
         <is>
-          <t>Spring.png</t>
+          <t>spring.png</t>
         </is>
       </c>
       <c r="I584" s="28" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="H585" s="30" t="inlineStr">
         <is>
-          <t>Summer.png</t>
+          <t>summer.png</t>
         </is>
       </c>
       <c r="I585" s="30" t="inlineStr">
@@ -32733,7 +32733,7 @@
       </c>
       <c r="H586" s="28" t="inlineStr">
         <is>
-          <t>Fall.png</t>
+          <t>fall.png</t>
         </is>
       </c>
       <c r="I586" s="28" t="inlineStr">
@@ -32788,7 +32788,7 @@
       </c>
       <c r="H587" s="30" t="inlineStr">
         <is>
-          <t>Winter.png</t>
+          <t>winter.png</t>
         </is>
       </c>
       <c r="I587" s="30" t="inlineStr">
@@ -32843,7 +32843,7 @@
       </c>
       <c r="H588" s="28" t="inlineStr">
         <is>
-          <t>Morning.png</t>
+          <t>morning.png</t>
         </is>
       </c>
       <c r="I588" s="28" t="inlineStr">
@@ -32898,7 +32898,7 @@
       </c>
       <c r="H589" s="30" t="inlineStr">
         <is>
-          <t>Afternoon.png</t>
+          <t>afternoon.png</t>
         </is>
       </c>
       <c r="I589" s="30" t="inlineStr">
@@ -32953,7 +32953,7 @@
       </c>
       <c r="H590" s="28" t="inlineStr">
         <is>
-          <t>Evening.png</t>
+          <t>evening.png</t>
         </is>
       </c>
       <c r="I590" s="28" t="inlineStr">
@@ -33008,7 +33008,7 @@
       </c>
       <c r="H591" s="30" t="inlineStr">
         <is>
-          <t>Night.png</t>
+          <t>night.png</t>
         </is>
       </c>
       <c r="I591" s="30" t="inlineStr">
@@ -33063,7 +33063,7 @@
       </c>
       <c r="H592" s="28" t="inlineStr">
         <is>
-          <t>Today.png</t>
+          <t>today.png</t>
         </is>
       </c>
       <c r="I592" s="28" t="inlineStr">
@@ -33118,7 +33118,7 @@
       </c>
       <c r="H593" s="30" t="inlineStr">
         <is>
-          <t>Tomorrow.png</t>
+          <t>tomorrow.png</t>
         </is>
       </c>
       <c r="I593" s="30" t="inlineStr">
@@ -33173,7 +33173,7 @@
       </c>
       <c r="H594" s="28" t="inlineStr">
         <is>
-          <t>Yesterday.png</t>
+          <t>yesterday.png</t>
         </is>
       </c>
       <c r="I594" s="28" t="inlineStr">
@@ -33228,7 +33228,7 @@
       </c>
       <c r="H595" s="30" t="inlineStr">
         <is>
-          <t>Week.png</t>
+          <t>week.png</t>
         </is>
       </c>
       <c r="I595" s="30" t="inlineStr">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="H596" s="28" t="inlineStr">
         <is>
-          <t>Month.png</t>
+          <t>month.png</t>
         </is>
       </c>
       <c r="I596" s="28" t="inlineStr">
@@ -33338,7 +33338,7 @@
       </c>
       <c r="H597" s="30" t="inlineStr">
         <is>
-          <t>Year.png</t>
+          <t>year.png</t>
         </is>
       </c>
       <c r="I597" s="30" t="inlineStr">
@@ -33393,7 +33393,7 @@
       </c>
       <c r="H598" s="28" t="inlineStr">
         <is>
-          <t>Monday.png</t>
+          <t>monday.png</t>
         </is>
       </c>
       <c r="I598" s="28" t="inlineStr">
@@ -33448,7 +33448,7 @@
       </c>
       <c r="H599" s="30" t="inlineStr">
         <is>
-          <t>Tuesday.png</t>
+          <t>tuesday.png</t>
         </is>
       </c>
       <c r="I599" s="30" t="inlineStr">
@@ -33503,7 +33503,7 @@
       </c>
       <c r="H600" s="28" t="inlineStr">
         <is>
-          <t>Wednesday.png</t>
+          <t>wednesday.png</t>
         </is>
       </c>
       <c r="I600" s="28" t="inlineStr">
@@ -33558,7 +33558,7 @@
       </c>
       <c r="H601" s="30" t="inlineStr">
         <is>
-          <t>Thursday.png</t>
+          <t>thursday.png</t>
         </is>
       </c>
       <c r="I601" s="30" t="inlineStr">
@@ -33613,7 +33613,7 @@
       </c>
       <c r="H602" s="28" t="inlineStr">
         <is>
-          <t>Friday.png</t>
+          <t>friday.png</t>
         </is>
       </c>
       <c r="I602" s="28" t="inlineStr">
@@ -33668,7 +33668,7 @@
       </c>
       <c r="H603" s="30" t="inlineStr">
         <is>
-          <t>Saturday.png</t>
+          <t>saturday.png</t>
         </is>
       </c>
       <c r="I603" s="30" t="inlineStr">
@@ -33723,7 +33723,7 @@
       </c>
       <c r="H604" s="28" t="inlineStr">
         <is>
-          <t>Sunday.png</t>
+          <t>sunday.png</t>
         </is>
       </c>
       <c r="I604" s="28" t="inlineStr">
@@ -33778,7 +33778,7 @@
       </c>
       <c r="H605" s="30" t="inlineStr">
         <is>
-          <t>January.png</t>
+          <t>january.png</t>
         </is>
       </c>
       <c r="I605" s="30" t="inlineStr">
@@ -33833,7 +33833,7 @@
       </c>
       <c r="H606" s="28" t="inlineStr">
         <is>
-          <t>February.png</t>
+          <t>february.png</t>
         </is>
       </c>
       <c r="I606" s="28" t="inlineStr">
@@ -33888,7 +33888,7 @@
       </c>
       <c r="H607" s="30" t="inlineStr">
         <is>
-          <t>March.png</t>
+          <t>march.png</t>
         </is>
       </c>
       <c r="I607" s="30" t="inlineStr">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="H608" s="28" t="inlineStr">
         <is>
-          <t>April.png</t>
+          <t>april.png</t>
         </is>
       </c>
       <c r="I608" s="28" t="inlineStr">
@@ -33998,7 +33998,7 @@
       </c>
       <c r="H609" s="30" t="inlineStr">
         <is>
-          <t>May.png</t>
+          <t>may.png</t>
         </is>
       </c>
       <c r="I609" s="30" t="inlineStr">
@@ -34053,7 +34053,7 @@
       </c>
       <c r="H610" s="28" t="inlineStr">
         <is>
-          <t>June.png</t>
+          <t>june.png</t>
         </is>
       </c>
       <c r="I610" s="28" t="inlineStr">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="H611" s="30" t="inlineStr">
         <is>
-          <t>July.png</t>
+          <t>july.png</t>
         </is>
       </c>
       <c r="I611" s="30" t="inlineStr">
@@ -34163,7 +34163,7 @@
       </c>
       <c r="H612" s="28" t="inlineStr">
         <is>
-          <t>August.png</t>
+          <t>august.png</t>
         </is>
       </c>
       <c r="I612" s="28" t="inlineStr">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="H613" s="30" t="inlineStr">
         <is>
-          <t>September.png</t>
+          <t>september.png</t>
         </is>
       </c>
       <c r="I613" s="30" t="inlineStr">
@@ -34273,7 +34273,7 @@
       </c>
       <c r="H614" s="28" t="inlineStr">
         <is>
-          <t>October.png</t>
+          <t>october.png</t>
         </is>
       </c>
       <c r="I614" s="28" t="inlineStr">
@@ -34328,7 +34328,7 @@
       </c>
       <c r="H615" s="30" t="inlineStr">
         <is>
-          <t>November.png</t>
+          <t>november.png</t>
         </is>
       </c>
       <c r="I615" s="30" t="inlineStr">
@@ -34383,7 +34383,7 @@
       </c>
       <c r="H616" s="28" t="inlineStr">
         <is>
-          <t>December.png</t>
+          <t>december.png</t>
         </is>
       </c>
       <c r="I616" s="28" t="inlineStr">
@@ -34438,7 +34438,7 @@
       </c>
       <c r="H617" s="30" t="inlineStr">
         <is>
-          <t>Holiday.png</t>
+          <t>holiday.png</t>
         </is>
       </c>
       <c r="I617" s="30" t="inlineStr">
@@ -34493,7 +34493,7 @@
       </c>
       <c r="H618" s="28" t="inlineStr">
         <is>
-          <t>Vacation.png</t>
+          <t>vacation.png</t>
         </is>
       </c>
       <c r="I618" s="28" t="inlineStr">
@@ -34548,7 +34548,7 @@
       </c>
       <c r="H619" s="30" t="inlineStr">
         <is>
-          <t>Century.png</t>
+          <t>century.png</t>
         </is>
       </c>
       <c r="I619" s="30" t="inlineStr">
@@ -34603,7 +34603,7 @@
       </c>
       <c r="H620" s="28" t="inlineStr">
         <is>
-          <t>Decade.png</t>
+          <t>decade.png</t>
         </is>
       </c>
       <c r="I620" s="28" t="inlineStr">
@@ -34658,7 +34658,7 @@
       </c>
       <c r="H621" s="30" t="inlineStr">
         <is>
-          <t>Weekend.png</t>
+          <t>weekend.png</t>
         </is>
       </c>
       <c r="I621" s="30" t="inlineStr">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="H622" s="28" t="inlineStr">
         <is>
-          <t>Weekday.png</t>
+          <t>weekday.png</t>
         </is>
       </c>
       <c r="I622" s="28" t="inlineStr">
@@ -34768,7 +34768,7 @@
       </c>
       <c r="H623" s="30" t="inlineStr">
         <is>
-          <t>Birthday.png</t>
+          <t>birthday.png</t>
         </is>
       </c>
       <c r="I623" s="30" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="H624" s="28" t="inlineStr">
         <is>
-          <t>Anniversary.png</t>
+          <t>anniversary.png</t>
         </is>
       </c>
       <c r="I624" s="28" t="inlineStr">
@@ -34878,7 +34878,7 @@
       </c>
       <c r="H625" s="30" t="inlineStr">
         <is>
-          <t>Midnight.png</t>
+          <t>midnight.png</t>
         </is>
       </c>
       <c r="I625" s="30" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="H626" s="28" t="inlineStr">
         <is>
-          <t>Noon.png</t>
+          <t>noon.png</t>
         </is>
       </c>
       <c r="I626" s="28" t="inlineStr">
@@ -34988,7 +34988,7 @@
       </c>
       <c r="H627" s="30" t="inlineStr">
         <is>
-          <t>Hour.png</t>
+          <t>hour.png</t>
         </is>
       </c>
       <c r="I627" s="30" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="H628" s="28" t="inlineStr">
         <is>
-          <t>Minute.png</t>
+          <t>minute.png</t>
         </is>
       </c>
       <c r="I628" s="28" t="inlineStr">
@@ -35098,7 +35098,7 @@
       </c>
       <c r="H629" s="30" t="inlineStr">
         <is>
-          <t>Red.png</t>
+          <t>red.png</t>
         </is>
       </c>
       <c r="I629" s="30" t="inlineStr">
@@ -35153,7 +35153,7 @@
       </c>
       <c r="H630" s="28" t="inlineStr">
         <is>
-          <t>Blue.png</t>
+          <t>blue.png</t>
         </is>
       </c>
       <c r="I630" s="28" t="inlineStr">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="H631" s="30" t="inlineStr">
         <is>
-          <t>Yellow.png</t>
+          <t>yellow.png</t>
         </is>
       </c>
       <c r="I631" s="30" t="inlineStr">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="H632" s="28" t="inlineStr">
         <is>
-          <t>Green.png</t>
+          <t>green.png</t>
         </is>
       </c>
       <c r="I632" s="28" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="H633" s="30" t="inlineStr">
         <is>
-          <t>Black.png</t>
+          <t>black.png</t>
         </is>
       </c>
       <c r="I633" s="30" t="inlineStr">
@@ -35373,7 +35373,7 @@
       </c>
       <c r="H634" s="28" t="inlineStr">
         <is>
-          <t>White.png</t>
+          <t>white.png</t>
         </is>
       </c>
       <c r="I634" s="28" t="inlineStr">
@@ -35428,7 +35428,7 @@
       </c>
       <c r="H635" s="30" t="inlineStr">
         <is>
-          <t>Pink.png</t>
+          <t>pink.png</t>
         </is>
       </c>
       <c r="I635" s="30" t="inlineStr">
@@ -35483,7 +35483,7 @@
       </c>
       <c r="H636" s="28" t="inlineStr">
         <is>
-          <t>Purple.png</t>
+          <t>purple.png</t>
         </is>
       </c>
       <c r="I636" s="28" t="inlineStr">
@@ -35538,7 +35538,7 @@
       </c>
       <c r="H637" s="30" t="inlineStr">
         <is>
-          <t>One.png</t>
+          <t>one.png</t>
         </is>
       </c>
       <c r="I637" s="30" t="inlineStr">
@@ -35593,7 +35593,7 @@
       </c>
       <c r="H638" s="28" t="inlineStr">
         <is>
-          <t>Two.png</t>
+          <t>two.png</t>
         </is>
       </c>
       <c r="I638" s="28" t="inlineStr">
@@ -35648,7 +35648,7 @@
       </c>
       <c r="H639" s="30" t="inlineStr">
         <is>
-          <t>Three.png</t>
+          <t>three.png</t>
         </is>
       </c>
       <c r="I639" s="30" t="inlineStr">
@@ -35703,7 +35703,7 @@
       </c>
       <c r="H640" s="28" t="inlineStr">
         <is>
-          <t>Four.png</t>
+          <t>four.png</t>
         </is>
       </c>
       <c r="I640" s="28" t="inlineStr">
@@ -35758,7 +35758,7 @@
       </c>
       <c r="H641" s="30" t="inlineStr">
         <is>
-          <t>Five.png</t>
+          <t>five.png</t>
         </is>
       </c>
       <c r="I641" s="30" t="inlineStr">
@@ -35813,7 +35813,7 @@
       </c>
       <c r="H642" s="28" t="inlineStr">
         <is>
-          <t>Ten.png</t>
+          <t>ten.png</t>
         </is>
       </c>
       <c r="I642" s="28" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H643" s="30" t="inlineStr">
         <is>
-          <t>Number.png</t>
+          <t>number.png</t>
         </is>
       </c>
       <c r="I643" s="30" t="inlineStr">
@@ -35923,7 +35923,7 @@
       </c>
       <c r="H644" s="28" t="inlineStr">
         <is>
-          <t>Brown.png</t>
+          <t>brown.png</t>
         </is>
       </c>
       <c r="I644" s="28" t="inlineStr">
@@ -35978,7 +35978,7 @@
       </c>
       <c r="H645" s="30" t="inlineStr">
         <is>
-          <t>Gray.png</t>
+          <t>gray.png</t>
         </is>
       </c>
       <c r="I645" s="30" t="inlineStr">
@@ -36033,7 +36033,7 @@
       </c>
       <c r="H646" s="28" t="inlineStr">
         <is>
-          <t>Six.png</t>
+          <t>six.png</t>
         </is>
       </c>
       <c r="I646" s="28" t="inlineStr">
@@ -36088,7 +36088,7 @@
       </c>
       <c r="H647" s="30" t="inlineStr">
         <is>
-          <t>Seven.png</t>
+          <t>seven.png</t>
         </is>
       </c>
       <c r="I647" s="30" t="inlineStr">
@@ -36143,7 +36143,7 @@
       </c>
       <c r="H648" s="28" t="inlineStr">
         <is>
-          <t>Eight.png</t>
+          <t>eight.png</t>
         </is>
       </c>
       <c r="I648" s="28" t="inlineStr">
@@ -36198,7 +36198,7 @@
       </c>
       <c r="H649" s="30" t="inlineStr">
         <is>
-          <t>Nine.png</t>
+          <t>nine.png</t>
         </is>
       </c>
       <c r="I649" s="30" t="inlineStr">
@@ -36253,7 +36253,7 @@
       </c>
       <c r="H650" s="28" t="inlineStr">
         <is>
-          <t>Navy.png</t>
+          <t>navy.png</t>
         </is>
       </c>
       <c r="I650" s="28" t="inlineStr">
@@ -36308,7 +36308,7 @@
       </c>
       <c r="H651" s="30" t="inlineStr">
         <is>
-          <t>Beige.png</t>
+          <t>beige.png</t>
         </is>
       </c>
       <c r="I651" s="30" t="inlineStr">
@@ -36363,7 +36363,7 @@
       </c>
       <c r="H652" s="28" t="inlineStr">
         <is>
-          <t>Dozen.png</t>
+          <t>dozen.png</t>
         </is>
       </c>
       <c r="I652" s="28" t="inlineStr">
@@ -36418,7 +36418,7 @@
       </c>
       <c r="H653" s="30" t="inlineStr">
         <is>
-          <t>Half.png</t>
+          <t>half.png</t>
         </is>
       </c>
       <c r="I653" s="30" t="inlineStr">
@@ -36473,7 +36473,7 @@
       </c>
       <c r="H654" s="28" t="inlineStr">
         <is>
-          <t>Quarter.png</t>
+          <t>quarter.png</t>
         </is>
       </c>
       <c r="I654" s="28" t="inlineStr">
@@ -36528,7 +36528,7 @@
       </c>
       <c r="H655" s="30" t="inlineStr">
         <is>
-          <t>Triple.png</t>
+          <t>triple.png</t>
         </is>
       </c>
       <c r="I655" s="30" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="H656" s="28" t="inlineStr">
         <is>
-          <t>Million.png</t>
+          <t>million.png</t>
         </is>
       </c>
       <c r="I656" s="28" t="inlineStr">
@@ -36638,7 +36638,7 @@
       </c>
       <c r="H657" s="30" t="inlineStr">
         <is>
-          <t>Billion.png</t>
+          <t>billion.png</t>
         </is>
       </c>
       <c r="I657" s="30" t="inlineStr">
@@ -36693,7 +36693,7 @@
       </c>
       <c r="H658" s="28" t="inlineStr">
         <is>
-          <t>Pair.png</t>
+          <t>pair.png</t>
         </is>
       </c>
       <c r="I658" s="28" t="inlineStr">
@@ -36748,7 +36748,7 @@
       </c>
       <c r="H659" s="30" t="inlineStr">
         <is>
-          <t>Dot.png</t>
+          <t>dot.png</t>
         </is>
       </c>
       <c r="I659" s="30" t="inlineStr">
@@ -36803,7 +36803,7 @@
       </c>
       <c r="H660" s="28" t="inlineStr">
         <is>
-          <t>Big.png</t>
+          <t>big.png</t>
         </is>
       </c>
       <c r="I660" s="28" t="inlineStr">
@@ -36858,7 +36858,7 @@
       </c>
       <c r="H661" s="30" t="inlineStr">
         <is>
-          <t>Small.png</t>
+          <t>small.png</t>
         </is>
       </c>
       <c r="I661" s="30" t="inlineStr">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="H662" s="28" t="inlineStr">
         <is>
-          <t>High.png</t>
+          <t>high.png</t>
         </is>
       </c>
       <c r="I662" s="28" t="inlineStr">
@@ -36968,7 +36968,7 @@
       </c>
       <c r="H663" s="30" t="inlineStr">
         <is>
-          <t>Low.png</t>
+          <t>low.png</t>
         </is>
       </c>
       <c r="I663" s="30" t="inlineStr">
@@ -37023,7 +37023,7 @@
       </c>
       <c r="H664" s="28" t="inlineStr">
         <is>
-          <t>Fast.png</t>
+          <t>fast.png</t>
         </is>
       </c>
       <c r="I664" s="28" t="inlineStr">
@@ -37078,7 +37078,7 @@
       </c>
       <c r="H665" s="30" t="inlineStr">
         <is>
-          <t>Slow.png</t>
+          <t>slow.png</t>
         </is>
       </c>
       <c r="I665" s="30" t="inlineStr">
@@ -37133,7 +37133,7 @@
       </c>
       <c r="H666" s="28" t="inlineStr">
         <is>
-          <t>Hot.png</t>
+          <t>hot.png</t>
         </is>
       </c>
       <c r="I666" s="28" t="inlineStr">
@@ -37188,7 +37188,7 @@
       </c>
       <c r="H667" s="30" t="inlineStr">
         <is>
-          <t>Cold.png</t>
+          <t>cold.png</t>
         </is>
       </c>
       <c r="I667" s="30" t="inlineStr">
@@ -37243,7 +37243,7 @@
       </c>
       <c r="H668" s="28" t="inlineStr">
         <is>
-          <t>Warm.png</t>
+          <t>warm.png</t>
         </is>
       </c>
       <c r="I668" s="28" t="inlineStr">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="H669" s="30" t="inlineStr">
         <is>
-          <t>Cool.png</t>
+          <t>cool.png</t>
         </is>
       </c>
       <c r="I669" s="30" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="H670" s="28" t="inlineStr">
         <is>
-          <t>Good.png</t>
+          <t>good.png</t>
         </is>
       </c>
       <c r="I670" s="28" t="inlineStr">
@@ -37408,7 +37408,7 @@
       </c>
       <c r="H671" s="30" t="inlineStr">
         <is>
-          <t>Bad.png</t>
+          <t>bad.png</t>
         </is>
       </c>
       <c r="I671" s="30" t="inlineStr">
@@ -37463,7 +37463,7 @@
       </c>
       <c r="H672" s="28" t="inlineStr">
         <is>
-          <t>New.png</t>
+          <t>new.png</t>
         </is>
       </c>
       <c r="I672" s="28" t="inlineStr">
@@ -37518,7 +37518,7 @@
       </c>
       <c r="H673" s="30" t="inlineStr">
         <is>
-          <t>Old.png</t>
+          <t>old.png</t>
         </is>
       </c>
       <c r="I673" s="30" t="inlineStr">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="H674" s="28" t="inlineStr">
         <is>
-          <t>Young.png</t>
+          <t>young.png</t>
         </is>
       </c>
       <c r="I674" s="28" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="H675" s="30" t="inlineStr">
         <is>
-          <t>Cute.png</t>
+          <t>cute.png</t>
         </is>
       </c>
       <c r="I675" s="30" t="inlineStr">
@@ -37683,7 +37683,7 @@
       </c>
       <c r="H676" s="28" t="inlineStr">
         <is>
-          <t>Nice.png</t>
+          <t>nice.png</t>
         </is>
       </c>
       <c r="I676" s="28" t="inlineStr">
@@ -37738,7 +37738,7 @@
       </c>
       <c r="H677" s="30" t="inlineStr">
         <is>
-          <t>Price.png</t>
+          <t>price.png</t>
         </is>
       </c>
       <c r="I677" s="30" t="inlineStr">
@@ -37793,7 +37793,7 @@
       </c>
       <c r="H678" s="28" t="inlineStr">
         <is>
-          <t>Cost.png</t>
+          <t>cost.png</t>
         </is>
       </c>
       <c r="I678" s="28" t="inlineStr">
@@ -37848,7 +37848,7 @@
       </c>
       <c r="H679" s="30" t="inlineStr">
         <is>
-          <t>Shallow.png</t>
+          <t>shallow.png</t>
         </is>
       </c>
       <c r="I679" s="30" t="inlineStr">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="H680" s="28" t="inlineStr">
         <is>
-          <t>Straight.png</t>
+          <t>straight.png</t>
         </is>
       </c>
       <c r="I680" s="28" t="inlineStr">
@@ -37958,7 +37958,7 @@
       </c>
       <c r="H681" s="30" t="inlineStr">
         <is>
-          <t>Curved.png</t>
+          <t>curved.png</t>
         </is>
       </c>
       <c r="I681" s="30" t="inlineStr">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="H682" s="28" t="inlineStr">
         <is>
-          <t>Square.png</t>
+          <t>square.png</t>
         </is>
       </c>
       <c r="I682" s="28" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H683" s="30" t="inlineStr">
         <is>
-          <t>Round.png</t>
+          <t>round.png</t>
         </is>
       </c>
       <c r="I683" s="30" t="inlineStr">
@@ -38123,7 +38123,7 @@
       </c>
       <c r="H684" s="28" t="inlineStr">
         <is>
-          <t>Weak.png</t>
+          <t>weak.png</t>
         </is>
       </c>
       <c r="I684" s="28" t="inlineStr">
@@ -38178,7 +38178,7 @@
       </c>
       <c r="H685" s="30" t="inlineStr">
         <is>
-          <t>Closed.png</t>
+          <t>closed.png</t>
         </is>
       </c>
       <c r="I685" s="30" t="inlineStr">
@@ -38233,7 +38233,7 @@
       </c>
       <c r="H686" s="28" t="inlineStr">
         <is>
-          <t>Sticky.png</t>
+          <t>sticky.png</t>
         </is>
       </c>
       <c r="I686" s="28" t="inlineStr">
@@ -38288,7 +38288,7 @@
       </c>
       <c r="H687" s="30" t="inlineStr">
         <is>
-          <t>Fluffy.png</t>
+          <t>fluffy.png</t>
         </is>
       </c>
       <c r="I687" s="30" t="inlineStr">
@@ -38343,7 +38343,7 @@
       </c>
       <c r="H688" s="28" t="inlineStr">
         <is>
-          <t>Crispy.png</t>
+          <t>crispy.png</t>
         </is>
       </c>
       <c r="I688" s="28" t="inlineStr">
@@ -38398,7 +38398,7 @@
       </c>
       <c r="H689" s="30" t="inlineStr">
         <is>
-          <t>Salty.png</t>
+          <t>salty.png</t>
         </is>
       </c>
       <c r="I689" s="30" t="inlineStr">
@@ -38453,7 +38453,7 @@
       </c>
       <c r="H690" s="28" t="inlineStr">
         <is>
-          <t>Spicy.png</t>
+          <t>spicy.png</t>
         </is>
       </c>
       <c r="I690" s="28" t="inlineStr">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="H691" s="30" t="inlineStr">
         <is>
-          <t>Bitter.png</t>
+          <t>bitter.png</t>
         </is>
       </c>
       <c r="I691" s="30" t="inlineStr">
@@ -38563,7 +38563,7 @@
       </c>
       <c r="H692" s="28" t="inlineStr">
         <is>
-          <t>Juicy.png</t>
+          <t>juicy.png</t>
         </is>
       </c>
       <c r="I692" s="28" t="inlineStr">
@@ -38618,7 +38618,7 @@
       </c>
       <c r="H693" s="30" t="inlineStr">
         <is>
-          <t>Tidy.png</t>
+          <t>tidy.png</t>
         </is>
       </c>
       <c r="I693" s="30" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="H694" s="28" t="inlineStr">
         <is>
-          <t>Messy.png</t>
+          <t>messy.png</t>
         </is>
       </c>
       <c r="I694" s="28" t="inlineStr">
@@ -38728,7 +38728,7 @@
       </c>
       <c r="H695" s="30" t="inlineStr">
         <is>
-          <t>Noisy.png</t>
+          <t>noisy.png</t>
         </is>
       </c>
       <c r="I695" s="30" t="inlineStr">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="H696" s="28" t="inlineStr">
         <is>
-          <t>Silly.png</t>
+          <t>silly.png</t>
         </is>
       </c>
       <c r="I696" s="28" t="inlineStr">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="H697" s="30" t="inlineStr">
         <is>
-          <t>Happy.png</t>
+          <t>happy.png</t>
         </is>
       </c>
       <c r="I697" s="30" t="inlineStr">
@@ -38893,7 +38893,7 @@
       </c>
       <c r="H698" s="28" t="inlineStr">
         <is>
-          <t>Sad.png</t>
+          <t>sad.png</t>
         </is>
       </c>
       <c r="I698" s="28" t="inlineStr">
@@ -38948,7 +38948,7 @@
       </c>
       <c r="H699" s="30" t="inlineStr">
         <is>
-          <t>Angry.png</t>
+          <t>angry.png</t>
         </is>
       </c>
       <c r="I699" s="30" t="inlineStr">
@@ -39003,7 +39003,7 @@
       </c>
       <c r="H700" s="28" t="inlineStr">
         <is>
-          <t>Tired.png</t>
+          <t>tired.png</t>
         </is>
       </c>
       <c r="I700" s="28" t="inlineStr">
@@ -39058,7 +39058,7 @@
       </c>
       <c r="H701" s="30" t="inlineStr">
         <is>
-          <t>Hungry.png</t>
+          <t>hungry.png</t>
         </is>
       </c>
       <c r="I701" s="30" t="inlineStr">
@@ -39113,7 +39113,7 @@
       </c>
       <c r="H702" s="28" t="inlineStr">
         <is>
-          <t>Thirsty.png</t>
+          <t>thirsty.png</t>
         </is>
       </c>
       <c r="I702" s="28" t="inlineStr">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="H703" s="30" t="inlineStr">
         <is>
-          <t>Sleepy.png</t>
+          <t>sleepy.png</t>
         </is>
       </c>
       <c r="I703" s="30" t="inlineStr">
@@ -39223,7 +39223,7 @@
       </c>
       <c r="H704" s="28" t="inlineStr">
         <is>
-          <t>Sick.png</t>
+          <t>sick.png</t>
         </is>
       </c>
       <c r="I704" s="28" t="inlineStr">
@@ -39278,7 +39278,7 @@
       </c>
       <c r="H705" s="30" t="inlineStr">
         <is>
-          <t>Scared.png</t>
+          <t>scared.png</t>
         </is>
       </c>
       <c r="I705" s="30" t="inlineStr">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="H706" s="28" t="inlineStr">
         <is>
-          <t>Excited.png</t>
+          <t>excited.png</t>
         </is>
       </c>
       <c r="I706" s="28" t="inlineStr">
@@ -39388,7 +39388,7 @@
       </c>
       <c r="H707" s="30" t="inlineStr">
         <is>
-          <t>Surprised.png</t>
+          <t>surprised.png</t>
         </is>
       </c>
       <c r="I707" s="30" t="inlineStr">
@@ -39443,7 +39443,7 @@
       </c>
       <c r="H708" s="28" t="inlineStr">
         <is>
-          <t>Love.png</t>
+          <t>love.png</t>
         </is>
       </c>
       <c r="I708" s="28" t="inlineStr">
@@ -39498,7 +39498,7 @@
       </c>
       <c r="H709" s="30" t="inlineStr">
         <is>
-          <t>Heart.png</t>
+          <t>heart.png</t>
         </is>
       </c>
       <c r="I709" s="30" t="inlineStr">
@@ -39553,7 +39553,7 @@
       </c>
       <c r="H710" s="28" t="inlineStr">
         <is>
-          <t>Sorry.png</t>
+          <t>sorry.png</t>
         </is>
       </c>
       <c r="I710" s="28" t="inlineStr">
@@ -39608,7 +39608,7 @@
       </c>
       <c r="H711" s="30" t="inlineStr">
         <is>
-          <t>Fine.png</t>
+          <t>fine.png</t>
         </is>
       </c>
       <c r="I711" s="30" t="inlineStr">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="H712" s="28" t="inlineStr">
         <is>
-          <t>Hurt.png</t>
+          <t>hurt.png</t>
         </is>
       </c>
       <c r="I712" s="28" t="inlineStr">
@@ -39718,7 +39718,7 @@
       </c>
       <c r="H713" s="30" t="inlineStr">
         <is>
-          <t>Well.png</t>
+          <t>well.png</t>
         </is>
       </c>
       <c r="I713" s="30" t="inlineStr">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="H714" s="28" t="inlineStr">
         <is>
-          <t>Smart.png</t>
+          <t>smart.png</t>
         </is>
       </c>
       <c r="I714" s="28" t="inlineStr">
@@ -39828,7 +39828,7 @@
       </c>
       <c r="H715" s="30" t="inlineStr">
         <is>
-          <t>Funny.png</t>
+          <t>funny.png</t>
         </is>
       </c>
       <c r="I715" s="30" t="inlineStr">
@@ -39883,7 +39883,7 @@
       </c>
       <c r="H716" s="28" t="inlineStr">
         <is>
-          <t>Friendly.png</t>
+          <t>friendly.png</t>
         </is>
       </c>
       <c r="I716" s="28" t="inlineStr">
@@ -39938,7 +39938,7 @@
       </c>
       <c r="H717" s="30" t="inlineStr">
         <is>
-          <t>Kind.png</t>
+          <t>kind.png</t>
         </is>
       </c>
       <c r="I717" s="30" t="inlineStr">
@@ -39993,7 +39993,7 @@
       </c>
       <c r="H718" s="28" t="inlineStr">
         <is>
-          <t>Merry.png</t>
+          <t>merry.png</t>
         </is>
       </c>
       <c r="I718" s="28" t="inlineStr">
@@ -40048,7 +40048,7 @@
       </c>
       <c r="H719" s="30" t="inlineStr">
         <is>
-          <t>Bold.png</t>
+          <t>bold.png</t>
         </is>
       </c>
       <c r="I719" s="30" t="inlineStr">
@@ -40103,7 +40103,7 @@
       </c>
       <c r="H720" s="28" t="inlineStr">
         <is>
-          <t>Safe.png</t>
+          <t>safe.png</t>
         </is>
       </c>
       <c r="I720" s="28" t="inlineStr">
@@ -40158,7 +40158,7 @@
       </c>
       <c r="H721" s="30" t="inlineStr">
         <is>
-          <t>Sure.png</t>
+          <t>sure.png</t>
         </is>
       </c>
       <c r="I721" s="30" t="inlineStr">
@@ -40213,7 +40213,7 @@
       </c>
       <c r="H722" s="28" t="inlineStr">
         <is>
-          <t>Run.png</t>
+          <t>run.png</t>
         </is>
       </c>
       <c r="I722" s="28" t="inlineStr">
@@ -40268,7 +40268,7 @@
       </c>
       <c r="H723" s="30" t="inlineStr">
         <is>
-          <t>Jump.png</t>
+          <t>jump.png</t>
         </is>
       </c>
       <c r="I723" s="30" t="inlineStr">
@@ -40323,7 +40323,7 @@
       </c>
       <c r="H724" s="28" t="inlineStr">
         <is>
-          <t>Walk.png</t>
+          <t>walk.png</t>
         </is>
       </c>
       <c r="I724" s="28" t="inlineStr">
@@ -40378,7 +40378,7 @@
       </c>
       <c r="H725" s="30" t="inlineStr">
         <is>
-          <t>Eat.png</t>
+          <t>eat.png</t>
         </is>
       </c>
       <c r="I725" s="30" t="inlineStr">
@@ -40433,7 +40433,7 @@
       </c>
       <c r="H726" s="28" t="inlineStr">
         <is>
-          <t>Drink.png</t>
+          <t>drink.png</t>
         </is>
       </c>
       <c r="I726" s="28" t="inlineStr">
@@ -40488,7 +40488,7 @@
       </c>
       <c r="H727" s="30" t="inlineStr">
         <is>
-          <t>Sleep.png</t>
+          <t>sleep.png</t>
         </is>
       </c>
       <c r="I727" s="30" t="inlineStr">
@@ -40543,7 +40543,7 @@
       </c>
       <c r="H728" s="28" t="inlineStr">
         <is>
-          <t>Read.png</t>
+          <t>read.png</t>
         </is>
       </c>
       <c r="I728" s="28" t="inlineStr">
@@ -40598,7 +40598,7 @@
       </c>
       <c r="H729" s="30" t="inlineStr">
         <is>
-          <t>Write.png</t>
+          <t>write.png</t>
         </is>
       </c>
       <c r="I729" s="30" t="inlineStr">
@@ -40653,7 +40653,7 @@
       </c>
       <c r="H730" s="28" t="inlineStr">
         <is>
-          <t>Sing.png</t>
+          <t>sing.png</t>
         </is>
       </c>
       <c r="I730" s="28" t="inlineStr">
@@ -40708,7 +40708,7 @@
       </c>
       <c r="H731" s="30" t="inlineStr">
         <is>
-          <t>Dance.png</t>
+          <t>dance.png</t>
         </is>
       </c>
       <c r="I731" s="30" t="inlineStr">
@@ -40763,7 +40763,7 @@
       </c>
       <c r="H732" s="28" t="inlineStr">
         <is>
-          <t>Play.png</t>
+          <t>play.png</t>
         </is>
       </c>
       <c r="I732" s="28" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="H733" s="30" t="inlineStr">
         <is>
-          <t>Study.png</t>
+          <t>study.png</t>
         </is>
       </c>
       <c r="I733" s="30" t="inlineStr">
@@ -40873,7 +40873,7 @@
       </c>
       <c r="H734" s="28" t="inlineStr">
         <is>
-          <t>Swim.png</t>
+          <t>swim.png</t>
         </is>
       </c>
       <c r="I734" s="28" t="inlineStr">
@@ -40928,7 +40928,7 @@
       </c>
       <c r="H735" s="30" t="inlineStr">
         <is>
-          <t>Fly.png</t>
+          <t>fly.png</t>
         </is>
       </c>
       <c r="I735" s="30" t="inlineStr">
@@ -40983,7 +40983,7 @@
       </c>
       <c r="H736" s="28" t="inlineStr">
         <is>
-          <t>Clean.png</t>
+          <t>clean.png</t>
         </is>
       </c>
       <c r="I736" s="28" t="inlineStr">
@@ -41038,7 +41038,7 @@
       </c>
       <c r="H737" s="30" t="inlineStr">
         <is>
-          <t>Wash.png</t>
+          <t>wash.png</t>
         </is>
       </c>
       <c r="I737" s="30" t="inlineStr">
@@ -41093,7 +41093,7 @@
       </c>
       <c r="H738" s="28" t="inlineStr">
         <is>
-          <t>Open.png</t>
+          <t>open.png</t>
         </is>
       </c>
       <c r="I738" s="28" t="inlineStr">
@@ -41148,7 +41148,7 @@
       </c>
       <c r="H739" s="30" t="inlineStr">
         <is>
-          <t>Close.png</t>
+          <t>close.png</t>
         </is>
       </c>
       <c r="I739" s="30" t="inlineStr">
@@ -41203,7 +41203,7 @@
       </c>
       <c r="H740" s="28" t="inlineStr">
         <is>
-          <t>Push.png</t>
+          <t>push.png</t>
         </is>
       </c>
       <c r="I740" s="28" t="inlineStr">
@@ -41258,7 +41258,7 @@
       </c>
       <c r="H741" s="30" t="inlineStr">
         <is>
-          <t>Pull.png</t>
+          <t>pull.png</t>
         </is>
       </c>
       <c r="I741" s="30" t="inlineStr">
@@ -41313,7 +41313,7 @@
       </c>
       <c r="H742" s="28" t="inlineStr">
         <is>
-          <t>Travel.png</t>
+          <t>travel.png</t>
         </is>
       </c>
       <c r="I742" s="28" t="inlineStr">
@@ -41368,7 +41368,7 @@
       </c>
       <c r="H743" s="30" t="inlineStr">
         <is>
-          <t>Pay.png</t>
+          <t>pay.png</t>
         </is>
       </c>
       <c r="I743" s="30" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="H744" s="28" t="inlineStr">
         <is>
-          <t>Buy.png</t>
+          <t>buy.png</t>
         </is>
       </c>
       <c r="I744" s="28" t="inlineStr">
@@ -41478,7 +41478,7 @@
       </c>
       <c r="H745" s="30" t="inlineStr">
         <is>
-          <t>Sell.png</t>
+          <t>sell.png</t>
         </is>
       </c>
       <c r="I745" s="30" t="inlineStr">
@@ -41533,7 +41533,7 @@
       </c>
       <c r="H746" s="28" t="inlineStr">
         <is>
-          <t>Sit.png</t>
+          <t>sit.png</t>
         </is>
       </c>
       <c r="I746" s="28" t="inlineStr">
@@ -41588,7 +41588,7 @@
       </c>
       <c r="H747" s="30" t="inlineStr">
         <is>
-          <t>Stand.png</t>
+          <t>stand.png</t>
         </is>
       </c>
       <c r="I747" s="30" t="inlineStr">
@@ -41643,7 +41643,7 @@
       </c>
       <c r="H748" s="28" t="inlineStr">
         <is>
-          <t>Hold.png</t>
+          <t>hold.png</t>
         </is>
       </c>
       <c r="I748" s="28" t="inlineStr">
@@ -41698,7 +41698,7 @@
       </c>
       <c r="H749" s="30" t="inlineStr">
         <is>
-          <t>Comb.png</t>
+          <t>comb.png</t>
         </is>
       </c>
       <c r="I749" s="30" t="inlineStr">
@@ -41753,7 +41753,7 @@
       </c>
       <c r="H750" s="28" t="inlineStr">
         <is>
-          <t>Bake.png</t>
+          <t>bake.png</t>
         </is>
       </c>
       <c r="I750" s="28" t="inlineStr">
@@ -41808,7 +41808,7 @@
       </c>
       <c r="H751" s="30" t="inlineStr">
         <is>
-          <t>Taste.png</t>
+          <t>taste.png</t>
         </is>
       </c>
       <c r="I751" s="30" t="inlineStr">
@@ -41863,7 +41863,7 @@
       </c>
       <c r="H752" s="28" t="inlineStr">
         <is>
-          <t>Smell.png</t>
+          <t>smell.png</t>
         </is>
       </c>
       <c r="I752" s="28" t="inlineStr">
@@ -41918,7 +41918,7 @@
       </c>
       <c r="H753" s="30" t="inlineStr">
         <is>
-          <t>Hear.png</t>
+          <t>hear.png</t>
         </is>
       </c>
       <c r="I753" s="30" t="inlineStr">
@@ -41973,7 +41973,7 @@
       </c>
       <c r="H754" s="28" t="inlineStr">
         <is>
-          <t>Listen.png</t>
+          <t>listen.png</t>
         </is>
       </c>
       <c r="I754" s="28" t="inlineStr">
@@ -42028,7 +42028,7 @@
       </c>
       <c r="H755" s="30" t="inlineStr">
         <is>
-          <t>Draw.png</t>
+          <t>draw.png</t>
         </is>
       </c>
       <c r="I755" s="30" t="inlineStr">
@@ -42083,7 +42083,7 @@
       </c>
       <c r="H756" s="28" t="inlineStr">
         <is>
-          <t>Clap.png</t>
+          <t>clap.png</t>
         </is>
       </c>
       <c r="I756" s="28" t="inlineStr">
@@ -42138,7 +42138,7 @@
       </c>
       <c r="H757" s="30" t="inlineStr">
         <is>
-          <t>Hug.png</t>
+          <t>hug.png</t>
         </is>
       </c>
       <c r="I757" s="30" t="inlineStr">
@@ -42193,7 +42193,7 @@
       </c>
       <c r="H758" s="28" t="inlineStr">
         <is>
-          <t>Ring.png</t>
+          <t>ring.png</t>
         </is>
       </c>
       <c r="I758" s="28" t="inlineStr">
@@ -42248,7 +42248,7 @@
       </c>
       <c r="H759" s="30" t="inlineStr">
         <is>
-          <t>Blow.png</t>
+          <t>blow.png</t>
         </is>
       </c>
       <c r="I759" s="30" t="inlineStr">
@@ -42303,7 +42303,7 @@
       </c>
       <c r="H760" s="28" t="inlineStr">
         <is>
-          <t>Bite.png</t>
+          <t>bite.png</t>
         </is>
       </c>
       <c r="I760" s="28" t="inlineStr">
@@ -42358,7 +42358,7 @@
       </c>
       <c r="H761" s="30" t="inlineStr">
         <is>
-          <t>Chew.png</t>
+          <t>chew.png</t>
         </is>
       </c>
       <c r="I761" s="30" t="inlineStr">
@@ -42413,7 +42413,7 @@
       </c>
       <c r="H762" s="28" t="inlineStr">
         <is>
-          <t>Lick.png</t>
+          <t>lick.png</t>
         </is>
       </c>
       <c r="I762" s="28" t="inlineStr">
@@ -42468,7 +42468,7 @@
       </c>
       <c r="H763" s="30" t="inlineStr">
         <is>
-          <t>Drive.png</t>
+          <t>drive.png</t>
         </is>
       </c>
       <c r="I763" s="30" t="inlineStr">
@@ -42523,7 +42523,7 @@
       </c>
       <c r="H764" s="28" t="inlineStr">
         <is>
-          <t>Slip.png</t>
+          <t>slip.png</t>
         </is>
       </c>
       <c r="I764" s="28" t="inlineStr">
@@ -42578,7 +42578,7 @@
       </c>
       <c r="H765" s="30" t="inlineStr">
         <is>
-          <t>Skip.png</t>
+          <t>skip.png</t>
         </is>
       </c>
       <c r="I765" s="30" t="inlineStr">
@@ -42633,7 +42633,7 @@
       </c>
       <c r="H766" s="28" t="inlineStr">
         <is>
-          <t>Hop.png</t>
+          <t>hop.png</t>
         </is>
       </c>
       <c r="I766" s="28" t="inlineStr">
@@ -42688,7 +42688,7 @@
       </c>
       <c r="H767" s="30" t="inlineStr">
         <is>
-          <t>Kneel.png</t>
+          <t>kneel.png</t>
         </is>
       </c>
       <c r="I767" s="30" t="inlineStr">
@@ -42743,7 +42743,7 @@
       </c>
       <c r="H768" s="28" t="inlineStr">
         <is>
-          <t>Pat.png</t>
+          <t>pat.png</t>
         </is>
       </c>
       <c r="I768" s="28" t="inlineStr">
@@ -42798,7 +42798,7 @@
       </c>
       <c r="H769" s="30" t="inlineStr">
         <is>
-          <t>Rub.png</t>
+          <t>rub.png</t>
         </is>
       </c>
       <c r="I769" s="30" t="inlineStr">
@@ -42853,7 +42853,7 @@
       </c>
       <c r="H770" s="28" t="inlineStr">
         <is>
-          <t>Ball.png</t>
+          <t>ball.png</t>
         </is>
       </c>
       <c r="I770" s="28" t="inlineStr">
@@ -42908,7 +42908,7 @@
       </c>
       <c r="H771" s="30" t="inlineStr">
         <is>
-          <t>Game.png</t>
+          <t>game.png</t>
         </is>
       </c>
       <c r="I771" s="30" t="inlineStr">
@@ -42963,7 +42963,7 @@
       </c>
       <c r="H772" s="28" t="inlineStr">
         <is>
-          <t>Song.png</t>
+          <t>song.png</t>
         </is>
       </c>
       <c r="I772" s="28" t="inlineStr">
@@ -43018,7 +43018,7 @@
       </c>
       <c r="H773" s="30" t="inlineStr">
         <is>
-          <t>Team.png</t>
+          <t>team.png</t>
         </is>
       </c>
       <c r="I773" s="30" t="inlineStr">
@@ -43073,7 +43073,7 @@
       </c>
       <c r="H774" s="28" t="inlineStr">
         <is>
-          <t>Show.png</t>
+          <t>show.png</t>
         </is>
       </c>
       <c r="I774" s="28" t="inlineStr">
@@ -43128,7 +43128,7 @@
       </c>
       <c r="H775" s="30" t="inlineStr">
         <is>
-          <t>Violin.png</t>
+          <t>violin.png</t>
         </is>
       </c>
       <c r="I775" s="30" t="inlineStr">
@@ -43183,7 +43183,7 @@
       </c>
       <c r="H776" s="28" t="inlineStr">
         <is>
-          <t>Flute.png</t>
+          <t>flute.png</t>
         </is>
       </c>
       <c r="I776" s="28" t="inlineStr">
@@ -43238,7 +43238,7 @@
       </c>
       <c r="H777" s="30" t="inlineStr">
         <is>
-          <t>Trumpet.png</t>
+          <t>trumpet.png</t>
         </is>
       </c>
       <c r="I777" s="30" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="H778" s="28" t="inlineStr">
         <is>
-          <t>Sport.png</t>
+          <t>sport.png</t>
         </is>
       </c>
       <c r="I778" s="28" t="inlineStr">
@@ -43348,7 +43348,7 @@
       </c>
       <c r="H779" s="30" t="inlineStr">
         <is>
-          <t>Soccer.png</t>
+          <t>soccer.png</t>
         </is>
       </c>
       <c r="I779" s="30" t="inlineStr">
@@ -43403,7 +43403,7 @@
       </c>
       <c r="H780" s="28" t="inlineStr">
         <is>
-          <t>Baseball.png</t>
+          <t>baseball.png</t>
         </is>
       </c>
       <c r="I780" s="28" t="inlineStr">
@@ -43458,7 +43458,7 @@
       </c>
       <c r="H781" s="30" t="inlineStr">
         <is>
-          <t>Basketball.png</t>
+          <t>basketball.png</t>
         </is>
       </c>
       <c r="I781" s="30" t="inlineStr">
@@ -43513,7 +43513,7 @@
       </c>
       <c r="H782" s="28" t="inlineStr">
         <is>
-          <t>Volleyball.png</t>
+          <t>volleyball.png</t>
         </is>
       </c>
       <c r="I782" s="28" t="inlineStr">
@@ -43568,7 +43568,7 @@
       </c>
       <c r="H783" s="30" t="inlineStr">
         <is>
-          <t>Tennis.png</t>
+          <t>tennis.png</t>
         </is>
       </c>
       <c r="I783" s="30" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="H784" s="28" t="inlineStr">
         <is>
-          <t>Golf.png</t>
+          <t>golf.png</t>
         </is>
       </c>
       <c r="I784" s="28" t="inlineStr">
@@ -43678,7 +43678,7 @@
       </c>
       <c r="H785" s="30" t="inlineStr">
         <is>
-          <t>Ski.png</t>
+          <t>ski.png</t>
         </is>
       </c>
       <c r="I785" s="30" t="inlineStr">
@@ -43733,7 +43733,7 @@
       </c>
       <c r="H786" s="28" t="inlineStr">
         <is>
-          <t>Skate.png</t>
+          <t>skate.png</t>
         </is>
       </c>
       <c r="I786" s="28" t="inlineStr">
@@ -43788,7 +43788,7 @@
       </c>
       <c r="H787" s="30" t="inlineStr">
         <is>
-          <t>Disk.png</t>
+          <t>disk.png</t>
         </is>
       </c>
       <c r="I787" s="30" t="inlineStr">
@@ -43843,7 +43843,7 @@
       </c>
       <c r="H788" s="28" t="inlineStr">
         <is>
-          <t>Firework.png</t>
+          <t>firework.png</t>
         </is>
       </c>
       <c r="I788" s="28" t="inlineStr">
@@ -43898,7 +43898,7 @@
       </c>
       <c r="H789" s="30" t="inlineStr">
         <is>
-          <t>Kite.png</t>
+          <t>kite.png</t>
         </is>
       </c>
       <c r="I789" s="30" t="inlineStr">
@@ -43953,7 +43953,7 @@
       </c>
       <c r="H790" s="28" t="inlineStr">
         <is>
-          <t>Badminton.png</t>
+          <t>badminton.png</t>
         </is>
       </c>
       <c r="I790" s="28" t="inlineStr">
@@ -44008,7 +44008,7 @@
       </c>
       <c r="H791" s="30" t="inlineStr">
         <is>
-          <t>Swimming.png</t>
+          <t>swimming.png</t>
         </is>
       </c>
       <c r="I791" s="30" t="inlineStr">
@@ -44063,7 +44063,7 @@
       </c>
       <c r="H792" s="28" t="inlineStr">
         <is>
-          <t>Skating.png</t>
+          <t>skating.png</t>
         </is>
       </c>
       <c r="I792" s="28" t="inlineStr">
@@ -44118,7 +44118,7 @@
       </c>
       <c r="H793" s="30" t="inlineStr">
         <is>
-          <t>Skiing.png</t>
+          <t>skiing.png</t>
         </is>
       </c>
       <c r="I793" s="30" t="inlineStr">
@@ -44173,7 +44173,7 @@
       </c>
       <c r="H794" s="28" t="inlineStr">
         <is>
-          <t>Boxing.png</t>
+          <t>boxing.png</t>
         </is>
       </c>
       <c r="I794" s="28" t="inlineStr">
@@ -44228,7 +44228,7 @@
       </c>
       <c r="H795" s="30" t="inlineStr">
         <is>
-          <t>Taekwondo.png</t>
+          <t>taekwondo.png</t>
         </is>
       </c>
       <c r="I795" s="30" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="H796" s="28" t="inlineStr">
         <is>
-          <t>Hiking.png</t>
+          <t>hiking.png</t>
         </is>
       </c>
       <c r="I796" s="28" t="inlineStr">
@@ -44338,7 +44338,7 @@
       </c>
       <c r="H797" s="30" t="inlineStr">
         <is>
-          <t>Camping.png</t>
+          <t>camping.png</t>
         </is>
       </c>
       <c r="I797" s="30" t="inlineStr">
@@ -44393,7 +44393,7 @@
       </c>
       <c r="H798" s="28" t="inlineStr">
         <is>
-          <t>Fishing.png</t>
+          <t>fishing.png</t>
         </is>
       </c>
       <c r="I798" s="28" t="inlineStr">
@@ -44448,7 +44448,7 @@
       </c>
       <c r="H799" s="30" t="inlineStr">
         <is>
-          <t>Drawing.png</t>
+          <t>drawing.png</t>
         </is>
       </c>
       <c r="I799" s="30" t="inlineStr">
@@ -44503,7 +44503,7 @@
       </c>
       <c r="H800" s="28" t="inlineStr">
         <is>
-          <t>Cooking.png</t>
+          <t>cooking.png</t>
         </is>
       </c>
       <c r="I800" s="28" t="inlineStr">
@@ -44558,7 +44558,7 @@
       </c>
       <c r="H801" s="30" t="inlineStr">
         <is>
-          <t>Puzzle.png</t>
+          <t>puzzle.png</t>
         </is>
       </c>
       <c r="I801" s="30" t="inlineStr">
